--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -43,7 +43,7 @@
     <t>payable to ranjita 3100</t>
   </si>
   <si>
-    <t>14550 to be pay to trungpham by ranjita</t>
+    <t>14550 to be pay to tungpham by ranjita</t>
   </si>
 </sst>
 </file>
@@ -324,7 +324,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -787,11 +786,11 @@
           </c:extLst>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="57019776"/>
-        <c:axId val="68555904"/>
+        <c:axId val="67114112"/>
+        <c:axId val="67115648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="57019776"/>
+        <c:axId val="67114112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -831,14 +830,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68555904"/>
+        <c:crossAx val="67115648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="68555904"/>
+        <c:axId val="67115648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -887,7 +886,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57019776"/>
+        <c:crossAx val="67114112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -901,7 +900,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -960,7 +958,7 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000311" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000311" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageMargins b="0.75000000000000322" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000322" header="0.30000000000000032" footer="0.30000000000000032"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1256,7 +1254,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1264,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H35"/>
+  <dimension ref="B1:H37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -1891,6 +1889,48 @@
         <v>9</v>
       </c>
     </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="10">
+        <v>45380</v>
+      </c>
+      <c r="C36" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D36" s="11">
+        <v>290600</v>
+      </c>
+      <c r="E36" s="11">
+        <v>29500</v>
+      </c>
+      <c r="F36" s="11">
+        <v>261100</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="10">
+        <v>45380</v>
+      </c>
+      <c r="C37" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D37" s="11">
+        <f>297400-500</f>
+        <v>296900</v>
+      </c>
+      <c r="E37" s="11">
+        <f>19500-500</f>
+        <v>19000</v>
+      </c>
+      <c r="F37" s="11">
+        <v>277900</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="6000" windowWidth="20640" windowHeight="11760"/>
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -49,13 +49,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,7 +296,17 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -324,6 +334,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -332,10 +343,12 @@
         <a:effectLst/>
       </c:spPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -443,6 +456,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-588A-4FD6-90A1-C2BC5C3DF530}"/>
@@ -556,6 +570,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-588A-4FD6-90A1-C2BC5C3DF530}"/>
@@ -666,6 +681,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-588A-4FD6-90A1-C2BC5C3DF530}"/>
@@ -779,23 +795,36 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
-        <c:axId val="67114112"/>
-        <c:axId val="67115648"/>
+        <c:smooth val="0"/>
+        <c:axId val="133678592"/>
+        <c:axId val="133680128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="67114112"/>
+        <c:axId val="133678592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -830,17 +859,18 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67115648"/>
+        <c:crossAx val="133680128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="67115648"/>
+        <c:axId val="133680128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -858,6 +888,7 @@
         </c:majorGridlines>
         <c:numFmt formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -886,7 +917,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67114112"/>
+        <c:crossAx val="133678592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -900,6 +931,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -930,6 +962,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1261,9 +1294,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:H46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="2" customWidth="1"/>
@@ -1276,8 +1309,8 @@
     <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="20.100000000000001" customHeight="1"/>
-    <row r="2" spans="2:8" ht="34.5" customHeight="1" thickBot="1">
+    <row r="1" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -1292,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:8" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1312,7 +1345,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" thickTop="1">
+    <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8">
         <v>45221</v>
       </c>
@@ -1329,7 +1362,7 @@
         <v>40400</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
         <v>45227</v>
       </c>
@@ -1346,7 +1379,7 @@
         <v>37100</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12">
         <v>45235</v>
       </c>
@@ -1363,7 +1396,7 @@
         <v>37100</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>45242</v>
       </c>
@@ -1381,7 +1414,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12">
         <v>45249</v>
       </c>
@@ -1396,7 +1429,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
         <v>45256</v>
       </c>
@@ -1413,7 +1446,7 @@
         <v>57200</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>45270</v>
       </c>
@@ -1431,7 +1464,7 @@
         <v>49400</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="12">
         <v>45277</v>
       </c>
@@ -1448,7 +1481,7 @@
         <v>177050</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
         <v>45284</v>
       </c>
@@ -1465,7 +1498,7 @@
         <v>216750</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>45291</v>
       </c>
@@ -1482,7 +1515,7 @@
         <v>205750</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>45298</v>
       </c>
@@ -1500,7 +1533,7 @@
         <v>211350</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>45301</v>
       </c>
@@ -1517,7 +1550,7 @@
         <v>250950</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10">
         <v>45305</v>
       </c>
@@ -1535,7 +1568,7 @@
       </c>
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10">
         <v>45308</v>
       </c>
@@ -1553,7 +1586,7 @@
       </c>
       <c r="G17" s="14"/>
     </row>
-    <row r="18" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>45316</v>
       </c>
@@ -1571,7 +1604,7 @@
       </c>
       <c r="G18" s="14"/>
     </row>
-    <row r="19" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="10">
         <v>45316</v>
       </c>
@@ -1589,7 +1622,7 @@
       </c>
       <c r="G19" s="14"/>
     </row>
-    <row r="20" spans="2:8" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="10">
         <v>45320</v>
       </c>
@@ -1610,7 +1643,7 @@
       </c>
       <c r="H20" s="14"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10">
         <v>45321</v>
       </c>
@@ -1627,7 +1660,7 @@
         <v>249250</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10">
         <v>45325</v>
       </c>
@@ -1645,7 +1678,7 @@
         <v>240150</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10">
         <v>45325</v>
       </c>
@@ -1662,7 +1695,7 @@
         <v>251850</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10">
         <v>45331</v>
       </c>
@@ -1679,7 +1712,7 @@
         <v>239750</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
         <v>45331</v>
       </c>
@@ -1696,7 +1729,7 @@
         <v>261650</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
         <v>45333</v>
       </c>
@@ -1713,7 +1746,7 @@
         <v>280050</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
         <v>45339</v>
       </c>
@@ -1731,7 +1764,7 @@
       </c>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
         <v>45339</v>
       </c>
@@ -1752,7 +1785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <v>45347</v>
       </c>
@@ -1772,7 +1805,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="10">
         <v>45353</v>
       </c>
@@ -1792,7 +1825,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="10">
         <v>45353</v>
       </c>
@@ -1812,7 +1845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
         <v>45359</v>
       </c>
@@ -1832,7 +1865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="10">
         <v>45359</v>
       </c>
@@ -1850,7 +1883,7 @@
       </c>
       <c r="G33" s="14"/>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="10">
         <v>45373</v>
       </c>
@@ -1869,7 +1902,7 @@
       </c>
       <c r="G34" s="14"/>
     </row>
-    <row r="35" spans="2:7">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="10">
         <v>45373</v>
       </c>
@@ -1889,7 +1922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="10">
         <v>45380</v>
       </c>
@@ -1909,7 +1942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="10">
         <v>45380</v>
       </c>
@@ -1929,6 +1962,160 @@
       </c>
       <c r="G37" s="14" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="10">
+        <v>45387</v>
+      </c>
+      <c r="C38" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D38" s="11">
+        <f>297400-500</f>
+        <v>296900</v>
+      </c>
+      <c r="E38" s="11">
+        <v>36650</v>
+      </c>
+      <c r="F38" s="11">
+        <v>260250</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="10">
+        <v>45387</v>
+      </c>
+      <c r="C39" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D39" s="11">
+        <v>300900</v>
+      </c>
+      <c r="E39" s="11">
+        <v>16650</v>
+      </c>
+      <c r="F39" s="11">
+        <v>284250</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="10">
+        <v>45392</v>
+      </c>
+      <c r="C40" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D40" s="11">
+        <v>300900</v>
+      </c>
+      <c r="E40" s="11">
+        <v>22800</v>
+      </c>
+      <c r="F40" s="11">
+        <v>278100</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="10">
+        <v>45392</v>
+      </c>
+      <c r="C41" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D41" s="11">
+        <v>307700</v>
+      </c>
+      <c r="E41" s="11">
+        <v>12800</v>
+      </c>
+      <c r="F41" s="11">
+        <v>294900</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="10">
+        <v>45399</v>
+      </c>
+      <c r="C42" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D42" s="11">
+        <v>307700</v>
+      </c>
+      <c r="E42" s="11">
+        <v>31150</v>
+      </c>
+      <c r="F42" s="11">
+        <v>276550</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="10">
+        <v>45399</v>
+      </c>
+      <c r="C43" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D43" s="11">
+        <v>312700</v>
+      </c>
+      <c r="E43" s="11">
+        <v>6150</v>
+      </c>
+      <c r="F43" s="11">
+        <v>306550</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="10">
+        <v>45410</v>
+      </c>
+      <c r="C44" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D44" s="11">
+        <v>312700</v>
+      </c>
+      <c r="E44" s="11">
+        <v>30600</v>
+      </c>
+      <c r="F44" s="11">
+        <v>282100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="10">
+        <v>45410</v>
+      </c>
+      <c r="C45" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D45" s="11">
+        <v>339900</v>
+      </c>
+      <c r="E45" s="11">
+        <v>-9400</v>
+      </c>
+      <c r="F45" s="11">
+        <v>349300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="10">
+        <v>45416</v>
+      </c>
+      <c r="C46" s="11">
+        <v>173380</v>
+      </c>
+      <c r="D46" s="11">
+        <v>339900</v>
+      </c>
+      <c r="E46" s="11">
+        <v>1150</v>
+      </c>
+      <c r="F46" s="11">
+        <v>338750</v>
       </c>
     </row>
   </sheetData>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>14550 to be pay to tungpham by ranjita</t>
+  </si>
+  <si>
+    <t>oil expenses 1000</t>
   </si>
 </sst>
 </file>
@@ -334,6 +337,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -812,11 +816,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="133678592"/>
-        <c:axId val="133680128"/>
+        <c:axId val="161495680"/>
+        <c:axId val="168243968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="133678592"/>
+        <c:axId val="161495680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -859,14 +863,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="133680128"/>
+        <c:crossAx val="168243968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="133680128"/>
+        <c:axId val="168243968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -917,7 +921,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="133678592"/>
+        <c:crossAx val="161495680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -931,6 +935,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1287,7 +1292,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1295,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -2118,6 +2123,60 @@
         <v>338750</v>
       </c>
     </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="10">
+        <v>45423</v>
+      </c>
+      <c r="C47" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D47" s="11">
+        <v>339900</v>
+      </c>
+      <c r="E47" s="11">
+        <v>17150</v>
+      </c>
+      <c r="F47" s="11">
+        <v>322750</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="10">
+        <v>45424</v>
+      </c>
+      <c r="C48" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D48" s="11">
+        <v>340900</v>
+      </c>
+      <c r="E48" s="11">
+        <v>12150</v>
+      </c>
+      <c r="F48" s="11">
+        <v>328750</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="10">
+        <v>45424</v>
+      </c>
+      <c r="C49" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D49" s="11">
+        <v>339900</v>
+      </c>
+      <c r="E49" s="11">
+        <v>11150</v>
+      </c>
+      <c r="F49" s="11">
+        <v>328750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>oil expenses 1000</t>
+  </si>
+  <si>
+    <t>payable 6000 to ranjita</t>
   </si>
 </sst>
 </file>
@@ -816,11 +819,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="161495680"/>
-        <c:axId val="168243968"/>
+        <c:axId val="48681728"/>
+        <c:axId val="48683264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="161495680"/>
+        <c:axId val="48681728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -863,14 +866,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="168243968"/>
+        <c:crossAx val="48683264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="168243968"/>
+        <c:axId val="48683264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -921,7 +924,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161495680"/>
+        <c:crossAx val="48681728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1292,7 +1295,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1300,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H49"/>
+  <dimension ref="B1:H55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -2160,7 +2163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="10">
         <v>45424</v>
       </c>
@@ -2176,6 +2179,101 @@
       <c r="F49" s="11">
         <v>328750</v>
       </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="10">
+        <v>45425</v>
+      </c>
+      <c r="C50" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D50" s="11">
+        <v>342500</v>
+      </c>
+      <c r="E50" s="11">
+        <v>-2050</v>
+      </c>
+      <c r="F50" s="11">
+        <v>344550</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="10">
+        <v>45429</v>
+      </c>
+      <c r="C51" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D51" s="11">
+        <v>342500</v>
+      </c>
+      <c r="E51" s="11">
+        <v>4250</v>
+      </c>
+      <c r="F51" s="11">
+        <v>338250</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="10">
+        <v>45429</v>
+      </c>
+      <c r="C52" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D52" s="11">
+        <v>343500</v>
+      </c>
+      <c r="E52" s="11">
+        <v>-750</v>
+      </c>
+      <c r="F52" s="11">
+        <v>344250</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="10">
+        <v>45431</v>
+      </c>
+      <c r="C53" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D53" s="11">
+        <v>343500</v>
+      </c>
+      <c r="E53" s="11">
+        <v>13700</v>
+      </c>
+      <c r="F53" s="11">
+        <v>329800</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="10">
+        <v>45431</v>
+      </c>
+      <c r="C54" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D54" s="11">
+        <v>365900</v>
+      </c>
+      <c r="E54" s="11">
+        <v>-6300</v>
+      </c>
+      <c r="F54" s="11">
+        <v>372200</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="10"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>payable 6000 to ranjita</t>
+  </si>
+  <si>
+    <t>payable 15000</t>
+  </si>
+  <si>
+    <t>payable 10000</t>
   </si>
 </sst>
 </file>
@@ -819,11 +825,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="48681728"/>
-        <c:axId val="48683264"/>
+        <c:axId val="164372480"/>
+        <c:axId val="164375936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="48681728"/>
+        <c:axId val="164372480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -866,14 +872,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48683264"/>
+        <c:crossAx val="164375936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="48683264"/>
+        <c:axId val="164375936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -924,7 +930,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48681728"/>
+        <c:crossAx val="164372480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1295,7 +1301,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1303,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H55"/>
+  <dimension ref="B1:H63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -2256,24 +2262,186 @@
         <v>178380</v>
       </c>
       <c r="D54" s="11">
-        <v>365900</v>
+        <v>348500</v>
       </c>
       <c r="E54" s="11">
-        <v>-6300</v>
+        <v>15300</v>
       </c>
       <c r="F54" s="11">
-        <v>372200</v>
+        <v>348200</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="10"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
+      <c r="B55" s="10">
+        <v>45436</v>
+      </c>
+      <c r="C55" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D55" s="11">
+        <v>348500</v>
+      </c>
+      <c r="E55" s="11">
+        <v>25050</v>
+      </c>
+      <c r="F55" s="11">
+        <v>338650</v>
+      </c>
+      <c r="G55" s="2">
+        <f>372200-24000</f>
+        <v>348200</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="10">
+        <v>45436</v>
+      </c>
+      <c r="C56" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D56" s="11">
+        <v>350800</v>
+      </c>
+      <c r="E56" s="11">
+        <v>15050</v>
+      </c>
+      <c r="F56" s="11">
+        <v>350550</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="10">
+        <v>45437</v>
+      </c>
+      <c r="C57" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D57" s="11">
+        <v>350800</v>
+      </c>
+      <c r="E57" s="11">
+        <v>24800</v>
+      </c>
+      <c r="F57" s="11">
+        <v>341050</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="10">
+        <v>45437</v>
+      </c>
+      <c r="C58" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D58" s="11">
+        <v>351850</v>
+      </c>
+      <c r="E58" s="11">
+        <v>19800</v>
+      </c>
+      <c r="F58" s="11">
+        <v>347050</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="10">
+        <v>45443</v>
+      </c>
+      <c r="C59" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D59" s="11">
+        <v>351850</v>
+      </c>
+      <c r="E59" s="11">
+        <v>28450</v>
+      </c>
+      <c r="F59" s="11">
+        <v>338400</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="10">
+        <v>45443</v>
+      </c>
+      <c r="C60" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D60" s="11">
+        <v>353850</v>
+      </c>
+      <c r="E60" s="11">
+        <v>18450</v>
+      </c>
+      <c r="F60" s="11">
+        <v>350400</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="10">
+        <v>45444</v>
+      </c>
+      <c r="C61" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D61" s="11">
+        <v>353850</v>
+      </c>
+      <c r="E61" s="11">
+        <v>31200</v>
+      </c>
+      <c r="F61" s="11">
+        <v>337650</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="10">
+        <v>45444</v>
+      </c>
+      <c r="C62" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D62" s="11">
+        <v>357850</v>
+      </c>
+      <c r="E62" s="11">
+        <v>11200</v>
+      </c>
+      <c r="F62" s="11">
+        <v>361650</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="10">
+        <v>45448</v>
+      </c>
+      <c r="C63" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D63" s="11">
+        <v>357850</v>
+      </c>
+      <c r="E63" s="11">
+        <v>8600</v>
+      </c>
+      <c r="F63" s="11">
+        <v>359250</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -23,9 +23,6 @@
   </si>
   <si>
     <t>CashBalance</t>
-  </si>
-  <si>
-    <t>Investments</t>
   </si>
   <si>
     <t>On Current Date</t>
@@ -56,6 +53,21 @@
   </si>
   <si>
     <t>payable 10000</t>
+  </si>
+  <si>
+    <t>collected 69600-1400</t>
+  </si>
+  <si>
+    <t>paid 50000 to suresh</t>
+  </si>
+  <si>
+    <t>paid loan 10000</t>
+  </si>
+  <si>
+    <t>equity</t>
+  </si>
+  <si>
+    <t>investment</t>
   </si>
 </sst>
 </file>
@@ -371,7 +383,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Investments</c:v>
+                  <c:v>equity</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -481,7 +493,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'2023TrendAnalysis'!$D$2</c:f>
+              <c:f>'2023TrendAnalysis'!$E$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -543,7 +555,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2023TrendAnalysis'!$D$3:$D$13</c:f>
+              <c:f>'2023TrendAnalysis'!$E$3:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="11"/>
@@ -595,7 +607,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'2023TrendAnalysis'!$E$2</c:f>
+              <c:f>'2023TrendAnalysis'!$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -657,7 +669,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2023TrendAnalysis'!$E$3:$E$13</c:f>
+              <c:f>'2023TrendAnalysis'!$F$3:$F$13</c:f>
               <c:numCache>
                 <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="11"/>
@@ -706,7 +718,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'2023TrendAnalysis'!$F$2</c:f>
+              <c:f>'2023TrendAnalysis'!$G$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -768,7 +780,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2023TrendAnalysis'!$F$3:$F$13</c:f>
+              <c:f>'2023TrendAnalysis'!$G$3:$G$13</c:f>
               <c:numCache>
                 <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="11"/>
@@ -825,11 +837,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="164372480"/>
-        <c:axId val="164375936"/>
+        <c:axId val="149872000"/>
+        <c:axId val="149877888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="164372480"/>
+        <c:axId val="149872000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -872,14 +884,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="164375936"/>
+        <c:crossAx val="149877888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="164375936"/>
+        <c:axId val="149877888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -930,7 +942,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="164372480"/>
+        <c:crossAx val="149872000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1015,13 +1027,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
@@ -1309,372 +1321,394 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H63"/>
+  <dimension ref="B1:I67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="4" width="15" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="C3" s="6">
         <v>35000</v>
       </c>
-      <c r="D3" s="6" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="D3" s="6"/>
       <c r="E3" s="6" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F3" s="7" t="e">
+      <c r="F3" s="6" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="7" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8">
         <v>45221</v>
       </c>
       <c r="C4" s="9">
         <v>35000</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9">
         <v>41200</v>
       </c>
-      <c r="E4" s="9">
+      <c r="F4" s="9">
         <v>800</v>
       </c>
-      <c r="F4" s="9">
+      <c r="G4" s="9">
         <v>40400</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
         <v>45227</v>
       </c>
       <c r="C5" s="11">
         <v>35000</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11">
         <v>41200</v>
       </c>
-      <c r="E5" s="11">
+      <c r="F5" s="11">
         <v>4100</v>
       </c>
-      <c r="F5" s="11">
+      <c r="G5" s="11">
         <v>37100</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12">
         <v>45235</v>
       </c>
       <c r="C6" s="13">
         <v>35000</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="13"/>
+      <c r="E6" s="13">
         <v>41200</v>
       </c>
-      <c r="E6" s="13">
+      <c r="F6" s="13">
         <v>4100</v>
       </c>
-      <c r="F6" s="13">
+      <c r="G6" s="13">
         <v>37100</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>45242</v>
       </c>
       <c r="C7" s="11">
         <v>34880</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="11"/>
+      <c r="E7" s="11">
         <v>46100</v>
       </c>
-      <c r="E7" s="11">
+      <c r="F7" s="11">
         <v>0</v>
       </c>
-      <c r="F7" s="11">
+      <c r="G7" s="11">
         <v>46100</v>
       </c>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12">
         <v>45249</v>
       </c>
       <c r="C8" s="13">
         <v>34880</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13">
         <v>46100</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13">
+      <c r="F8" s="13"/>
+      <c r="G8" s="13">
         <v>46100</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
         <v>45256</v>
       </c>
       <c r="C9" s="11">
         <v>44880</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="11"/>
+      <c r="E9" s="11">
         <v>59050</v>
       </c>
-      <c r="E9" s="11">
+      <c r="F9" s="11">
         <v>1850</v>
       </c>
-      <c r="F9" s="11">
+      <c r="G9" s="11">
         <v>57200</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>45270</v>
       </c>
       <c r="C10" s="11">
         <v>44880</v>
       </c>
-      <c r="D10" s="11">
-        <f>E10+F10</f>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11">
+        <f>F10+G10</f>
         <v>58500</v>
       </c>
-      <c r="E10" s="11">
+      <c r="F10" s="11">
         <v>9100</v>
       </c>
-      <c r="F10" s="11">
+      <c r="G10" s="11">
         <v>49400</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="12">
         <v>45277</v>
       </c>
       <c r="C11" s="13">
         <v>134880</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="13"/>
+      <c r="E11" s="13">
         <v>190050</v>
       </c>
-      <c r="E11" s="13">
+      <c r="F11" s="13">
         <v>13000</v>
       </c>
-      <c r="F11" s="13">
+      <c r="G11" s="13">
         <v>177050</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
         <v>45284</v>
       </c>
       <c r="C12" s="11">
         <v>159880</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11">
         <v>222250</v>
       </c>
-      <c r="E12" s="11">
+      <c r="F12" s="11">
         <v>5500</v>
       </c>
-      <c r="F12" s="11">
+      <c r="G12" s="11">
         <v>216750</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>45291</v>
       </c>
       <c r="C13" s="11">
         <v>159880</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="11"/>
+      <c r="E13" s="13">
         <v>222250</v>
       </c>
-      <c r="E13" s="13">
+      <c r="F13" s="13">
         <v>16800</v>
       </c>
-      <c r="F13" s="13">
+      <c r="G13" s="13">
         <v>205750</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>45298</v>
       </c>
       <c r="C14" s="11">
         <v>159880</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11">
         <v>230000</v>
       </c>
-      <c r="E14" s="11">
+      <c r="F14" s="11">
         <f>5000+8100+2850+2700</f>
         <v>18650</v>
       </c>
-      <c r="F14" s="11">
+      <c r="G14" s="11">
         <v>211350</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>45301</v>
       </c>
       <c r="C15" s="11">
         <v>159880</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="11"/>
+      <c r="E15" s="13">
         <v>250800</v>
       </c>
-      <c r="E15" s="13">
+      <c r="F15" s="13">
         <v>-150</v>
       </c>
-      <c r="F15" s="13">
+      <c r="G15" s="13">
         <v>250950</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10">
         <v>45305</v>
       </c>
       <c r="C16" s="11">
         <v>159880</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="11"/>
+      <c r="E16" s="11">
         <v>242050</v>
       </c>
-      <c r="E16" s="11">
+      <c r="F16" s="11">
         <v>5950</v>
       </c>
-      <c r="F16" s="11">
+      <c r="G16" s="11">
         <v>236100</v>
       </c>
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10">
         <v>45308</v>
       </c>
       <c r="C17" s="11">
         <v>159880</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="11"/>
+      <c r="E17" s="11">
         <v>242050</v>
       </c>
-      <c r="E17" s="11">
+      <c r="F17" s="11">
         <v>12550</v>
       </c>
-      <c r="F17" s="11">
+      <c r="G17" s="11">
         <v>229250</v>
       </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>45316</v>
       </c>
       <c r="C18" s="11">
         <v>159880</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11">
         <v>242050</v>
       </c>
-      <c r="E18" s="11">
+      <c r="F18" s="11">
         <v>17550</v>
       </c>
-      <c r="F18" s="11">
+      <c r="G18" s="11">
         <v>224900</v>
       </c>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="10">
         <v>45316</v>
       </c>
       <c r="C19" s="11">
         <v>159880</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="11"/>
+      <c r="E19" s="11">
         <v>249250</v>
       </c>
-      <c r="E19" s="11">
+      <c r="F19" s="11">
         <v>7550</v>
       </c>
-      <c r="F19" s="11">
+      <c r="G19" s="11">
         <v>241700</v>
       </c>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="10">
         <v>45320</v>
       </c>
       <c r="C20" s="11">
         <v>159880</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="11"/>
+      <c r="E20" s="11">
         <v>249250</v>
       </c>
-      <c r="E20" s="11">
+      <c r="F20" s="11">
         <v>16800</v>
       </c>
-      <c r="F20" s="11">
+      <c r="G20" s="11">
         <v>232450</v>
       </c>
-      <c r="G20" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="10">
         <v>45321</v>
       </c>
       <c r="C21" s="11">
         <v>159880</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="11"/>
+      <c r="E21" s="11">
         <v>255900</v>
       </c>
-      <c r="E21" s="11">
+      <c r="F21" s="11">
         <v>6650</v>
       </c>
-      <c r="F21" s="11">
+      <c r="G21" s="11">
         <v>249250</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="10">
         <v>45325</v>
       </c>
@@ -1682,765 +1716,895 @@
         <f>159880+1500</f>
         <v>161380</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="11"/>
+      <c r="E22" s="11">
         <v>257400</v>
       </c>
-      <c r="E22" s="11">
+      <c r="F22" s="11">
         <v>18650</v>
       </c>
-      <c r="F22" s="11">
+      <c r="G22" s="11">
         <v>240150</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="10">
         <v>45325</v>
       </c>
       <c r="C23" s="11">
         <v>161380</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11">
         <v>252850</v>
       </c>
-      <c r="E23" s="11">
+      <c r="F23" s="11">
         <v>1000</v>
       </c>
-      <c r="F23" s="11">
+      <c r="G23" s="11">
         <v>251850</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="10">
         <v>45331</v>
       </c>
       <c r="C24" s="11">
         <v>161380</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="11"/>
+      <c r="E24" s="11">
         <v>251450</v>
       </c>
-      <c r="E24" s="11">
+      <c r="F24" s="11">
         <v>11700</v>
       </c>
-      <c r="F24" s="11">
+      <c r="G24" s="11">
         <v>239750</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
         <v>45331</v>
       </c>
       <c r="C25" s="11">
         <v>161380</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11">
         <v>253500</v>
       </c>
-      <c r="E25" s="11">
+      <c r="F25" s="11">
         <v>-8150</v>
       </c>
-      <c r="F25" s="11">
+      <c r="G25" s="11">
         <v>261650</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
         <v>45333</v>
       </c>
       <c r="C26" s="11">
         <v>161380</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="11"/>
+      <c r="E26" s="11">
         <v>257450</v>
       </c>
-      <c r="E26" s="11">
+      <c r="F26" s="11">
         <v>-22600</v>
       </c>
-      <c r="F26" s="11">
+      <c r="G26" s="11">
         <v>280050</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
         <v>45339</v>
       </c>
       <c r="C27" s="11">
         <v>161380</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="11"/>
+      <c r="E27" s="11">
         <v>257450</v>
       </c>
-      <c r="E27" s="11">
+      <c r="F27" s="11">
         <v>-7450</v>
       </c>
-      <c r="F27" s="11">
+      <c r="G27" s="11">
         <v>265300</v>
       </c>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
         <v>45339</v>
       </c>
       <c r="C28" s="11">
         <v>173380</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="11"/>
+      <c r="E28" s="11">
         <f>272250+1600</f>
         <v>273850</v>
       </c>
-      <c r="E28" s="11">
+      <c r="F28" s="11">
         <v>-15450</v>
       </c>
-      <c r="F28" s="11">
+      <c r="G28" s="11">
         <v>287700</v>
       </c>
-      <c r="G28" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H28" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <v>45347</v>
       </c>
       <c r="C29" s="11">
         <v>173380</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="11"/>
+      <c r="E29" s="11">
         <v>273850</v>
       </c>
-      <c r="E29" s="11">
+      <c r="F29" s="11">
         <v>-2000</v>
       </c>
-      <c r="F29" s="11">
+      <c r="G29" s="11">
         <v>275850</v>
       </c>
-      <c r="G29" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H29" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="10">
         <v>45353</v>
       </c>
       <c r="C30" s="11">
         <v>173380</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="11"/>
+      <c r="E30" s="11">
         <v>273850</v>
       </c>
-      <c r="E30" s="11">
+      <c r="F30" s="11">
         <v>11150</v>
       </c>
-      <c r="F30" s="11">
+      <c r="G30" s="11">
         <v>262700</v>
       </c>
-      <c r="G30" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H30" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="10">
         <v>45353</v>
       </c>
       <c r="C31" s="11">
         <v>173380</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="11"/>
+      <c r="E31" s="11">
         <v>279800</v>
       </c>
-      <c r="E31" s="11">
+      <c r="F31" s="11">
         <v>-3100</v>
       </c>
-      <c r="F31" s="11">
+      <c r="G31" s="11">
         <v>282900</v>
       </c>
-      <c r="G31" s="14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H31" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
         <v>45359</v>
       </c>
       <c r="C32" s="11">
         <v>173380</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="11"/>
+      <c r="E32" s="11">
         <v>279800</v>
       </c>
-      <c r="E32" s="11">
+      <c r="F32" s="11">
         <v>11600</v>
       </c>
-      <c r="F32" s="11">
+      <c r="G32" s="11">
         <v>268200</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="10">
         <v>45359</v>
       </c>
       <c r="C33" s="11">
         <v>173380</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="11"/>
+      <c r="E33" s="11">
         <v>286600</v>
       </c>
-      <c r="E33" s="11">
+      <c r="F33" s="11">
         <v>1600</v>
       </c>
-      <c r="F33" s="11">
+      <c r="G33" s="11">
         <v>285000</v>
       </c>
-      <c r="G33" s="14"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="10">
         <v>45373</v>
       </c>
       <c r="C34" s="11">
         <v>173380</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="11"/>
+      <c r="E34" s="11">
         <v>286600</v>
       </c>
-      <c r="E34" s="11">
+      <c r="F34" s="11">
         <f>32450+2100</f>
         <v>34550</v>
       </c>
-      <c r="F34" s="11">
+      <c r="G34" s="11">
         <v>252050</v>
       </c>
-      <c r="G34" s="14"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="10">
         <v>45373</v>
       </c>
       <c r="C35" s="11">
         <v>173380</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="11"/>
+      <c r="E35" s="11">
         <v>290600</v>
       </c>
-      <c r="E35" s="11">
+      <c r="F35" s="11">
         <v>14550</v>
       </c>
-      <c r="F35" s="11">
+      <c r="G35" s="11">
         <v>276050</v>
       </c>
-      <c r="G35" s="14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="10">
         <v>45380</v>
       </c>
       <c r="C36" s="11">
         <v>173380</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="11"/>
+      <c r="E36" s="11">
         <v>290600</v>
       </c>
-      <c r="E36" s="11">
+      <c r="F36" s="11">
         <v>29500</v>
       </c>
-      <c r="F36" s="11">
+      <c r="G36" s="11">
         <v>261100</v>
       </c>
-      <c r="G36" s="14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="10">
         <v>45380</v>
       </c>
       <c r="C37" s="11">
         <v>173380</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="11"/>
+      <c r="E37" s="11">
         <f>297400-500</f>
         <v>296900</v>
       </c>
-      <c r="E37" s="11">
+      <c r="F37" s="11">
         <f>19500-500</f>
         <v>19000</v>
       </c>
-      <c r="F37" s="11">
+      <c r="G37" s="11">
         <v>277900</v>
       </c>
-      <c r="G37" s="14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="10">
         <v>45387</v>
       </c>
       <c r="C38" s="11">
         <v>173380</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="11"/>
+      <c r="E38" s="11">
         <f>297400-500</f>
         <v>296900</v>
       </c>
-      <c r="E38" s="11">
+      <c r="F38" s="11">
         <v>36650</v>
       </c>
-      <c r="F38" s="11">
+      <c r="G38" s="11">
         <v>260250</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="10">
         <v>45387</v>
       </c>
       <c r="C39" s="11">
         <v>173380</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="11"/>
+      <c r="E39" s="11">
         <v>300900</v>
       </c>
-      <c r="E39" s="11">
+      <c r="F39" s="11">
         <v>16650</v>
       </c>
-      <c r="F39" s="11">
+      <c r="G39" s="11">
         <v>284250</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="10">
         <v>45392</v>
       </c>
       <c r="C40" s="11">
         <v>173380</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="11"/>
+      <c r="E40" s="11">
         <v>300900</v>
       </c>
-      <c r="E40" s="11">
+      <c r="F40" s="11">
         <v>22800</v>
       </c>
-      <c r="F40" s="11">
+      <c r="G40" s="11">
         <v>278100</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="10">
         <v>45392</v>
       </c>
       <c r="C41" s="11">
         <v>173380</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="11"/>
+      <c r="E41" s="11">
         <v>307700</v>
       </c>
-      <c r="E41" s="11">
+      <c r="F41" s="11">
         <v>12800</v>
       </c>
-      <c r="F41" s="11">
+      <c r="G41" s="11">
         <v>294900</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="10">
         <v>45399</v>
       </c>
       <c r="C42" s="11">
         <v>173380</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="11"/>
+      <c r="E42" s="11">
         <v>307700</v>
       </c>
-      <c r="E42" s="11">
+      <c r="F42" s="11">
         <v>31150</v>
       </c>
-      <c r="F42" s="11">
+      <c r="G42" s="11">
         <v>276550</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="10">
         <v>45399</v>
       </c>
       <c r="C43" s="11">
         <v>173380</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="11"/>
+      <c r="E43" s="11">
         <v>312700</v>
       </c>
-      <c r="E43" s="11">
+      <c r="F43" s="11">
         <v>6150</v>
       </c>
-      <c r="F43" s="11">
+      <c r="G43" s="11">
         <v>306550</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="10">
         <v>45410</v>
       </c>
       <c r="C44" s="11">
         <v>173380</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="11"/>
+      <c r="E44" s="11">
         <v>312700</v>
       </c>
-      <c r="E44" s="11">
+      <c r="F44" s="11">
         <v>30600</v>
       </c>
-      <c r="F44" s="11">
+      <c r="G44" s="11">
         <v>282100</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="10">
         <v>45410</v>
       </c>
       <c r="C45" s="11">
         <v>173380</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="11"/>
+      <c r="E45" s="11">
         <v>339900</v>
       </c>
-      <c r="E45" s="11">
+      <c r="F45" s="11">
         <v>-9400</v>
       </c>
-      <c r="F45" s="11">
+      <c r="G45" s="11">
         <v>349300</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="10">
         <v>45416</v>
       </c>
       <c r="C46" s="11">
         <v>173380</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="11"/>
+      <c r="E46" s="11">
         <v>339900</v>
       </c>
-      <c r="E46" s="11">
+      <c r="F46" s="11">
         <v>1150</v>
       </c>
-      <c r="F46" s="11">
+      <c r="G46" s="11">
         <v>338750</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="10">
         <v>45423</v>
       </c>
       <c r="C47" s="11">
         <v>178380</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="11"/>
+      <c r="E47" s="11">
         <v>339900</v>
       </c>
-      <c r="E47" s="11">
+      <c r="F47" s="11">
         <v>17150</v>
       </c>
-      <c r="F47" s="11">
+      <c r="G47" s="11">
         <v>322750</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B48" s="10">
         <v>45424</v>
       </c>
       <c r="C48" s="11">
         <v>178380</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="11"/>
+      <c r="E48" s="11">
         <v>340900</v>
       </c>
-      <c r="E48" s="11">
+      <c r="F48" s="11">
         <v>12150</v>
       </c>
-      <c r="F48" s="11">
+      <c r="G48" s="11">
         <v>328750</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="10">
         <v>45424</v>
       </c>
       <c r="C49" s="11">
         <v>178380</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="11"/>
+      <c r="E49" s="11">
         <v>339900</v>
       </c>
-      <c r="E49" s="11">
+      <c r="F49" s="11">
         <v>11150</v>
       </c>
-      <c r="F49" s="11">
+      <c r="G49" s="11">
         <v>328750</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B50" s="10">
         <v>45425</v>
       </c>
       <c r="C50" s="11">
         <v>178380</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="11"/>
+      <c r="E50" s="11">
         <v>342500</v>
       </c>
-      <c r="E50" s="11">
+      <c r="F50" s="11">
         <v>-2050</v>
       </c>
-      <c r="F50" s="11">
+      <c r="G50" s="11">
         <v>344550</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51" s="10">
         <v>45429</v>
       </c>
       <c r="C51" s="11">
         <v>178380</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="11"/>
+      <c r="E51" s="11">
         <v>342500</v>
       </c>
-      <c r="E51" s="11">
+      <c r="F51" s="11">
         <v>4250</v>
       </c>
-      <c r="F51" s="11">
+      <c r="G51" s="11">
         <v>338250</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B52" s="10">
         <v>45429</v>
       </c>
       <c r="C52" s="11">
         <v>178380</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="11"/>
+      <c r="E52" s="11">
         <v>343500</v>
       </c>
-      <c r="E52" s="11">
+      <c r="F52" s="11">
         <v>-750</v>
       </c>
-      <c r="F52" s="11">
+      <c r="G52" s="11">
         <v>344250</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B53" s="10">
         <v>45431</v>
       </c>
       <c r="C53" s="11">
         <v>178380</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="11"/>
+      <c r="E53" s="11">
         <v>343500</v>
       </c>
-      <c r="E53" s="11">
+      <c r="F53" s="11">
         <v>13700</v>
       </c>
-      <c r="F53" s="11">
+      <c r="G53" s="11">
         <v>329800</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B54" s="10">
         <v>45431</v>
       </c>
       <c r="C54" s="11">
         <v>178380</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="11"/>
+      <c r="E54" s="11">
         <v>348500</v>
       </c>
-      <c r="E54" s="11">
+      <c r="F54" s="11">
         <v>15300</v>
       </c>
-      <c r="F54" s="11">
+      <c r="G54" s="11">
         <v>348200</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H54" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="10">
         <v>45436</v>
       </c>
       <c r="C55" s="11">
         <v>178380</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="11"/>
+      <c r="E55" s="11">
         <v>348500</v>
       </c>
-      <c r="E55" s="11">
+      <c r="F55" s="11">
         <v>25050</v>
       </c>
-      <c r="F55" s="11">
+      <c r="G55" s="11">
         <v>338650</v>
       </c>
-      <c r="G55" s="2">
+      <c r="H55" s="2">
         <f>372200-24000</f>
         <v>348200</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B56" s="10">
         <v>45436</v>
       </c>
       <c r="C56" s="11">
         <v>178380</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="11"/>
+      <c r="E56" s="11">
         <v>350800</v>
       </c>
-      <c r="E56" s="11">
+      <c r="F56" s="11">
         <v>15050</v>
       </c>
-      <c r="F56" s="11">
+      <c r="G56" s="11">
         <v>350550</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="10">
         <v>45437</v>
       </c>
       <c r="C57" s="11">
         <v>178380</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="11"/>
+      <c r="E57" s="11">
         <v>350800</v>
       </c>
-      <c r="E57" s="11">
+      <c r="F57" s="11">
         <v>24800</v>
       </c>
-      <c r="F57" s="11">
+      <c r="G57" s="11">
         <v>341050</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="10">
         <v>45437</v>
       </c>
       <c r="C58" s="11">
         <v>178380</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="11"/>
+      <c r="E58" s="11">
         <v>351850</v>
       </c>
-      <c r="E58" s="11">
+      <c r="F58" s="11">
         <v>19800</v>
       </c>
-      <c r="F58" s="11">
+      <c r="G58" s="11">
         <v>347050</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="10">
         <v>45443</v>
       </c>
       <c r="C59" s="11">
         <v>178380</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="11"/>
+      <c r="E59" s="11">
         <v>351850</v>
       </c>
-      <c r="E59" s="11">
+      <c r="F59" s="11">
         <v>28450</v>
       </c>
-      <c r="F59" s="11">
+      <c r="G59" s="11">
         <v>338400</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H59" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60" s="10">
         <v>45443</v>
       </c>
       <c r="C60" s="11">
         <v>178380</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="11"/>
+      <c r="E60" s="11">
         <v>353850</v>
       </c>
-      <c r="E60" s="11">
+      <c r="F60" s="11">
         <v>18450</v>
       </c>
-      <c r="F60" s="11">
+      <c r="G60" s="11">
         <v>350400</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" s="10">
         <v>45444</v>
       </c>
       <c r="C61" s="11">
         <v>178380</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="11"/>
+      <c r="E61" s="11">
         <v>353850</v>
       </c>
-      <c r="E61" s="11">
+      <c r="F61" s="11">
         <v>31200</v>
       </c>
-      <c r="F61" s="11">
+      <c r="G61" s="11">
         <v>337650</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62" s="10">
         <v>45444</v>
       </c>
       <c r="C62" s="11">
         <v>178380</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="11"/>
+      <c r="E62" s="11">
         <v>357850</v>
       </c>
-      <c r="E62" s="11">
+      <c r="F62" s="11">
         <v>11200</v>
       </c>
-      <c r="F62" s="11">
+      <c r="G62" s="11">
         <v>361650</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H62" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63" s="10">
         <v>45448</v>
       </c>
       <c r="C63" s="11">
         <v>178380</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="11"/>
+      <c r="E63" s="11">
         <v>357850</v>
       </c>
-      <c r="E63" s="11">
+      <c r="F63" s="11">
         <v>8600</v>
       </c>
-      <c r="F63" s="11">
+      <c r="G63" s="11">
         <v>359250</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="10">
+        <v>45472</v>
+      </c>
+      <c r="C64" s="11">
+        <v>178380</v>
+      </c>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11">
+        <v>357850</v>
+      </c>
+      <c r="F64" s="11">
+        <v>68200</v>
+      </c>
+      <c r="G64" s="11">
+        <v>289650</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B65" s="10">
+        <v>45473</v>
+      </c>
+      <c r="C65" s="11">
+        <f>C64+10000</f>
+        <v>188380</v>
+      </c>
+      <c r="D65" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E65" s="11">
+        <v>369850</v>
+      </c>
+      <c r="F65" s="11">
+        <v>8200</v>
+      </c>
+      <c r="G65" s="11">
+        <v>301650</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B66" s="10">
+        <v>45484</v>
+      </c>
+      <c r="C66" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D66" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E66" s="11">
+        <v>369850</v>
+      </c>
+      <c r="F66" s="11">
+        <v>37150</v>
+      </c>
+      <c r="G66" s="11">
+        <v>272700</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B67" s="10">
+        <v>45484</v>
+      </c>
+      <c r="C67" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D67" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E67" s="11">
+        <v>373850</v>
+      </c>
+      <c r="F67" s="11">
+        <v>17150</v>
+      </c>
+      <c r="G67" s="11">
+        <v>296700</v>
       </c>
     </row>
   </sheetData>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -252,7 +252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -290,6 +290,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -837,11 +838,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="149872000"/>
-        <c:axId val="149877888"/>
+        <c:axId val="40084224"/>
+        <c:axId val="40085760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="149872000"/>
+        <c:axId val="40084224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -884,14 +885,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="149877888"/>
+        <c:crossAx val="40085760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="149877888"/>
+        <c:axId val="40085760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -942,7 +943,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="149872000"/>
+        <c:crossAx val="40084224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1313,7 +1314,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1321,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I67"/>
+  <dimension ref="B1:I78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -1331,7 +1332,7 @@
     <col min="6" max="6" width="21.85546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="25.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -2607,6 +2608,193 @@
         <v>296700</v>
       </c>
     </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="10">
+        <v>45490</v>
+      </c>
+      <c r="C68" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D68" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E68" s="11">
+        <v>373850</v>
+      </c>
+      <c r="F68" s="11">
+        <v>31950</v>
+      </c>
+      <c r="G68" s="11">
+        <v>281900</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B69" s="10">
+        <v>45490</v>
+      </c>
+      <c r="C69" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D69" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E69" s="11">
+        <v>375850</v>
+      </c>
+      <c r="F69" s="11">
+        <v>21950</v>
+      </c>
+      <c r="G69" s="11">
+        <v>293900</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B70" s="10">
+        <v>45492</v>
+      </c>
+      <c r="C70" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D70" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E70" s="11">
+        <v>375850</v>
+      </c>
+      <c r="F70" s="11">
+        <v>32000</v>
+      </c>
+      <c r="G70" s="11">
+        <v>283850</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B71" s="10">
+        <v>45492</v>
+      </c>
+      <c r="C71" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D71" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E71" s="11">
+        <v>379850</v>
+      </c>
+      <c r="F71" s="11">
+        <v>12000</v>
+      </c>
+      <c r="G71" s="11">
+        <v>307850</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B72" s="10">
+        <v>45495</v>
+      </c>
+      <c r="C72" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D72" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E72" s="11">
+        <v>379850</v>
+      </c>
+      <c r="F72" s="11">
+        <v>24550</v>
+      </c>
+      <c r="G72" s="11">
+        <v>295300</v>
+      </c>
+      <c r="H72" s="15"/>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" s="10">
+        <v>45495</v>
+      </c>
+      <c r="C73" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D73" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E73" s="11">
+        <v>381850</v>
+      </c>
+      <c r="F73" s="11">
+        <v>14550</v>
+      </c>
+      <c r="G73" s="11">
+        <v>307300</v>
+      </c>
+      <c r="H73" s="15"/>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B74" s="10">
+        <v>45500</v>
+      </c>
+      <c r="C74" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D74" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E74" s="11">
+        <v>381850</v>
+      </c>
+      <c r="F74" s="11">
+        <v>34050</v>
+      </c>
+      <c r="G74" s="11">
+        <v>287800</v>
+      </c>
+      <c r="H74" s="15">
+        <v>285400</v>
+      </c>
+      <c r="I74" s="15">
+        <f>G74-H74</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B75" s="10">
+        <v>45500</v>
+      </c>
+      <c r="C75" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D75" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E75" s="11">
+        <v>385850</v>
+      </c>
+      <c r="F75" s="11">
+        <v>14050</v>
+      </c>
+      <c r="G75" s="11">
+        <v>311800</v>
+      </c>
+      <c r="H75" s="2">
+        <f>1400+1000</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="10"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H77" s="15"/>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H78" s="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -68,6 +68,24 @@
   </si>
   <si>
     <t>investment</t>
+  </si>
+  <si>
+    <t>tombi loan 5000</t>
+  </si>
+  <si>
+    <t>marup +oil 5500</t>
+  </si>
+  <si>
+    <t>ricky loan 20000</t>
+  </si>
+  <si>
+    <t>ibeyaima 10000 loan</t>
+  </si>
+  <si>
+    <t>Rambhabati 20000 loan</t>
+  </si>
+  <si>
+    <t>pratima 10000 loan</t>
   </si>
 </sst>
 </file>
@@ -359,7 +377,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -838,11 +855,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="40084224"/>
-        <c:axId val="40085760"/>
+        <c:axId val="197638784"/>
+        <c:axId val="197644672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="40084224"/>
+        <c:axId val="197638784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -885,14 +902,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40085760"/>
+        <c:crossAx val="197644672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="40085760"/>
+        <c:axId val="197644672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -943,7 +960,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40084224"/>
+        <c:crossAx val="197638784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -957,7 +974,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1322,11 +1338,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I78"/>
+  <dimension ref="B1:I103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" style="2" customWidth="1"/>
     <col min="3" max="4" width="15" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" style="3" customWidth="1"/>
@@ -2782,18 +2798,542 @@
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B76" s="10"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
+      <c r="B76" s="10">
+        <v>45506</v>
+      </c>
+      <c r="C76" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D76" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E76" s="11">
+        <v>385850</v>
+      </c>
+      <c r="F76" s="11">
+        <v>42750</v>
+      </c>
+      <c r="G76" s="11">
+        <v>283100</v>
+      </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B77" s="10">
+        <v>45506</v>
+      </c>
+      <c r="C77" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D77" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E77" s="11">
+        <v>392800</v>
+      </c>
+      <c r="F77" s="11">
+        <v>7750</v>
+      </c>
+      <c r="G77" s="11">
+        <v>325050</v>
+      </c>
       <c r="H77" s="15"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H78" s="15"/>
+      <c r="B78" s="10">
+        <v>45513</v>
+      </c>
+      <c r="C78" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D78" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E78" s="11">
+        <v>392800</v>
+      </c>
+      <c r="F78" s="11">
+        <v>25400</v>
+      </c>
+      <c r="G78" s="11">
+        <v>307400</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B79" s="10">
+        <v>45513</v>
+      </c>
+      <c r="C79" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D79" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E79" s="11">
+        <v>394800</v>
+      </c>
+      <c r="F79" s="11">
+        <v>15400</v>
+      </c>
+      <c r="G79" s="11">
+        <v>319400</v>
+      </c>
+      <c r="H79" s="14"/>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B80" s="10">
+        <v>45522</v>
+      </c>
+      <c r="C80" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D80" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E80" s="11">
+        <v>394800</v>
+      </c>
+      <c r="F80" s="11">
+        <v>41800</v>
+      </c>
+      <c r="G80" s="11">
+        <v>293000</v>
+      </c>
+      <c r="H80" s="14"/>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B81" s="10">
+        <v>45522</v>
+      </c>
+      <c r="C81" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D81" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E81" s="11">
+        <v>400800</v>
+      </c>
+      <c r="F81" s="11">
+        <v>11800</v>
+      </c>
+      <c r="G81" s="11">
+        <v>329000</v>
+      </c>
+      <c r="H81" s="14"/>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B82" s="10">
+        <v>45529</v>
+      </c>
+      <c r="C82" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D82" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E82" s="11">
+        <v>400800</v>
+      </c>
+      <c r="F82" s="11">
+        <v>27200</v>
+      </c>
+      <c r="G82" s="11">
+        <v>308600</v>
+      </c>
+      <c r="H82" s="14"/>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" s="10">
+        <v>45529</v>
+      </c>
+      <c r="C83" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D83" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E83" s="11">
+        <v>398800</v>
+      </c>
+      <c r="F83" s="11">
+        <v>12200</v>
+      </c>
+      <c r="G83" s="11">
+        <v>326600</v>
+      </c>
+      <c r="H83" s="14"/>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B84" s="10">
+        <v>45534</v>
+      </c>
+      <c r="C84" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D84" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E84" s="11">
+        <v>398800</v>
+      </c>
+      <c r="F84" s="11">
+        <v>34150</v>
+      </c>
+      <c r="G84" s="11">
+        <v>304650</v>
+      </c>
+      <c r="H84" s="14"/>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B85" s="10">
+        <v>45534</v>
+      </c>
+      <c r="C85" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D85" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E85" s="11">
+        <v>403800</v>
+      </c>
+      <c r="F85" s="11">
+        <v>9150</v>
+      </c>
+      <c r="G85" s="11">
+        <v>334650</v>
+      </c>
+      <c r="H85" s="14"/>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B86" s="10">
+        <v>45542</v>
+      </c>
+      <c r="C86" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D86" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E86" s="11">
+        <v>403800</v>
+      </c>
+      <c r="F86" s="11">
+        <v>33700</v>
+      </c>
+      <c r="G86" s="11">
+        <v>310100</v>
+      </c>
+      <c r="H86" s="14"/>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B87" s="10">
+        <v>45542</v>
+      </c>
+      <c r="C87" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D87" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E87" s="11">
+        <v>404800</v>
+      </c>
+      <c r="F87" s="11">
+        <v>28700</v>
+      </c>
+      <c r="G87" s="11">
+        <v>316100</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B88" s="10">
+        <v>45544</v>
+      </c>
+      <c r="C88" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D88" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E88" s="11">
+        <v>399300</v>
+      </c>
+      <c r="F88" s="11">
+        <v>23200</v>
+      </c>
+      <c r="G88" s="11">
+        <v>316100</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B89" s="10">
+        <v>45549</v>
+      </c>
+      <c r="C89" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D89" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E89" s="11">
+        <v>399300</v>
+      </c>
+      <c r="F89" s="11">
+        <v>41150</v>
+      </c>
+      <c r="G89" s="11">
+        <v>298150</v>
+      </c>
+      <c r="H89" s="14"/>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B90" s="10">
+        <v>45549</v>
+      </c>
+      <c r="C90" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D90" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E90" s="11">
+        <v>403300</v>
+      </c>
+      <c r="F90" s="11">
+        <v>21150</v>
+      </c>
+      <c r="G90" s="11">
+        <v>322150</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B91" s="10">
+        <v>45556</v>
+      </c>
+      <c r="C91" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D91" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E91" s="11">
+        <v>403300</v>
+      </c>
+      <c r="F91" s="11">
+        <v>54700</v>
+      </c>
+      <c r="G91" s="11">
+        <v>288600</v>
+      </c>
+      <c r="H91" s="14"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B92" s="10">
+        <v>45556</v>
+      </c>
+      <c r="C92" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D92" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E92" s="11">
+        <v>407250</v>
+      </c>
+      <c r="F92" s="11">
+        <v>34700</v>
+      </c>
+      <c r="G92" s="11">
+        <v>312550</v>
+      </c>
+      <c r="H92" s="14"/>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B93" s="10">
+        <v>45560</v>
+      </c>
+      <c r="C93" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D93" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E93" s="11">
+        <v>407250</v>
+      </c>
+      <c r="F93" s="11">
+        <v>45750</v>
+      </c>
+      <c r="G93" s="11">
+        <v>301500</v>
+      </c>
+      <c r="H93" s="14"/>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B94" s="10">
+        <v>45560</v>
+      </c>
+      <c r="C94" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D94" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E94" s="11">
+        <v>409250</v>
+      </c>
+      <c r="F94" s="11">
+        <v>35750</v>
+      </c>
+      <c r="G94" s="11">
+        <v>313500</v>
+      </c>
+      <c r="H94" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B95" s="10">
+        <v>45561</v>
+      </c>
+      <c r="C95" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D95" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E95" s="11">
+        <v>409250</v>
+      </c>
+      <c r="F95" s="11">
+        <v>51900</v>
+      </c>
+      <c r="G95" s="11">
+        <v>297350</v>
+      </c>
+      <c r="H95" s="14"/>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B96" s="10">
+        <v>45561</v>
+      </c>
+      <c r="C96" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D96" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E96" s="11">
+        <v>413250</v>
+      </c>
+      <c r="F96" s="11">
+        <v>31900</v>
+      </c>
+      <c r="G96" s="11">
+        <v>321350</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B97" s="10">
+        <v>45561</v>
+      </c>
+      <c r="C97" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D97" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E97" s="11">
+        <v>413250</v>
+      </c>
+      <c r="F97" s="11">
+        <v>33400</v>
+      </c>
+      <c r="G97" s="11">
+        <v>319850</v>
+      </c>
+      <c r="H97" s="14"/>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B98" s="10">
+        <v>45561</v>
+      </c>
+      <c r="C98" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D98" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E98" s="11">
+        <v>415250</v>
+      </c>
+      <c r="F98" s="11">
+        <v>23400</v>
+      </c>
+      <c r="G98" s="11">
+        <v>331850</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B99" s="10"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="11"/>
+      <c r="H99" s="14"/>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B100" s="10"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="14"/>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B101" s="10"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="14"/>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B102" s="10"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="14"/>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B103" s="10"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>pratima 10000 loan</t>
+  </si>
+  <si>
+    <t>renit loan 15000</t>
+  </si>
+  <si>
+    <t>anita loan 50000</t>
   </si>
 </sst>
 </file>
@@ -855,11 +861,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="197638784"/>
-        <c:axId val="197644672"/>
+        <c:axId val="51851648"/>
+        <c:axId val="51853184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="197638784"/>
+        <c:axId val="51851648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -902,14 +908,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197644672"/>
+        <c:crossAx val="51853184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="197644672"/>
+        <c:axId val="51853184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -960,7 +966,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197638784"/>
+        <c:crossAx val="51851648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1338,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I103"/>
+  <dimension ref="B1:I108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -3291,49 +3297,131 @@
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B99" s="10"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11"/>
+      <c r="B99" s="10">
+        <v>45569</v>
+      </c>
+      <c r="C99" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D99" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E99" s="11">
+        <v>415250</v>
+      </c>
+      <c r="F99" s="11">
+        <v>41000</v>
+      </c>
+      <c r="G99" s="11">
+        <v>314250</v>
+      </c>
       <c r="H99" s="14"/>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B100" s="10"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
-      <c r="H100" s="14"/>
+      <c r="B100" s="10">
+        <v>45569</v>
+      </c>
+      <c r="C100" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D100" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E100" s="11">
+        <v>418250</v>
+      </c>
+      <c r="F100" s="11">
+        <v>26000</v>
+      </c>
+      <c r="G100" s="11">
+        <v>332250</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B101" s="10"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
+      <c r="B101" s="10">
+        <v>45577</v>
+      </c>
+      <c r="C101" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D101" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E101" s="11">
+        <v>418250</v>
+      </c>
+      <c r="F101" s="11">
+        <v>56850</v>
+      </c>
+      <c r="G101" s="11">
+        <v>301400</v>
+      </c>
       <c r="H101" s="14"/>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B102" s="10"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11"/>
-      <c r="H102" s="14"/>
+      <c r="B102" s="10">
+        <v>45577</v>
+      </c>
+      <c r="C102" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D102" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E102" s="11">
+        <v>428250</v>
+      </c>
+      <c r="F102" s="11">
+        <v>6850</v>
+      </c>
+      <c r="G102" s="11">
+        <v>361400</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B103" s="10"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="11"/>
+      <c r="B103" s="10">
+        <v>45577</v>
+      </c>
+      <c r="C103" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D103" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E103" s="11">
+        <v>428250</v>
+      </c>
+      <c r="F103" s="11">
+        <v>16450</v>
+      </c>
+      <c r="G103" s="11">
+        <v>351800</v>
+      </c>
       <c r="H103" s="14"/>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H104" s="14"/>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H105" s="14"/>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G107" s="3">
+        <f>G102-G103</f>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G108" s="3">
+        <f>F102+G107</f>
+        <v>16450</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>anita loan 50000</t>
+  </si>
+  <si>
+    <t>marup 198000</t>
   </si>
 </sst>
 </file>
@@ -861,11 +864,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="51851648"/>
-        <c:axId val="51853184"/>
+        <c:axId val="175913216"/>
+        <c:axId val="176164864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="51851648"/>
+        <c:axId val="175913216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -908,14 +911,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51853184"/>
+        <c:crossAx val="176164864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="51853184"/>
+        <c:axId val="176164864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -966,7 +969,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51851648"/>
+        <c:crossAx val="175913216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1336,7 +1339,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1344,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I108"/>
+  <dimension ref="B1:I110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -3406,22 +3409,108 @@
       <c r="H103" s="14"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B104" s="10">
+        <v>45583</v>
+      </c>
+      <c r="C104" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D104" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E104" s="11">
+        <v>428250</v>
+      </c>
+      <c r="F104" s="11">
+        <v>72100</v>
+      </c>
+      <c r="G104" s="11">
+        <v>296150</v>
+      </c>
       <c r="H104" s="14"/>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H105" s="14"/>
+      <c r="B105" s="10">
+        <v>45583</v>
+      </c>
+      <c r="C105" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D105" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E105" s="11">
+        <v>428250</v>
+      </c>
+      <c r="F105" s="11">
+        <v>270100</v>
+      </c>
+      <c r="G105" s="11">
+        <v>296150</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B106" s="10">
+        <v>45583</v>
+      </c>
+      <c r="C106" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D106" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E106" s="11">
+        <v>716250</v>
+      </c>
+      <c r="F106" s="11">
+        <v>20100</v>
+      </c>
+      <c r="G106" s="11">
+        <v>636150</v>
+      </c>
+      <c r="H106" s="14"/>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G107" s="3">
-        <f>G102-G103</f>
-        <v>9600</v>
-      </c>
+      <c r="B107" s="10"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="14"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G108" s="3">
-        <f>F102+G107</f>
-        <v>16450</v>
-      </c>
+      <c r="B108" s="10"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="14"/>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B109" s="10"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="14">
+        <f>E106-E105</f>
+        <v>288000</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B110" s="10"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="11"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>marup 198000</t>
+  </si>
+  <si>
+    <t>loan 10000 sunamani</t>
+  </si>
+  <si>
+    <t>bijent loan 20000</t>
+  </si>
+  <si>
+    <t>loan bidyapati+ thasana 40000</t>
+  </si>
+  <si>
+    <t>joyshree loan 30000</t>
   </si>
 </sst>
 </file>
@@ -864,11 +876,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="175913216"/>
-        <c:axId val="176164864"/>
+        <c:axId val="170452096"/>
+        <c:axId val="170453632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="175913216"/>
+        <c:axId val="170452096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -911,14 +923,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="176164864"/>
+        <c:crossAx val="170453632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="176164864"/>
+        <c:axId val="170453632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -969,7 +981,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="175913216"/>
+        <c:crossAx val="170452096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1339,7 +1351,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1347,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I110"/>
+  <dimension ref="B1:I118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -3474,43 +3486,234 @@
       <c r="H106" s="14"/>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B107" s="10"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="11"/>
+      <c r="B107" s="10">
+        <v>45586</v>
+      </c>
+      <c r="C107" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D107" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E107" s="11">
+        <v>716250</v>
+      </c>
+      <c r="F107" s="11">
+        <v>31200</v>
+      </c>
+      <c r="G107" s="11">
+        <v>625050</v>
+      </c>
       <c r="H107" s="14"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B108" s="10"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="14"/>
+      <c r="B108" s="10">
+        <v>45586</v>
+      </c>
+      <c r="C108" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D108" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E108" s="11">
+        <v>718250</v>
+      </c>
+      <c r="F108" s="11">
+        <v>21200</v>
+      </c>
+      <c r="G108" s="11">
+        <v>637050</v>
+      </c>
+      <c r="H108" s="14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B109" s="10"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="14">
-        <f>E106-E105</f>
-        <v>288000</v>
-      </c>
+      <c r="B109" s="10">
+        <v>45590</v>
+      </c>
+      <c r="C109" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D109" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E109" s="11">
+        <v>718250</v>
+      </c>
+      <c r="F109" s="11">
+        <v>40550</v>
+      </c>
+      <c r="G109" s="11">
+        <v>617700</v>
+      </c>
+      <c r="H109" s="14"/>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B110" s="10"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
-      <c r="G110" s="11"/>
-      <c r="H110" s="14"/>
+      <c r="B110" s="10">
+        <v>45590</v>
+      </c>
+      <c r="C110" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D110" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E110" s="11">
+        <v>722250</v>
+      </c>
+      <c r="F110" s="11">
+        <v>20550</v>
+      </c>
+      <c r="G110" s="11">
+        <v>641700</v>
+      </c>
+      <c r="H110" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B111" s="10">
+        <v>45595</v>
+      </c>
+      <c r="C111" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D111" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E111" s="11">
+        <v>722250</v>
+      </c>
+      <c r="F111" s="11">
+        <v>62650</v>
+      </c>
+      <c r="G111" s="11">
+        <v>599600</v>
+      </c>
+      <c r="H111" s="14"/>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B112" s="10">
+        <v>45595</v>
+      </c>
+      <c r="C112" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D112" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E112" s="11">
+        <v>730250</v>
+      </c>
+      <c r="F112" s="11">
+        <v>22650</v>
+      </c>
+      <c r="G112" s="11">
+        <v>647600</v>
+      </c>
+      <c r="H112" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B113" s="10">
+        <v>45601</v>
+      </c>
+      <c r="C113" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D113" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E113" s="11">
+        <v>730250</v>
+      </c>
+      <c r="F113" s="11">
+        <v>51000</v>
+      </c>
+      <c r="G113" s="11">
+        <v>619250</v>
+      </c>
+      <c r="H113" s="14"/>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B114" s="10">
+        <v>45601</v>
+      </c>
+      <c r="C114" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D114" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E114" s="11">
+        <v>736250</v>
+      </c>
+      <c r="F114" s="11">
+        <v>21000</v>
+      </c>
+      <c r="G114" s="11">
+        <v>655250</v>
+      </c>
+      <c r="H114" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B115" s="10">
+        <v>45602</v>
+      </c>
+      <c r="C115" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D115" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E115" s="11">
+        <v>736250</v>
+      </c>
+      <c r="F115" s="11">
+        <v>30550</v>
+      </c>
+      <c r="G115" s="11">
+        <v>645700</v>
+      </c>
+      <c r="H115" s="14"/>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B116" s="10"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="14">
+        <f>G114-G115</f>
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B117" s="10"/>
+      <c r="C117" s="11"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
+      <c r="F117" s="11"/>
+      <c r="G117" s="11"/>
+      <c r="H117" s="14">
+        <f>F114+H116</f>
+        <v>30550</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B118" s="10"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
+      <c r="F118" s="11"/>
+      <c r="G118" s="11"/>
+      <c r="H118" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -107,6 +107,15 @@
   </si>
   <si>
     <t>joyshree loan 30000</t>
+  </si>
+  <si>
+    <t>loan Asiqi 50000+ kiranmala 10000</t>
+  </si>
+  <si>
+    <t>marup 6500</t>
+  </si>
+  <si>
+    <t>loan sunanda 100000 ; paid 7000; due 30000</t>
   </si>
 </sst>
 </file>
@@ -876,11 +885,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="170452096"/>
-        <c:axId val="170453632"/>
+        <c:axId val="49765760"/>
+        <c:axId val="148506112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="170452096"/>
+        <c:axId val="49765760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -923,14 +932,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="170453632"/>
+        <c:crossAx val="148506112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="170453632"/>
+        <c:axId val="148506112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -981,7 +990,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="170452096"/>
+        <c:crossAx val="49765760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1359,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I118"/>
+  <dimension ref="B1:I126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -3683,37 +3692,183 @@
       <c r="H115" s="14"/>
     </row>
     <row r="116" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B116" s="10"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="11"/>
-      <c r="H116" s="14">
-        <f>G114-G115</f>
-        <v>9550</v>
-      </c>
+      <c r="B116" s="10">
+        <v>45611</v>
+      </c>
+      <c r="C116" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D116" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E116" s="11">
+        <v>736250</v>
+      </c>
+      <c r="F116" s="11">
+        <v>92100</v>
+      </c>
+      <c r="G116" s="11">
+        <v>584150</v>
+      </c>
+      <c r="H116" s="14"/>
     </row>
     <row r="117" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B117" s="10"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="11"/>
-      <c r="H117" s="14">
-        <f>F114+H116</f>
-        <v>30550</v>
+      <c r="B117" s="10">
+        <v>45611</v>
+      </c>
+      <c r="C117" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D117" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E117" s="11">
+        <v>748250</v>
+      </c>
+      <c r="F117" s="11">
+        <v>32100</v>
+      </c>
+      <c r="G117" s="11">
+        <v>656150</v>
+      </c>
+      <c r="H117" s="14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="118" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B118" s="10"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="11"/>
-      <c r="H118" s="14"/>
+      <c r="B118" s="10">
+        <v>45611</v>
+      </c>
+      <c r="C118" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D118" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E118" s="11">
+        <v>741750</v>
+      </c>
+      <c r="F118" s="11">
+        <v>25600</v>
+      </c>
+      <c r="G118" s="11">
+        <v>656150</v>
+      </c>
+      <c r="H118" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B119" s="10">
+        <v>45611</v>
+      </c>
+      <c r="C119" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D119" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E119" s="11">
+        <v>741750</v>
+      </c>
+      <c r="F119" s="11">
+        <v>43400</v>
+      </c>
+      <c r="G119" s="11">
+        <v>638350</v>
+      </c>
+      <c r="H119" s="14"/>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B120" s="10">
+        <v>45618</v>
+      </c>
+      <c r="C120" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D120" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E120" s="11">
+        <f>831950-30000</f>
+        <v>801950</v>
+      </c>
+      <c r="F120" s="11">
+        <v>36400</v>
+      </c>
+      <c r="G120" s="11">
+        <v>735550</v>
+      </c>
+      <c r="H120" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B121" s="10">
+        <v>45621</v>
+      </c>
+      <c r="C121" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D121" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E121" s="11">
+        <f>831950-30000</f>
+        <v>801950</v>
+      </c>
+      <c r="F121" s="11">
+        <v>50300</v>
+      </c>
+      <c r="G121" s="11">
+        <v>721650</v>
+      </c>
+      <c r="H121" s="14"/>
+    </row>
+    <row r="122" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B122" s="10"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
+      <c r="F122" s="11"/>
+      <c r="G122" s="11"/>
+      <c r="H122" s="14"/>
+    </row>
+    <row r="123" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B123" s="10"/>
+      <c r="C123" s="11"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
+      <c r="F123" s="11"/>
+      <c r="G123" s="11"/>
+      <c r="H123" s="14"/>
+    </row>
+    <row r="124" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B124" s="10"/>
+      <c r="C124" s="11"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="14"/>
+    </row>
+    <row r="125" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B125" s="10"/>
+      <c r="C125" s="11"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="11"/>
+      <c r="G125" s="11"/>
+      <c r="H125" s="14"/>
+    </row>
+    <row r="126" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B126" s="10"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="11"/>
+      <c r="G126" s="11"/>
+      <c r="H126" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -116,6 +116,12 @@
   </si>
   <si>
     <t>loan sunanda 100000 ; paid 7000; due 30000</t>
+  </si>
+  <si>
+    <t>clear sunanda 5000 remaining 25000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loan kamala 50000 </t>
   </si>
 </sst>
 </file>
@@ -407,6 +413,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -885,11 +892,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="49765760"/>
-        <c:axId val="148506112"/>
+        <c:axId val="196524672"/>
+        <c:axId val="196526464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="49765760"/>
+        <c:axId val="196524672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -932,14 +939,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="148506112"/>
+        <c:crossAx val="196526464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="148506112"/>
+        <c:axId val="196526464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -990,7 +997,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49765760"/>
+        <c:crossAx val="196524672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1004,6 +1011,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1360,7 +1368,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1368,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I126"/>
+  <dimension ref="B1:I128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -3826,39 +3834,95 @@
       <c r="H121" s="14"/>
     </row>
     <row r="122" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B122" s="10"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="11"/>
-      <c r="E122" s="11"/>
-      <c r="F122" s="11"/>
-      <c r="G122" s="11"/>
+      <c r="B122" s="10">
+        <v>45626</v>
+      </c>
+      <c r="C122" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D122" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E122" s="11">
+        <f>831950-30000</f>
+        <v>801950</v>
+      </c>
+      <c r="F122" s="11">
+        <v>76050</v>
+      </c>
+      <c r="G122" s="11">
+        <v>695900</v>
+      </c>
       <c r="H122" s="14"/>
     </row>
     <row r="123" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B123" s="10"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="11"/>
-      <c r="F123" s="11"/>
-      <c r="G123" s="11"/>
-      <c r="H123" s="14"/>
+      <c r="B123" s="10">
+        <v>45626</v>
+      </c>
+      <c r="C123" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D123" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E123" s="11">
+        <f>831950-30000</f>
+        <v>801950</v>
+      </c>
+      <c r="F123" s="11">
+        <v>71050</v>
+      </c>
+      <c r="G123" s="11">
+        <v>695900</v>
+      </c>
+      <c r="H123" s="14" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="124" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B124" s="10"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="11"/>
-      <c r="G124" s="11"/>
-      <c r="H124" s="14"/>
+      <c r="B124" s="10">
+        <v>45626</v>
+      </c>
+      <c r="C124" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D124" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E124" s="11">
+        <f>836950-25000</f>
+        <v>811950</v>
+      </c>
+      <c r="F124" s="11">
+        <v>21050</v>
+      </c>
+      <c r="G124" s="11">
+        <v>755900</v>
+      </c>
+      <c r="H124" s="14" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="125" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B125" s="10"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="11"/>
-      <c r="F125" s="11"/>
-      <c r="G125" s="11"/>
+      <c r="B125" s="10">
+        <v>45628</v>
+      </c>
+      <c r="C125" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D125" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E125" s="11">
+        <f>836950-25000</f>
+        <v>811950</v>
+      </c>
+      <c r="F125" s="11">
+        <v>29950</v>
+      </c>
+      <c r="G125" s="11">
+        <v>747000</v>
+      </c>
       <c r="H125" s="14"/>
     </row>
     <row r="126" spans="2:8" x14ac:dyDescent="0.25">
@@ -3870,6 +3934,12 @@
       <c r="G126" s="11"/>
       <c r="H126" s="14"/>
     </row>
+    <row r="127" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H127" s="14"/>
+    </row>
+    <row r="128" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H128" s="14"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t xml:space="preserve">loan kamala 50000 </t>
+  </si>
+  <si>
+    <t>clear sunanda 5000 remaining 20000</t>
+  </si>
+  <si>
+    <t>loan ibobi 30000+ dinita 10000+ sandhyarani 10000</t>
   </si>
 </sst>
 </file>
@@ -413,7 +419,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -892,11 +897,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="196524672"/>
-        <c:axId val="196526464"/>
+        <c:axId val="48256896"/>
+        <c:axId val="48258432"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="196524672"/>
+        <c:axId val="48256896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -939,14 +944,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="196526464"/>
+        <c:crossAx val="48258432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="196526464"/>
+        <c:axId val="48258432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -997,7 +1002,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="196524672"/>
+        <c:crossAx val="48256896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1011,7 +1016,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1376,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I128"/>
+  <dimension ref="B1:I152"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -3879,7 +3883,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="10">
         <v>45626</v>
       </c>
@@ -3903,7 +3907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="10">
         <v>45628</v>
       </c>
@@ -3925,20 +3929,268 @@
       </c>
       <c r="H125" s="14"/>
     </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B126" s="10"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="11"/>
-      <c r="G126" s="11"/>
+    <row r="126" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="10">
+        <v>45632</v>
+      </c>
+      <c r="C126" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D126" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E126" s="11">
+        <f>836950-25000</f>
+        <v>811950</v>
+      </c>
+      <c r="F126" s="11">
+        <v>83550</v>
+      </c>
+      <c r="G126" s="11">
+        <v>693400</v>
+      </c>
       <c r="H126" s="14"/>
     </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H127" s="14"/>
-    </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H128" s="14"/>
+    <row r="127" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="10">
+        <v>45632</v>
+      </c>
+      <c r="C127" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D127" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E127" s="11">
+        <v>811950</v>
+      </c>
+      <c r="F127" s="11">
+        <f>F126-5000</f>
+        <v>78550</v>
+      </c>
+      <c r="G127" s="11">
+        <v>693400</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B128" s="10">
+        <v>45632</v>
+      </c>
+      <c r="C128" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D128" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E128" s="11">
+        <f>841950-20000</f>
+        <v>821950</v>
+      </c>
+      <c r="F128" s="11">
+        <v>28550</v>
+      </c>
+      <c r="G128" s="11">
+        <v>753400</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="10"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+    </row>
+    <row r="130" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="10"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
+      <c r="F130" s="11"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="14"/>
+    </row>
+    <row r="131" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="10"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
+      <c r="F131" s="11"/>
+      <c r="G131" s="11"/>
+    </row>
+    <row r="132" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="10"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="11"/>
+    </row>
+    <row r="133" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="10"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
+    </row>
+    <row r="134" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="10"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
+      <c r="F134" s="11"/>
+      <c r="G134" s="11"/>
+    </row>
+    <row r="135" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="10"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
+      <c r="F135" s="11"/>
+      <c r="G135" s="11"/>
+    </row>
+    <row r="136" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="10"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="11"/>
+    </row>
+    <row r="137" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="10"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="11"/>
+    </row>
+    <row r="138" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="10"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="11"/>
+    </row>
+    <row r="139" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="10"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
+    </row>
+    <row r="140" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="10"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="11"/>
+    </row>
+    <row r="141" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="10"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
+      <c r="F141" s="11"/>
+      <c r="G141" s="11"/>
+    </row>
+    <row r="142" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="10"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
+    </row>
+    <row r="143" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="10"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="11"/>
+    </row>
+    <row r="144" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="10"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+    </row>
+    <row r="145" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="10"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="11"/>
+      <c r="G145" s="11"/>
+    </row>
+    <row r="146" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="10"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+    </row>
+    <row r="147" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="10"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+    </row>
+    <row r="148" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="10"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+    </row>
+    <row r="149" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="10"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
+      <c r="F149" s="11"/>
+      <c r="G149" s="11"/>
+    </row>
+    <row r="150" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="10"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="11"/>
+      <c r="G150" s="11"/>
+    </row>
+    <row r="151" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="10"/>
+      <c r="C151" s="11"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11"/>
+      <c r="F151" s="11"/>
+      <c r="G151" s="11"/>
+    </row>
+    <row r="152" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="10"/>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
+      <c r="F152" s="11"/>
+      <c r="G152" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -128,6 +128,33 @@
   </si>
   <si>
     <t>loan ibobi 30000+ dinita 10000+ sandhyarani 10000</t>
+  </si>
+  <si>
+    <t>clear sunanda 3000 ,remaining 17000</t>
+  </si>
+  <si>
+    <t>adjusted 174700; remaining to be pay 11900; adjusted 13400</t>
+  </si>
+  <si>
+    <t>bomcha marup 6500</t>
+  </si>
+  <si>
+    <t>rambhabati loan 200000; remaning 25300</t>
+  </si>
+  <si>
+    <t>rambhabati pay4000 remaining 21300</t>
+  </si>
+  <si>
+    <t>adjusted 13400; remaining 7900</t>
+  </si>
+  <si>
+    <t>loan lukham 10000</t>
+  </si>
+  <si>
+    <t>deposit robita 10000</t>
+  </si>
+  <si>
+    <t>deposit</t>
   </si>
 </sst>
 </file>
@@ -419,6 +446,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -553,7 +581,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'2023TrendAnalysis'!$E$2</c:f>
+              <c:f>'2023TrendAnalysis'!$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -615,7 +643,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2023TrendAnalysis'!$E$3:$E$13</c:f>
+              <c:f>'2023TrendAnalysis'!$F$3:$F$13</c:f>
               <c:numCache>
                 <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="11"/>
@@ -667,7 +695,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'2023TrendAnalysis'!$F$2</c:f>
+              <c:f>'2023TrendAnalysis'!$G$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -729,7 +757,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2023TrendAnalysis'!$F$3:$F$13</c:f>
+              <c:f>'2023TrendAnalysis'!$G$3:$G$13</c:f>
               <c:numCache>
                 <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="11"/>
@@ -778,7 +806,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'2023TrendAnalysis'!$G$2</c:f>
+              <c:f>'2023TrendAnalysis'!$H$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -840,7 +868,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2023TrendAnalysis'!$G$3:$G$13</c:f>
+              <c:f>'2023TrendAnalysis'!$H$3:$H$13</c:f>
               <c:numCache>
                 <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="11"/>
@@ -897,11 +925,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="48256896"/>
-        <c:axId val="48258432"/>
+        <c:axId val="196722688"/>
+        <c:axId val="196724224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="48256896"/>
+        <c:axId val="196722688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -944,14 +972,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48258432"/>
+        <c:crossAx val="196724224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="48258432"/>
+        <c:axId val="196724224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1002,7 +1030,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48256896"/>
+        <c:crossAx val="196722688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1016,6 +1044,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1086,13 +1115,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
@@ -1372,7 +1401,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1380,22 +1409,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I152"/>
+  <dimension ref="B1:J184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="15" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="5" width="15" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:9" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:10" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
         <v>16</v>
@@ -1404,16 +1433,19 @@
         <v>17</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1421,20 +1453,21 @@
         <v>35000</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="F3" s="6" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G3" s="7" t="e">
+      <c r="G3" s="6" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="7" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8">
         <v>45221</v>
       </c>
@@ -1442,17 +1475,18 @@
         <v>35000</v>
       </c>
       <c r="D4" s="9"/>
-      <c r="E4" s="9">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9">
         <v>41200</v>
       </c>
-      <c r="F4" s="9">
+      <c r="G4" s="9">
         <v>800</v>
       </c>
-      <c r="G4" s="9">
+      <c r="H4" s="9">
         <v>40400</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
         <v>45227</v>
       </c>
@@ -1460,17 +1494,18 @@
         <v>35000</v>
       </c>
       <c r="D5" s="11"/>
-      <c r="E5" s="11">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11">
         <v>41200</v>
       </c>
-      <c r="F5" s="11">
+      <c r="G5" s="11">
         <v>4100</v>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="11">
         <v>37100</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12">
         <v>45235</v>
       </c>
@@ -1478,17 +1513,18 @@
         <v>35000</v>
       </c>
       <c r="D6" s="13"/>
-      <c r="E6" s="13">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13">
         <v>41200</v>
       </c>
-      <c r="F6" s="13">
+      <c r="G6" s="13">
         <v>4100</v>
       </c>
-      <c r="G6" s="13">
+      <c r="H6" s="13">
         <v>37100</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>45242</v>
       </c>
@@ -1496,18 +1532,19 @@
         <v>34880</v>
       </c>
       <c r="D7" s="11"/>
-      <c r="E7" s="11">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11">
         <v>46100</v>
       </c>
-      <c r="F7" s="11">
+      <c r="G7" s="11">
         <v>0</v>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="11">
         <v>46100</v>
       </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12">
         <v>45249</v>
       </c>
@@ -1515,15 +1552,16 @@
         <v>34880</v>
       </c>
       <c r="D8" s="13"/>
-      <c r="E8" s="13">
+      <c r="E8" s="13"/>
+      <c r="F8" s="13">
         <v>46100</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13">
         <v>46100</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
         <v>45256</v>
       </c>
@@ -1531,17 +1569,18 @@
         <v>44880</v>
       </c>
       <c r="D9" s="11"/>
-      <c r="E9" s="11">
+      <c r="E9" s="11"/>
+      <c r="F9" s="11">
         <v>59050</v>
       </c>
-      <c r="F9" s="11">
+      <c r="G9" s="11">
         <v>1850</v>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="11">
         <v>57200</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>45270</v>
       </c>
@@ -1549,18 +1588,19 @@
         <v>44880</v>
       </c>
       <c r="D10" s="11"/>
-      <c r="E10" s="11">
-        <f>F10+G10</f>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11">
+        <f>G10+H10</f>
         <v>58500</v>
       </c>
-      <c r="F10" s="11">
+      <c r="G10" s="11">
         <v>9100</v>
       </c>
-      <c r="G10" s="11">
+      <c r="H10" s="11">
         <v>49400</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="12">
         <v>45277</v>
       </c>
@@ -1568,17 +1608,18 @@
         <v>134880</v>
       </c>
       <c r="D11" s="13"/>
-      <c r="E11" s="13">
+      <c r="E11" s="13"/>
+      <c r="F11" s="13">
         <v>190050</v>
       </c>
-      <c r="F11" s="13">
+      <c r="G11" s="13">
         <v>13000</v>
       </c>
-      <c r="G11" s="13">
+      <c r="H11" s="13">
         <v>177050</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
         <v>45284</v>
       </c>
@@ -1586,17 +1627,18 @@
         <v>159880</v>
       </c>
       <c r="D12" s="11"/>
-      <c r="E12" s="11">
+      <c r="E12" s="11"/>
+      <c r="F12" s="11">
         <v>222250</v>
       </c>
-      <c r="F12" s="11">
+      <c r="G12" s="11">
         <v>5500</v>
       </c>
-      <c r="G12" s="11">
+      <c r="H12" s="11">
         <v>216750</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>45291</v>
       </c>
@@ -1604,17 +1646,18 @@
         <v>159880</v>
       </c>
       <c r="D13" s="11"/>
-      <c r="E13" s="13">
+      <c r="E13" s="11"/>
+      <c r="F13" s="13">
         <v>222250</v>
       </c>
-      <c r="F13" s="13">
+      <c r="G13" s="13">
         <v>16800</v>
       </c>
-      <c r="G13" s="13">
+      <c r="H13" s="13">
         <v>205750</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>45298</v>
       </c>
@@ -1622,18 +1665,19 @@
         <v>159880</v>
       </c>
       <c r="D14" s="11"/>
-      <c r="E14" s="11">
+      <c r="E14" s="11"/>
+      <c r="F14" s="11">
         <v>230000</v>
       </c>
-      <c r="F14" s="11">
+      <c r="G14" s="11">
         <f>5000+8100+2850+2700</f>
         <v>18650</v>
       </c>
-      <c r="G14" s="11">
+      <c r="H14" s="11">
         <v>211350</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>45301</v>
       </c>
@@ -1641,17 +1685,18 @@
         <v>159880</v>
       </c>
       <c r="D15" s="11"/>
-      <c r="E15" s="13">
+      <c r="E15" s="11"/>
+      <c r="F15" s="13">
         <v>250800</v>
       </c>
-      <c r="F15" s="13">
+      <c r="G15" s="13">
         <v>-150</v>
       </c>
-      <c r="G15" s="13">
+      <c r="H15" s="13">
         <v>250950</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10">
         <v>45305</v>
       </c>
@@ -1659,18 +1704,19 @@
         <v>159880</v>
       </c>
       <c r="D16" s="11"/>
-      <c r="E16" s="11">
+      <c r="E16" s="11"/>
+      <c r="F16" s="11">
         <v>242050</v>
       </c>
-      <c r="F16" s="11">
+      <c r="G16" s="11">
         <v>5950</v>
       </c>
-      <c r="G16" s="11">
+      <c r="H16" s="11">
         <v>236100</v>
       </c>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10">
         <v>45308</v>
       </c>
@@ -1678,18 +1724,19 @@
         <v>159880</v>
       </c>
       <c r="D17" s="11"/>
-      <c r="E17" s="11">
+      <c r="E17" s="11"/>
+      <c r="F17" s="11">
         <v>242050</v>
       </c>
-      <c r="F17" s="11">
+      <c r="G17" s="11">
         <v>12550</v>
       </c>
-      <c r="G17" s="11">
+      <c r="H17" s="11">
         <v>229250</v>
       </c>
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>45316</v>
       </c>
@@ -1697,18 +1744,19 @@
         <v>159880</v>
       </c>
       <c r="D18" s="11"/>
-      <c r="E18" s="11">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11">
         <v>242050</v>
       </c>
-      <c r="F18" s="11">
+      <c r="G18" s="11">
         <v>17550</v>
       </c>
-      <c r="G18" s="11">
+      <c r="H18" s="11">
         <v>224900</v>
       </c>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="10">
         <v>45316</v>
       </c>
@@ -1716,18 +1764,19 @@
         <v>159880</v>
       </c>
       <c r="D19" s="11"/>
-      <c r="E19" s="11">
+      <c r="E19" s="11"/>
+      <c r="F19" s="11">
         <v>249250</v>
       </c>
-      <c r="F19" s="11">
+      <c r="G19" s="11">
         <v>7550</v>
       </c>
-      <c r="G19" s="11">
+      <c r="H19" s="11">
         <v>241700</v>
       </c>
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="10">
         <v>45320</v>
       </c>
@@ -1735,21 +1784,22 @@
         <v>159880</v>
       </c>
       <c r="D20" s="11"/>
-      <c r="E20" s="11">
+      <c r="E20" s="11"/>
+      <c r="F20" s="11">
         <v>249250</v>
       </c>
-      <c r="F20" s="11">
+      <c r="G20" s="11">
         <v>16800</v>
       </c>
-      <c r="G20" s="11">
+      <c r="H20" s="11">
         <v>232450</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="I20" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="10">
         <v>45321</v>
       </c>
@@ -1757,17 +1807,18 @@
         <v>159880</v>
       </c>
       <c r="D21" s="11"/>
-      <c r="E21" s="11">
+      <c r="E21" s="11"/>
+      <c r="F21" s="11">
         <v>255900</v>
       </c>
-      <c r="F21" s="11">
+      <c r="G21" s="11">
         <v>6650</v>
       </c>
-      <c r="G21" s="11">
+      <c r="H21" s="11">
         <v>249250</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="10">
         <v>45325</v>
       </c>
@@ -1776,17 +1827,18 @@
         <v>161380</v>
       </c>
       <c r="D22" s="11"/>
-      <c r="E22" s="11">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11">
         <v>257400</v>
       </c>
-      <c r="F22" s="11">
+      <c r="G22" s="11">
         <v>18650</v>
       </c>
-      <c r="G22" s="11">
+      <c r="H22" s="11">
         <v>240150</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="10">
         <v>45325</v>
       </c>
@@ -1794,17 +1846,18 @@
         <v>161380</v>
       </c>
       <c r="D23" s="11"/>
-      <c r="E23" s="11">
+      <c r="E23" s="11"/>
+      <c r="F23" s="11">
         <v>252850</v>
       </c>
-      <c r="F23" s="11">
+      <c r="G23" s="11">
         <v>1000</v>
       </c>
-      <c r="G23" s="11">
+      <c r="H23" s="11">
         <v>251850</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="10">
         <v>45331</v>
       </c>
@@ -1812,17 +1865,18 @@
         <v>161380</v>
       </c>
       <c r="D24" s="11"/>
-      <c r="E24" s="11">
+      <c r="E24" s="11"/>
+      <c r="F24" s="11">
         <v>251450</v>
       </c>
-      <c r="F24" s="11">
+      <c r="G24" s="11">
         <v>11700</v>
       </c>
-      <c r="G24" s="11">
+      <c r="H24" s="11">
         <v>239750</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
         <v>45331</v>
       </c>
@@ -1830,17 +1884,18 @@
         <v>161380</v>
       </c>
       <c r="D25" s="11"/>
-      <c r="E25" s="11">
+      <c r="E25" s="11"/>
+      <c r="F25" s="11">
         <v>253500</v>
       </c>
-      <c r="F25" s="11">
+      <c r="G25" s="11">
         <v>-8150</v>
       </c>
-      <c r="G25" s="11">
+      <c r="H25" s="11">
         <v>261650</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
         <v>45333</v>
       </c>
@@ -1848,17 +1903,18 @@
         <v>161380</v>
       </c>
       <c r="D26" s="11"/>
-      <c r="E26" s="11">
+      <c r="E26" s="11"/>
+      <c r="F26" s="11">
         <v>257450</v>
       </c>
-      <c r="F26" s="11">
+      <c r="G26" s="11">
         <v>-22600</v>
       </c>
-      <c r="G26" s="11">
+      <c r="H26" s="11">
         <v>280050</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
         <v>45339</v>
       </c>
@@ -1866,18 +1922,19 @@
         <v>161380</v>
       </c>
       <c r="D27" s="11"/>
-      <c r="E27" s="11">
+      <c r="E27" s="11"/>
+      <c r="F27" s="11">
         <v>257450</v>
       </c>
-      <c r="F27" s="11">
+      <c r="G27" s="11">
         <v>-7450</v>
       </c>
-      <c r="G27" s="11">
+      <c r="H27" s="11">
         <v>265300</v>
       </c>
-      <c r="H27" s="14"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I27" s="14"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
         <v>45339</v>
       </c>
@@ -1885,21 +1942,22 @@
         <v>173380</v>
       </c>
       <c r="D28" s="11"/>
-      <c r="E28" s="11">
+      <c r="E28" s="11"/>
+      <c r="F28" s="11">
         <f>272250+1600</f>
         <v>273850</v>
       </c>
-      <c r="F28" s="11">
+      <c r="G28" s="11">
         <v>-15450</v>
       </c>
-      <c r="G28" s="11">
+      <c r="H28" s="11">
         <v>287700</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="I28" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <v>45347</v>
       </c>
@@ -1907,20 +1965,21 @@
         <v>173380</v>
       </c>
       <c r="D29" s="11"/>
-      <c r="E29" s="11">
+      <c r="E29" s="11"/>
+      <c r="F29" s="11">
         <v>273850</v>
       </c>
-      <c r="F29" s="11">
+      <c r="G29" s="11">
         <v>-2000</v>
       </c>
-      <c r="G29" s="11">
+      <c r="H29" s="11">
         <v>275850</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="I29" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="10">
         <v>45353</v>
       </c>
@@ -1928,20 +1987,21 @@
         <v>173380</v>
       </c>
       <c r="D30" s="11"/>
-      <c r="E30" s="11">
+      <c r="E30" s="11"/>
+      <c r="F30" s="11">
         <v>273850</v>
       </c>
-      <c r="F30" s="11">
+      <c r="G30" s="11">
         <v>11150</v>
       </c>
-      <c r="G30" s="11">
+      <c r="H30" s="11">
         <v>262700</v>
       </c>
-      <c r="H30" s="14" t="s">
+      <c r="I30" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="10">
         <v>45353</v>
       </c>
@@ -1949,20 +2009,21 @@
         <v>173380</v>
       </c>
       <c r="D31" s="11"/>
-      <c r="E31" s="11">
+      <c r="E31" s="11"/>
+      <c r="F31" s="11">
         <v>279800</v>
       </c>
-      <c r="F31" s="11">
+      <c r="G31" s="11">
         <v>-3100</v>
       </c>
-      <c r="G31" s="11">
+      <c r="H31" s="11">
         <v>282900</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="I31" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
         <v>45359</v>
       </c>
@@ -1970,20 +2031,21 @@
         <v>173380</v>
       </c>
       <c r="D32" s="11"/>
-      <c r="E32" s="11">
+      <c r="E32" s="11"/>
+      <c r="F32" s="11">
         <v>279800</v>
       </c>
-      <c r="F32" s="11">
+      <c r="G32" s="11">
         <v>11600</v>
       </c>
-      <c r="G32" s="11">
+      <c r="H32" s="11">
         <v>268200</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="I32" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="10">
         <v>45359</v>
       </c>
@@ -1991,18 +2053,19 @@
         <v>173380</v>
       </c>
       <c r="D33" s="11"/>
-      <c r="E33" s="11">
+      <c r="E33" s="11"/>
+      <c r="F33" s="11">
         <v>286600</v>
       </c>
-      <c r="F33" s="11">
+      <c r="G33" s="11">
         <v>1600</v>
       </c>
-      <c r="G33" s="11">
+      <c r="H33" s="11">
         <v>285000</v>
       </c>
-      <c r="H33" s="14"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="14"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="10">
         <v>45373</v>
       </c>
@@ -2010,19 +2073,20 @@
         <v>173380</v>
       </c>
       <c r="D34" s="11"/>
-      <c r="E34" s="11">
+      <c r="E34" s="11"/>
+      <c r="F34" s="11">
         <v>286600</v>
       </c>
-      <c r="F34" s="11">
+      <c r="G34" s="11">
         <f>32450+2100</f>
         <v>34550</v>
       </c>
-      <c r="G34" s="11">
+      <c r="H34" s="11">
         <v>252050</v>
       </c>
-      <c r="H34" s="14"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="14"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="10">
         <v>45373</v>
       </c>
@@ -2030,20 +2094,21 @@
         <v>173380</v>
       </c>
       <c r="D35" s="11"/>
-      <c r="E35" s="11">
+      <c r="E35" s="11"/>
+      <c r="F35" s="11">
         <v>290600</v>
       </c>
-      <c r="F35" s="11">
+      <c r="G35" s="11">
         <v>14550</v>
       </c>
-      <c r="G35" s="11">
+      <c r="H35" s="11">
         <v>276050</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="I35" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="10">
         <v>45380</v>
       </c>
@@ -2051,20 +2116,21 @@
         <v>173380</v>
       </c>
       <c r="D36" s="11"/>
-      <c r="E36" s="11">
+      <c r="E36" s="11"/>
+      <c r="F36" s="11">
         <v>290600</v>
       </c>
-      <c r="F36" s="11">
+      <c r="G36" s="11">
         <v>29500</v>
       </c>
-      <c r="G36" s="11">
+      <c r="H36" s="11">
         <v>261100</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="I36" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="10">
         <v>45380</v>
       </c>
@@ -2072,22 +2138,23 @@
         <v>173380</v>
       </c>
       <c r="D37" s="11"/>
-      <c r="E37" s="11">
+      <c r="E37" s="11"/>
+      <c r="F37" s="11">
         <f>297400-500</f>
         <v>296900</v>
       </c>
-      <c r="F37" s="11">
+      <c r="G37" s="11">
         <f>19500-500</f>
         <v>19000</v>
       </c>
-      <c r="G37" s="11">
+      <c r="H37" s="11">
         <v>277900</v>
       </c>
-      <c r="H37" s="14" t="s">
+      <c r="I37" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="10">
         <v>45387</v>
       </c>
@@ -2095,18 +2162,19 @@
         <v>173380</v>
       </c>
       <c r="D38" s="11"/>
-      <c r="E38" s="11">
+      <c r="E38" s="11"/>
+      <c r="F38" s="11">
         <f>297400-500</f>
         <v>296900</v>
       </c>
-      <c r="F38" s="11">
+      <c r="G38" s="11">
         <v>36650</v>
       </c>
-      <c r="G38" s="11">
+      <c r="H38" s="11">
         <v>260250</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="10">
         <v>45387</v>
       </c>
@@ -2114,17 +2182,18 @@
         <v>173380</v>
       </c>
       <c r="D39" s="11"/>
-      <c r="E39" s="11">
+      <c r="E39" s="11"/>
+      <c r="F39" s="11">
         <v>300900</v>
       </c>
-      <c r="F39" s="11">
+      <c r="G39" s="11">
         <v>16650</v>
       </c>
-      <c r="G39" s="11">
+      <c r="H39" s="11">
         <v>284250</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="10">
         <v>45392</v>
       </c>
@@ -2132,17 +2201,18 @@
         <v>173380</v>
       </c>
       <c r="D40" s="11"/>
-      <c r="E40" s="11">
+      <c r="E40" s="11"/>
+      <c r="F40" s="11">
         <v>300900</v>
       </c>
-      <c r="F40" s="11">
+      <c r="G40" s="11">
         <v>22800</v>
       </c>
-      <c r="G40" s="11">
+      <c r="H40" s="11">
         <v>278100</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="10">
         <v>45392</v>
       </c>
@@ -2150,17 +2220,18 @@
         <v>173380</v>
       </c>
       <c r="D41" s="11"/>
-      <c r="E41" s="11">
+      <c r="E41" s="11"/>
+      <c r="F41" s="11">
         <v>307700</v>
       </c>
-      <c r="F41" s="11">
+      <c r="G41" s="11">
         <v>12800</v>
       </c>
-      <c r="G41" s="11">
+      <c r="H41" s="11">
         <v>294900</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="10">
         <v>45399</v>
       </c>
@@ -2168,17 +2239,18 @@
         <v>173380</v>
       </c>
       <c r="D42" s="11"/>
-      <c r="E42" s="11">
+      <c r="E42" s="11"/>
+      <c r="F42" s="11">
         <v>307700</v>
       </c>
-      <c r="F42" s="11">
+      <c r="G42" s="11">
         <v>31150</v>
       </c>
-      <c r="G42" s="11">
+      <c r="H42" s="11">
         <v>276550</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="10">
         <v>45399</v>
       </c>
@@ -2186,17 +2258,18 @@
         <v>173380</v>
       </c>
       <c r="D43" s="11"/>
-      <c r="E43" s="11">
+      <c r="E43" s="11"/>
+      <c r="F43" s="11">
         <v>312700</v>
       </c>
-      <c r="F43" s="11">
+      <c r="G43" s="11">
         <v>6150</v>
       </c>
-      <c r="G43" s="11">
+      <c r="H43" s="11">
         <v>306550</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="10">
         <v>45410</v>
       </c>
@@ -2204,17 +2277,18 @@
         <v>173380</v>
       </c>
       <c r="D44" s="11"/>
-      <c r="E44" s="11">
+      <c r="E44" s="11"/>
+      <c r="F44" s="11">
         <v>312700</v>
       </c>
-      <c r="F44" s="11">
+      <c r="G44" s="11">
         <v>30600</v>
       </c>
-      <c r="G44" s="11">
+      <c r="H44" s="11">
         <v>282100</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="10">
         <v>45410</v>
       </c>
@@ -2222,17 +2296,18 @@
         <v>173380</v>
       </c>
       <c r="D45" s="11"/>
-      <c r="E45" s="11">
+      <c r="E45" s="11"/>
+      <c r="F45" s="11">
         <v>339900</v>
       </c>
-      <c r="F45" s="11">
+      <c r="G45" s="11">
         <v>-9400</v>
       </c>
-      <c r="G45" s="11">
+      <c r="H45" s="11">
         <v>349300</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="10">
         <v>45416</v>
       </c>
@@ -2240,17 +2315,18 @@
         <v>173380</v>
       </c>
       <c r="D46" s="11"/>
-      <c r="E46" s="11">
+      <c r="E46" s="11"/>
+      <c r="F46" s="11">
         <v>339900</v>
       </c>
-      <c r="F46" s="11">
+      <c r="G46" s="11">
         <v>1150</v>
       </c>
-      <c r="G46" s="11">
+      <c r="H46" s="11">
         <v>338750</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" s="10">
         <v>45423</v>
       </c>
@@ -2258,17 +2334,18 @@
         <v>178380</v>
       </c>
       <c r="D47" s="11"/>
-      <c r="E47" s="11">
+      <c r="E47" s="11"/>
+      <c r="F47" s="11">
         <v>339900</v>
       </c>
-      <c r="F47" s="11">
+      <c r="G47" s="11">
         <v>17150</v>
       </c>
-      <c r="G47" s="11">
+      <c r="H47" s="11">
         <v>322750</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="10">
         <v>45424</v>
       </c>
@@ -2276,20 +2353,21 @@
         <v>178380</v>
       </c>
       <c r="D48" s="11"/>
-      <c r="E48" s="11">
+      <c r="E48" s="11"/>
+      <c r="F48" s="11">
         <v>340900</v>
       </c>
-      <c r="F48" s="11">
+      <c r="G48" s="11">
         <v>12150</v>
       </c>
-      <c r="G48" s="11">
+      <c r="H48" s="11">
         <v>328750</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="10">
         <v>45424</v>
       </c>
@@ -2297,17 +2375,18 @@
         <v>178380</v>
       </c>
       <c r="D49" s="11"/>
-      <c r="E49" s="11">
+      <c r="E49" s="11"/>
+      <c r="F49" s="11">
         <v>339900</v>
       </c>
-      <c r="F49" s="11">
+      <c r="G49" s="11">
         <v>11150</v>
       </c>
-      <c r="G49" s="11">
+      <c r="H49" s="11">
         <v>328750</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="10">
         <v>45425</v>
       </c>
@@ -2315,17 +2394,18 @@
         <v>178380</v>
       </c>
       <c r="D50" s="11"/>
-      <c r="E50" s="11">
+      <c r="E50" s="11"/>
+      <c r="F50" s="11">
         <v>342500</v>
       </c>
-      <c r="F50" s="11">
+      <c r="G50" s="11">
         <v>-2050</v>
       </c>
-      <c r="G50" s="11">
+      <c r="H50" s="11">
         <v>344550</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="10">
         <v>45429</v>
       </c>
@@ -2333,17 +2413,18 @@
         <v>178380</v>
       </c>
       <c r="D51" s="11"/>
-      <c r="E51" s="11">
+      <c r="E51" s="11"/>
+      <c r="F51" s="11">
         <v>342500</v>
       </c>
-      <c r="F51" s="11">
+      <c r="G51" s="11">
         <v>4250</v>
       </c>
-      <c r="G51" s="11">
+      <c r="H51" s="11">
         <v>338250</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="10">
         <v>45429</v>
       </c>
@@ -2351,17 +2432,18 @@
         <v>178380</v>
       </c>
       <c r="D52" s="11"/>
-      <c r="E52" s="11">
+      <c r="E52" s="11"/>
+      <c r="F52" s="11">
         <v>343500</v>
       </c>
-      <c r="F52" s="11">
+      <c r="G52" s="11">
         <v>-750</v>
       </c>
-      <c r="G52" s="11">
+      <c r="H52" s="11">
         <v>344250</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="10">
         <v>45431</v>
       </c>
@@ -2369,17 +2451,18 @@
         <v>178380</v>
       </c>
       <c r="D53" s="11"/>
-      <c r="E53" s="11">
+      <c r="E53" s="11"/>
+      <c r="F53" s="11">
         <v>343500</v>
       </c>
-      <c r="F53" s="11">
+      <c r="G53" s="11">
         <v>13700</v>
       </c>
-      <c r="G53" s="11">
+      <c r="H53" s="11">
         <v>329800</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="10">
         <v>45431</v>
       </c>
@@ -2387,20 +2470,21 @@
         <v>178380</v>
       </c>
       <c r="D54" s="11"/>
-      <c r="E54" s="11">
+      <c r="E54" s="11"/>
+      <c r="F54" s="11">
         <v>348500</v>
       </c>
-      <c r="F54" s="11">
+      <c r="G54" s="11">
         <v>15300</v>
       </c>
-      <c r="G54" s="11">
+      <c r="H54" s="11">
         <v>348200</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="I54" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="10">
         <v>45436</v>
       </c>
@@ -2408,21 +2492,22 @@
         <v>178380</v>
       </c>
       <c r="D55" s="11"/>
-      <c r="E55" s="11">
+      <c r="E55" s="11"/>
+      <c r="F55" s="11">
         <v>348500</v>
       </c>
-      <c r="F55" s="11">
+      <c r="G55" s="11">
         <v>25050</v>
       </c>
-      <c r="G55" s="11">
+      <c r="H55" s="11">
         <v>338650</v>
       </c>
-      <c r="H55" s="2">
+      <c r="I55" s="2">
         <f>372200-24000</f>
         <v>348200</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="10">
         <v>45436</v>
       </c>
@@ -2430,17 +2515,18 @@
         <v>178380</v>
       </c>
       <c r="D56" s="11"/>
-      <c r="E56" s="11">
+      <c r="E56" s="11"/>
+      <c r="F56" s="11">
         <v>350800</v>
       </c>
-      <c r="F56" s="11">
+      <c r="G56" s="11">
         <v>15050</v>
       </c>
-      <c r="G56" s="11">
+      <c r="H56" s="11">
         <v>350550</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="10">
         <v>45437</v>
       </c>
@@ -2448,17 +2534,18 @@
         <v>178380</v>
       </c>
       <c r="D57" s="11"/>
-      <c r="E57" s="11">
+      <c r="E57" s="11"/>
+      <c r="F57" s="11">
         <v>350800</v>
       </c>
-      <c r="F57" s="11">
+      <c r="G57" s="11">
         <v>24800</v>
       </c>
-      <c r="G57" s="11">
+      <c r="H57" s="11">
         <v>341050</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" s="10">
         <v>45437</v>
       </c>
@@ -2466,17 +2553,18 @@
         <v>178380</v>
       </c>
       <c r="D58" s="11"/>
-      <c r="E58" s="11">
+      <c r="E58" s="11"/>
+      <c r="F58" s="11">
         <v>351850</v>
       </c>
-      <c r="F58" s="11">
+      <c r="G58" s="11">
         <v>19800</v>
       </c>
-      <c r="G58" s="11">
+      <c r="H58" s="11">
         <v>347050</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" s="10">
         <v>45443</v>
       </c>
@@ -2484,20 +2572,21 @@
         <v>178380</v>
       </c>
       <c r="D59" s="11"/>
-      <c r="E59" s="11">
+      <c r="E59" s="11"/>
+      <c r="F59" s="11">
         <v>351850</v>
       </c>
-      <c r="F59" s="11">
+      <c r="G59" s="11">
         <v>28450</v>
       </c>
-      <c r="G59" s="11">
+      <c r="H59" s="11">
         <v>338400</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="I59" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" s="10">
         <v>45443</v>
       </c>
@@ -2505,20 +2594,21 @@
         <v>178380</v>
       </c>
       <c r="D60" s="11"/>
-      <c r="E60" s="11">
+      <c r="E60" s="11"/>
+      <c r="F60" s="11">
         <v>353850</v>
       </c>
-      <c r="F60" s="11">
+      <c r="G60" s="11">
         <v>18450</v>
       </c>
-      <c r="G60" s="11">
+      <c r="H60" s="11">
         <v>350400</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="I60" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="10">
         <v>45444</v>
       </c>
@@ -2526,17 +2616,18 @@
         <v>178380</v>
       </c>
       <c r="D61" s="11"/>
-      <c r="E61" s="11">
+      <c r="E61" s="11"/>
+      <c r="F61" s="11">
         <v>353850</v>
       </c>
-      <c r="F61" s="11">
+      <c r="G61" s="11">
         <v>31200</v>
       </c>
-      <c r="G61" s="11">
+      <c r="H61" s="11">
         <v>337650</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="10">
         <v>45444</v>
       </c>
@@ -2544,20 +2635,21 @@
         <v>178380</v>
       </c>
       <c r="D62" s="11"/>
-      <c r="E62" s="11">
+      <c r="E62" s="11"/>
+      <c r="F62" s="11">
         <v>357850</v>
       </c>
-      <c r="F62" s="11">
+      <c r="G62" s="11">
         <v>11200</v>
       </c>
-      <c r="G62" s="11">
+      <c r="H62" s="11">
         <v>361650</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="I62" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="10">
         <v>45448</v>
       </c>
@@ -2565,20 +2657,21 @@
         <v>178380</v>
       </c>
       <c r="D63" s="11"/>
-      <c r="E63" s="11">
+      <c r="E63" s="11"/>
+      <c r="F63" s="11">
         <v>357850</v>
       </c>
-      <c r="F63" s="11">
+      <c r="G63" s="11">
         <v>8600</v>
       </c>
-      <c r="G63" s="11">
+      <c r="H63" s="11">
         <v>359250</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="I63" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="10">
         <v>45472</v>
       </c>
@@ -2586,20 +2679,21 @@
         <v>178380</v>
       </c>
       <c r="D64" s="11"/>
-      <c r="E64" s="11">
+      <c r="E64" s="11"/>
+      <c r="F64" s="11">
         <v>357850</v>
       </c>
-      <c r="F64" s="11">
+      <c r="G64" s="11">
         <v>68200</v>
       </c>
-      <c r="G64" s="11">
+      <c r="H64" s="11">
         <v>289650</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="I64" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="10">
         <v>45473</v>
       </c>
@@ -2610,20 +2704,21 @@
       <c r="D65" s="11">
         <v>60000</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="11"/>
+      <c r="F65" s="11">
         <v>369850</v>
       </c>
-      <c r="F65" s="11">
+      <c r="G65" s="11">
         <v>8200</v>
       </c>
-      <c r="G65" s="11">
+      <c r="H65" s="11">
         <v>301650</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="J65" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="10">
         <v>45484</v>
       </c>
@@ -2633,20 +2728,21 @@
       <c r="D66" s="11">
         <v>60000</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="11"/>
+      <c r="F66" s="11">
         <v>369850</v>
       </c>
-      <c r="F66" s="11">
+      <c r="G66" s="11">
         <v>37150</v>
       </c>
-      <c r="G66" s="11">
+      <c r="H66" s="11">
         <v>272700</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="J66" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="10">
         <v>45484</v>
       </c>
@@ -2656,17 +2752,18 @@
       <c r="D67" s="11">
         <v>60000</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="11"/>
+      <c r="F67" s="11">
         <v>373850</v>
       </c>
-      <c r="F67" s="11">
+      <c r="G67" s="11">
         <v>17150</v>
       </c>
-      <c r="G67" s="11">
+      <c r="H67" s="11">
         <v>296700</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="10">
         <v>45490</v>
       </c>
@@ -2676,17 +2773,18 @@
       <c r="D68" s="11">
         <v>60000</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="11"/>
+      <c r="F68" s="11">
         <v>373850</v>
       </c>
-      <c r="F68" s="11">
+      <c r="G68" s="11">
         <v>31950</v>
       </c>
-      <c r="G68" s="11">
+      <c r="H68" s="11">
         <v>281900</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="10">
         <v>45490</v>
       </c>
@@ -2696,17 +2794,18 @@
       <c r="D69" s="11">
         <v>60000</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="11"/>
+      <c r="F69" s="11">
         <v>375850</v>
       </c>
-      <c r="F69" s="11">
+      <c r="G69" s="11">
         <v>21950</v>
       </c>
-      <c r="G69" s="11">
+      <c r="H69" s="11">
         <v>293900</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="10">
         <v>45492</v>
       </c>
@@ -2716,17 +2815,18 @@
       <c r="D70" s="11">
         <v>60000</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="11"/>
+      <c r="F70" s="11">
         <v>375850</v>
       </c>
-      <c r="F70" s="11">
+      <c r="G70" s="11">
         <v>32000</v>
       </c>
-      <c r="G70" s="11">
+      <c r="H70" s="11">
         <v>283850</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="10">
         <v>45492</v>
       </c>
@@ -2736,17 +2836,18 @@
       <c r="D71" s="11">
         <v>60000</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="11"/>
+      <c r="F71" s="11">
         <v>379850</v>
       </c>
-      <c r="F71" s="11">
+      <c r="G71" s="11">
         <v>12000</v>
       </c>
-      <c r="G71" s="11">
+      <c r="H71" s="11">
         <v>307850</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="10">
         <v>45495</v>
       </c>
@@ -2756,18 +2857,19 @@
       <c r="D72" s="11">
         <v>60000</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="11"/>
+      <c r="F72" s="11">
         <v>379850</v>
       </c>
-      <c r="F72" s="11">
+      <c r="G72" s="11">
         <v>24550</v>
       </c>
-      <c r="G72" s="11">
+      <c r="H72" s="11">
         <v>295300</v>
       </c>
-      <c r="H72" s="15"/>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I72" s="15"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="10">
         <v>45495</v>
       </c>
@@ -2777,18 +2879,19 @@
       <c r="D73" s="11">
         <v>60000</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="11"/>
+      <c r="F73" s="11">
         <v>381850</v>
       </c>
-      <c r="F73" s="11">
+      <c r="G73" s="11">
         <v>14550</v>
       </c>
-      <c r="G73" s="11">
+      <c r="H73" s="11">
         <v>307300</v>
       </c>
-      <c r="H73" s="15"/>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I73" s="15"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="10">
         <v>45500</v>
       </c>
@@ -2798,24 +2901,25 @@
       <c r="D74" s="11">
         <v>60000</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="11"/>
+      <c r="F74" s="11">
         <v>381850</v>
       </c>
-      <c r="F74" s="11">
+      <c r="G74" s="11">
         <v>34050</v>
       </c>
-      <c r="G74" s="11">
+      <c r="H74" s="11">
         <v>287800</v>
       </c>
-      <c r="H74" s="15">
+      <c r="I74" s="15">
         <v>285400</v>
       </c>
-      <c r="I74" s="15">
-        <f>G74-H74</f>
+      <c r="J74" s="15">
+        <f>H74-I74</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="10">
         <v>45500</v>
       </c>
@@ -2825,21 +2929,22 @@
       <c r="D75" s="11">
         <v>60000</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="11"/>
+      <c r="F75" s="11">
         <v>385850</v>
       </c>
-      <c r="F75" s="11">
+      <c r="G75" s="11">
         <v>14050</v>
       </c>
-      <c r="G75" s="11">
+      <c r="H75" s="11">
         <v>311800</v>
       </c>
-      <c r="H75" s="2">
+      <c r="I75" s="2">
         <f>1400+1000</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="10">
         <v>45506</v>
       </c>
@@ -2849,17 +2954,18 @@
       <c r="D76" s="11">
         <v>60000</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="11"/>
+      <c r="F76" s="11">
         <v>385850</v>
       </c>
-      <c r="F76" s="11">
+      <c r="G76" s="11">
         <v>42750</v>
       </c>
-      <c r="G76" s="11">
+      <c r="H76" s="11">
         <v>283100</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="10">
         <v>45506</v>
       </c>
@@ -2869,18 +2975,19 @@
       <c r="D77" s="11">
         <v>60000</v>
       </c>
-      <c r="E77" s="11">
+      <c r="E77" s="11"/>
+      <c r="F77" s="11">
         <v>392800</v>
       </c>
-      <c r="F77" s="11">
+      <c r="G77" s="11">
         <v>7750</v>
       </c>
-      <c r="G77" s="11">
+      <c r="H77" s="11">
         <v>325050</v>
       </c>
-      <c r="H77" s="15"/>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I77" s="15"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="10">
         <v>45513</v>
       </c>
@@ -2890,17 +2997,18 @@
       <c r="D78" s="11">
         <v>60000</v>
       </c>
-      <c r="E78" s="11">
+      <c r="E78" s="11"/>
+      <c r="F78" s="11">
         <v>392800</v>
       </c>
-      <c r="F78" s="11">
+      <c r="G78" s="11">
         <v>25400</v>
       </c>
-      <c r="G78" s="11">
+      <c r="H78" s="11">
         <v>307400</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="10">
         <v>45513</v>
       </c>
@@ -2910,18 +3018,19 @@
       <c r="D79" s="11">
         <v>60000</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="11"/>
+      <c r="F79" s="11">
         <v>394800</v>
       </c>
-      <c r="F79" s="11">
+      <c r="G79" s="11">
         <v>15400</v>
       </c>
-      <c r="G79" s="11">
+      <c r="H79" s="11">
         <v>319400</v>
       </c>
-      <c r="H79" s="14"/>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I79" s="14"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="10">
         <v>45522</v>
       </c>
@@ -2931,18 +3040,19 @@
       <c r="D80" s="11">
         <v>60000</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="11"/>
+      <c r="F80" s="11">
         <v>394800</v>
       </c>
-      <c r="F80" s="11">
+      <c r="G80" s="11">
         <v>41800</v>
       </c>
-      <c r="G80" s="11">
+      <c r="H80" s="11">
         <v>293000</v>
       </c>
-      <c r="H80" s="14"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I80" s="14"/>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" s="10">
         <v>45522</v>
       </c>
@@ -2952,18 +3062,19 @@
       <c r="D81" s="11">
         <v>60000</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="11"/>
+      <c r="F81" s="11">
         <v>400800</v>
       </c>
-      <c r="F81" s="11">
+      <c r="G81" s="11">
         <v>11800</v>
       </c>
-      <c r="G81" s="11">
+      <c r="H81" s="11">
         <v>329000</v>
       </c>
-      <c r="H81" s="14"/>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I81" s="14"/>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" s="10">
         <v>45529</v>
       </c>
@@ -2973,18 +3084,19 @@
       <c r="D82" s="11">
         <v>60000</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="11"/>
+      <c r="F82" s="11">
         <v>400800</v>
       </c>
-      <c r="F82" s="11">
+      <c r="G82" s="11">
         <v>27200</v>
       </c>
-      <c r="G82" s="11">
+      <c r="H82" s="11">
         <v>308600</v>
       </c>
-      <c r="H82" s="14"/>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I82" s="14"/>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" s="10">
         <v>45529</v>
       </c>
@@ -2994,18 +3106,19 @@
       <c r="D83" s="11">
         <v>60000</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E83" s="11"/>
+      <c r="F83" s="11">
         <v>398800</v>
       </c>
-      <c r="F83" s="11">
+      <c r="G83" s="11">
         <v>12200</v>
       </c>
-      <c r="G83" s="11">
+      <c r="H83" s="11">
         <v>326600</v>
       </c>
-      <c r="H83" s="14"/>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I83" s="14"/>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" s="10">
         <v>45534</v>
       </c>
@@ -3015,18 +3128,19 @@
       <c r="D84" s="11">
         <v>60000</v>
       </c>
-      <c r="E84" s="11">
+      <c r="E84" s="11"/>
+      <c r="F84" s="11">
         <v>398800</v>
       </c>
-      <c r="F84" s="11">
+      <c r="G84" s="11">
         <v>34150</v>
       </c>
-      <c r="G84" s="11">
+      <c r="H84" s="11">
         <v>304650</v>
       </c>
-      <c r="H84" s="14"/>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I84" s="14"/>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" s="10">
         <v>45534</v>
       </c>
@@ -3036,18 +3150,19 @@
       <c r="D85" s="11">
         <v>60000</v>
       </c>
-      <c r="E85" s="11">
+      <c r="E85" s="11"/>
+      <c r="F85" s="11">
         <v>403800</v>
       </c>
-      <c r="F85" s="11">
+      <c r="G85" s="11">
         <v>9150</v>
       </c>
-      <c r="G85" s="11">
+      <c r="H85" s="11">
         <v>334650</v>
       </c>
-      <c r="H85" s="14"/>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I85" s="14"/>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" s="10">
         <v>45542</v>
       </c>
@@ -3057,18 +3172,19 @@
       <c r="D86" s="11">
         <v>60000</v>
       </c>
-      <c r="E86" s="11">
+      <c r="E86" s="11"/>
+      <c r="F86" s="11">
         <v>403800</v>
       </c>
-      <c r="F86" s="11">
+      <c r="G86" s="11">
         <v>33700</v>
       </c>
-      <c r="G86" s="11">
+      <c r="H86" s="11">
         <v>310100</v>
       </c>
-      <c r="H86" s="14"/>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I86" s="14"/>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" s="10">
         <v>45542</v>
       </c>
@@ -3078,20 +3194,21 @@
       <c r="D87" s="11">
         <v>60000</v>
       </c>
-      <c r="E87" s="11">
+      <c r="E87" s="11"/>
+      <c r="F87" s="11">
         <v>404800</v>
       </c>
-      <c r="F87" s="11">
+      <c r="G87" s="11">
         <v>28700</v>
       </c>
-      <c r="G87" s="11">
+      <c r="H87" s="11">
         <v>316100</v>
       </c>
-      <c r="H87" s="14" t="s">
+      <c r="I87" s="14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" s="10">
         <v>45544</v>
       </c>
@@ -3101,20 +3218,21 @@
       <c r="D88" s="11">
         <v>60000</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="11"/>
+      <c r="F88" s="11">
         <v>399300</v>
       </c>
-      <c r="F88" s="11">
+      <c r="G88" s="11">
         <v>23200</v>
       </c>
-      <c r="G88" s="11">
+      <c r="H88" s="11">
         <v>316100</v>
       </c>
-      <c r="H88" s="14" t="s">
+      <c r="I88" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" s="10">
         <v>45549</v>
       </c>
@@ -3124,18 +3242,19 @@
       <c r="D89" s="11">
         <v>60000</v>
       </c>
-      <c r="E89" s="11">
+      <c r="E89" s="11"/>
+      <c r="F89" s="11">
         <v>399300</v>
       </c>
-      <c r="F89" s="11">
+      <c r="G89" s="11">
         <v>41150</v>
       </c>
-      <c r="G89" s="11">
+      <c r="H89" s="11">
         <v>298150</v>
       </c>
-      <c r="H89" s="14"/>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I89" s="14"/>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" s="10">
         <v>45549</v>
       </c>
@@ -3145,20 +3264,21 @@
       <c r="D90" s="11">
         <v>60000</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="11"/>
+      <c r="F90" s="11">
         <v>403300</v>
       </c>
-      <c r="F90" s="11">
+      <c r="G90" s="11">
         <v>21150</v>
       </c>
-      <c r="G90" s="11">
+      <c r="H90" s="11">
         <v>322150</v>
       </c>
-      <c r="H90" s="14" t="s">
+      <c r="I90" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" s="10">
         <v>45556</v>
       </c>
@@ -3168,18 +3288,19 @@
       <c r="D91" s="11">
         <v>60000</v>
       </c>
-      <c r="E91" s="11">
+      <c r="E91" s="11"/>
+      <c r="F91" s="11">
         <v>403300</v>
       </c>
-      <c r="F91" s="11">
+      <c r="G91" s="11">
         <v>54700</v>
       </c>
-      <c r="G91" s="11">
+      <c r="H91" s="11">
         <v>288600</v>
       </c>
-      <c r="H91" s="14"/>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I91" s="14"/>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" s="10">
         <v>45556</v>
       </c>
@@ -3189,18 +3310,19 @@
       <c r="D92" s="11">
         <v>60000</v>
       </c>
-      <c r="E92" s="11">
+      <c r="E92" s="11"/>
+      <c r="F92" s="11">
         <v>407250</v>
       </c>
-      <c r="F92" s="11">
+      <c r="G92" s="11">
         <v>34700</v>
       </c>
-      <c r="G92" s="11">
+      <c r="H92" s="11">
         <v>312550</v>
       </c>
-      <c r="H92" s="14"/>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I92" s="14"/>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" s="10">
         <v>45560</v>
       </c>
@@ -3210,18 +3332,19 @@
       <c r="D93" s="11">
         <v>60000</v>
       </c>
-      <c r="E93" s="11">
+      <c r="E93" s="11"/>
+      <c r="F93" s="11">
         <v>407250</v>
       </c>
-      <c r="F93" s="11">
+      <c r="G93" s="11">
         <v>45750</v>
       </c>
-      <c r="G93" s="11">
+      <c r="H93" s="11">
         <v>301500</v>
       </c>
-      <c r="H93" s="14"/>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" s="10">
         <v>45560</v>
       </c>
@@ -3231,20 +3354,21 @@
       <c r="D94" s="11">
         <v>60000</v>
       </c>
-      <c r="E94" s="11">
+      <c r="E94" s="11"/>
+      <c r="F94" s="11">
         <v>409250</v>
       </c>
-      <c r="F94" s="11">
+      <c r="G94" s="11">
         <v>35750</v>
       </c>
-      <c r="G94" s="11">
+      <c r="H94" s="11">
         <v>313500</v>
       </c>
-      <c r="H94" s="14" t="s">
+      <c r="I94" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95" s="10">
         <v>45561</v>
       </c>
@@ -3254,18 +3378,19 @@
       <c r="D95" s="11">
         <v>60000</v>
       </c>
-      <c r="E95" s="11">
+      <c r="E95" s="11"/>
+      <c r="F95" s="11">
         <v>409250</v>
       </c>
-      <c r="F95" s="11">
+      <c r="G95" s="11">
         <v>51900</v>
       </c>
-      <c r="G95" s="11">
+      <c r="H95" s="11">
         <v>297350</v>
       </c>
-      <c r="H95" s="14"/>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I95" s="14"/>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" s="10">
         <v>45561</v>
       </c>
@@ -3275,20 +3400,21 @@
       <c r="D96" s="11">
         <v>60000</v>
       </c>
-      <c r="E96" s="11">
+      <c r="E96" s="11"/>
+      <c r="F96" s="11">
         <v>413250</v>
       </c>
-      <c r="F96" s="11">
+      <c r="G96" s="11">
         <v>31900</v>
       </c>
-      <c r="G96" s="11">
+      <c r="H96" s="11">
         <v>321350</v>
       </c>
-      <c r="H96" s="14" t="s">
+      <c r="I96" s="14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" s="10">
         <v>45561</v>
       </c>
@@ -3298,18 +3424,19 @@
       <c r="D97" s="11">
         <v>60000</v>
       </c>
-      <c r="E97" s="11">
+      <c r="E97" s="11"/>
+      <c r="F97" s="11">
         <v>413250</v>
       </c>
-      <c r="F97" s="11">
+      <c r="G97" s="11">
         <v>33400</v>
       </c>
-      <c r="G97" s="11">
+      <c r="H97" s="11">
         <v>319850</v>
       </c>
-      <c r="H97" s="14"/>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" s="10">
         <v>45561</v>
       </c>
@@ -3319,20 +3446,21 @@
       <c r="D98" s="11">
         <v>60000</v>
       </c>
-      <c r="E98" s="11">
+      <c r="E98" s="11"/>
+      <c r="F98" s="11">
         <v>415250</v>
       </c>
-      <c r="F98" s="11">
+      <c r="G98" s="11">
         <v>23400</v>
       </c>
-      <c r="G98" s="11">
+      <c r="H98" s="11">
         <v>331850</v>
       </c>
-      <c r="H98" s="14" t="s">
+      <c r="I98" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" s="10">
         <v>45569</v>
       </c>
@@ -3342,18 +3470,19 @@
       <c r="D99" s="11">
         <v>60000</v>
       </c>
-      <c r="E99" s="11">
+      <c r="E99" s="11"/>
+      <c r="F99" s="11">
         <v>415250</v>
       </c>
-      <c r="F99" s="11">
+      <c r="G99" s="11">
         <v>41000</v>
       </c>
-      <c r="G99" s="11">
+      <c r="H99" s="11">
         <v>314250</v>
       </c>
-      <c r="H99" s="14"/>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I99" s="14"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" s="10">
         <v>45569</v>
       </c>
@@ -3363,20 +3492,21 @@
       <c r="D100" s="11">
         <v>60000</v>
       </c>
-      <c r="E100" s="11">
+      <c r="E100" s="11"/>
+      <c r="F100" s="11">
         <v>418250</v>
       </c>
-      <c r="F100" s="11">
+      <c r="G100" s="11">
         <v>26000</v>
       </c>
-      <c r="G100" s="11">
+      <c r="H100" s="11">
         <v>332250</v>
       </c>
-      <c r="H100" s="14" t="s">
+      <c r="I100" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" s="10">
         <v>45577</v>
       </c>
@@ -3386,18 +3516,19 @@
       <c r="D101" s="11">
         <v>60000</v>
       </c>
-      <c r="E101" s="11">
+      <c r="E101" s="11"/>
+      <c r="F101" s="11">
         <v>418250</v>
       </c>
-      <c r="F101" s="11">
+      <c r="G101" s="11">
         <v>56850</v>
       </c>
-      <c r="G101" s="11">
+      <c r="H101" s="11">
         <v>301400</v>
       </c>
-      <c r="H101" s="14"/>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I101" s="14"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" s="10">
         <v>45577</v>
       </c>
@@ -3407,20 +3538,21 @@
       <c r="D102" s="11">
         <v>60000</v>
       </c>
-      <c r="E102" s="11">
+      <c r="E102" s="11"/>
+      <c r="F102" s="11">
         <v>428250</v>
       </c>
-      <c r="F102" s="11">
+      <c r="G102" s="11">
         <v>6850</v>
       </c>
-      <c r="G102" s="11">
+      <c r="H102" s="11">
         <v>361400</v>
       </c>
-      <c r="H102" s="14" t="s">
+      <c r="I102" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B103" s="10">
         <v>45577</v>
       </c>
@@ -3430,18 +3562,19 @@
       <c r="D103" s="11">
         <v>60000</v>
       </c>
-      <c r="E103" s="11">
+      <c r="E103" s="11"/>
+      <c r="F103" s="11">
         <v>428250</v>
       </c>
-      <c r="F103" s="11">
+      <c r="G103" s="11">
         <v>16450</v>
       </c>
-      <c r="G103" s="11">
+      <c r="H103" s="11">
         <v>351800</v>
       </c>
-      <c r="H103" s="14"/>
-    </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I103" s="14"/>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" s="10">
         <v>45583</v>
       </c>
@@ -3451,18 +3584,19 @@
       <c r="D104" s="11">
         <v>60000</v>
       </c>
-      <c r="E104" s="11">
+      <c r="E104" s="11"/>
+      <c r="F104" s="11">
         <v>428250</v>
       </c>
-      <c r="F104" s="11">
+      <c r="G104" s="11">
         <v>72100</v>
       </c>
-      <c r="G104" s="11">
+      <c r="H104" s="11">
         <v>296150</v>
       </c>
-      <c r="H104" s="14"/>
-    </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I104" s="14"/>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" s="10">
         <v>45583</v>
       </c>
@@ -3472,20 +3606,21 @@
       <c r="D105" s="11">
         <v>60000</v>
       </c>
-      <c r="E105" s="11">
+      <c r="E105" s="11"/>
+      <c r="F105" s="11">
         <v>428250</v>
       </c>
-      <c r="F105" s="11">
+      <c r="G105" s="11">
         <v>270100</v>
       </c>
-      <c r="G105" s="11">
+      <c r="H105" s="11">
         <v>296150</v>
       </c>
-      <c r="H105" s="14" t="s">
+      <c r="I105" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" s="10">
         <v>45583</v>
       </c>
@@ -3495,18 +3630,19 @@
       <c r="D106" s="11">
         <v>60000</v>
       </c>
-      <c r="E106" s="11">
+      <c r="E106" s="11"/>
+      <c r="F106" s="11">
         <v>716250</v>
       </c>
-      <c r="F106" s="11">
+      <c r="G106" s="11">
         <v>20100</v>
       </c>
-      <c r="G106" s="11">
+      <c r="H106" s="11">
         <v>636150</v>
       </c>
-      <c r="H106" s="14"/>
-    </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I106" s="14"/>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" s="10">
         <v>45586</v>
       </c>
@@ -3516,18 +3652,19 @@
       <c r="D107" s="11">
         <v>60000</v>
       </c>
-      <c r="E107" s="11">
+      <c r="E107" s="11"/>
+      <c r="F107" s="11">
         <v>716250</v>
       </c>
-      <c r="F107" s="11">
+      <c r="G107" s="11">
         <v>31200</v>
       </c>
-      <c r="G107" s="11">
+      <c r="H107" s="11">
         <v>625050</v>
       </c>
-      <c r="H107" s="14"/>
-    </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I107" s="14"/>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" s="10">
         <v>45586</v>
       </c>
@@ -3537,20 +3674,21 @@
       <c r="D108" s="11">
         <v>60000</v>
       </c>
-      <c r="E108" s="11">
+      <c r="E108" s="11"/>
+      <c r="F108" s="11">
         <v>718250</v>
       </c>
-      <c r="F108" s="11">
+      <c r="G108" s="11">
         <v>21200</v>
       </c>
-      <c r="G108" s="11">
+      <c r="H108" s="11">
         <v>637050</v>
       </c>
-      <c r="H108" s="14" t="s">
+      <c r="I108" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" s="10">
         <v>45590</v>
       </c>
@@ -3560,18 +3698,19 @@
       <c r="D109" s="11">
         <v>60000</v>
       </c>
-      <c r="E109" s="11">
+      <c r="E109" s="11"/>
+      <c r="F109" s="11">
         <v>718250</v>
       </c>
-      <c r="F109" s="11">
+      <c r="G109" s="11">
         <v>40550</v>
       </c>
-      <c r="G109" s="11">
+      <c r="H109" s="11">
         <v>617700</v>
       </c>
-      <c r="H109" s="14"/>
-    </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I109" s="14"/>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" s="10">
         <v>45590</v>
       </c>
@@ -3581,20 +3720,21 @@
       <c r="D110" s="11">
         <v>60000</v>
       </c>
-      <c r="E110" s="11">
+      <c r="E110" s="11"/>
+      <c r="F110" s="11">
         <v>722250</v>
       </c>
-      <c r="F110" s="11">
+      <c r="G110" s="11">
         <v>20550</v>
       </c>
-      <c r="G110" s="11">
+      <c r="H110" s="11">
         <v>641700</v>
       </c>
-      <c r="H110" s="14" t="s">
+      <c r="I110" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="10">
         <v>45595</v>
       </c>
@@ -3604,18 +3744,19 @@
       <c r="D111" s="11">
         <v>60000</v>
       </c>
-      <c r="E111" s="11">
+      <c r="E111" s="11"/>
+      <c r="F111" s="11">
         <v>722250</v>
       </c>
-      <c r="F111" s="11">
+      <c r="G111" s="11">
         <v>62650</v>
       </c>
-      <c r="G111" s="11">
+      <c r="H111" s="11">
         <v>599600</v>
       </c>
-      <c r="H111" s="14"/>
-    </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I111" s="14"/>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="10">
         <v>45595</v>
       </c>
@@ -3625,20 +3766,21 @@
       <c r="D112" s="11">
         <v>60000</v>
       </c>
-      <c r="E112" s="11">
+      <c r="E112" s="11"/>
+      <c r="F112" s="11">
         <v>730250</v>
       </c>
-      <c r="F112" s="11">
+      <c r="G112" s="11">
         <v>22650</v>
       </c>
-      <c r="G112" s="11">
+      <c r="H112" s="11">
         <v>647600</v>
       </c>
-      <c r="H112" s="14" t="s">
+      <c r="I112" s="14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="10">
         <v>45601</v>
       </c>
@@ -3648,18 +3790,19 @@
       <c r="D113" s="11">
         <v>60000</v>
       </c>
-      <c r="E113" s="11">
+      <c r="E113" s="11"/>
+      <c r="F113" s="11">
         <v>730250</v>
       </c>
-      <c r="F113" s="11">
+      <c r="G113" s="11">
         <v>51000</v>
       </c>
-      <c r="G113" s="11">
+      <c r="H113" s="11">
         <v>619250</v>
       </c>
-      <c r="H113" s="14"/>
-    </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I113" s="14"/>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" s="10">
         <v>45601</v>
       </c>
@@ -3669,20 +3812,21 @@
       <c r="D114" s="11">
         <v>60000</v>
       </c>
-      <c r="E114" s="11">
+      <c r="E114" s="11"/>
+      <c r="F114" s="11">
         <v>736250</v>
       </c>
-      <c r="F114" s="11">
+      <c r="G114" s="11">
         <v>21000</v>
       </c>
-      <c r="G114" s="11">
+      <c r="H114" s="11">
         <v>655250</v>
       </c>
-      <c r="H114" s="14" t="s">
+      <c r="I114" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B115" s="10">
         <v>45602</v>
       </c>
@@ -3692,18 +3836,19 @@
       <c r="D115" s="11">
         <v>60000</v>
       </c>
-      <c r="E115" s="11">
+      <c r="E115" s="11"/>
+      <c r="F115" s="11">
         <v>736250</v>
       </c>
-      <c r="F115" s="11">
+      <c r="G115" s="11">
         <v>30550</v>
       </c>
-      <c r="G115" s="11">
+      <c r="H115" s="11">
         <v>645700</v>
       </c>
-      <c r="H115" s="14"/>
-    </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I115" s="14"/>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" s="10">
         <v>45611</v>
       </c>
@@ -3713,18 +3858,19 @@
       <c r="D116" s="11">
         <v>60000</v>
       </c>
-      <c r="E116" s="11">
+      <c r="E116" s="11"/>
+      <c r="F116" s="11">
         <v>736250</v>
       </c>
-      <c r="F116" s="11">
+      <c r="G116" s="11">
         <v>92100</v>
       </c>
-      <c r="G116" s="11">
+      <c r="H116" s="11">
         <v>584150</v>
       </c>
-      <c r="H116" s="14"/>
-    </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I116" s="14"/>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" s="10">
         <v>45611</v>
       </c>
@@ -3734,20 +3880,21 @@
       <c r="D117" s="11">
         <v>60000</v>
       </c>
-      <c r="E117" s="11">
+      <c r="E117" s="11"/>
+      <c r="F117" s="11">
         <v>748250</v>
       </c>
-      <c r="F117" s="11">
+      <c r="G117" s="11">
         <v>32100</v>
       </c>
-      <c r="G117" s="11">
+      <c r="H117" s="11">
         <v>656150</v>
       </c>
-      <c r="H117" s="14" t="s">
+      <c r="I117" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B118" s="10">
         <v>45611</v>
       </c>
@@ -3757,20 +3904,21 @@
       <c r="D118" s="11">
         <v>60000</v>
       </c>
-      <c r="E118" s="11">
+      <c r="E118" s="11"/>
+      <c r="F118" s="11">
         <v>741750</v>
       </c>
-      <c r="F118" s="11">
+      <c r="G118" s="11">
         <v>25600</v>
       </c>
-      <c r="G118" s="11">
+      <c r="H118" s="11">
         <v>656150</v>
       </c>
-      <c r="H118" s="14" t="s">
+      <c r="I118" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" s="10">
         <v>45611</v>
       </c>
@@ -3780,18 +3928,19 @@
       <c r="D119" s="11">
         <v>60000</v>
       </c>
-      <c r="E119" s="11">
+      <c r="E119" s="11"/>
+      <c r="F119" s="11">
         <v>741750</v>
       </c>
-      <c r="F119" s="11">
+      <c r="G119" s="11">
         <v>43400</v>
       </c>
-      <c r="G119" s="11">
+      <c r="H119" s="11">
         <v>638350</v>
       </c>
-      <c r="H119" s="14"/>
-    </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I119" s="14"/>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" s="10">
         <v>45618</v>
       </c>
@@ -3801,21 +3950,22 @@
       <c r="D120" s="11">
         <v>60000</v>
       </c>
-      <c r="E120" s="11">
+      <c r="E120" s="11"/>
+      <c r="F120" s="11">
         <f>831950-30000</f>
         <v>801950</v>
       </c>
-      <c r="F120" s="11">
+      <c r="G120" s="11">
         <v>36400</v>
       </c>
-      <c r="G120" s="11">
+      <c r="H120" s="11">
         <v>735550</v>
       </c>
-      <c r="H120" s="14" t="s">
+      <c r="I120" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" s="10">
         <v>45621</v>
       </c>
@@ -3825,19 +3975,20 @@
       <c r="D121" s="11">
         <v>60000</v>
       </c>
-      <c r="E121" s="11">
+      <c r="E121" s="11"/>
+      <c r="F121" s="11">
         <f>831950-30000</f>
         <v>801950</v>
       </c>
-      <c r="F121" s="11">
+      <c r="G121" s="11">
         <v>50300</v>
       </c>
-      <c r="G121" s="11">
+      <c r="H121" s="11">
         <v>721650</v>
       </c>
-      <c r="H121" s="14"/>
-    </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I121" s="14"/>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B122" s="10">
         <v>45626</v>
       </c>
@@ -3847,19 +3998,20 @@
       <c r="D122" s="11">
         <v>60000</v>
       </c>
-      <c r="E122" s="11">
+      <c r="E122" s="11"/>
+      <c r="F122" s="11">
         <f>831950-30000</f>
         <v>801950</v>
       </c>
-      <c r="F122" s="11">
+      <c r="G122" s="11">
         <v>76050</v>
       </c>
-      <c r="G122" s="11">
+      <c r="H122" s="11">
         <v>695900</v>
       </c>
-      <c r="H122" s="14"/>
-    </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I122" s="14"/>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" s="10">
         <v>45626</v>
       </c>
@@ -3869,21 +4021,22 @@
       <c r="D123" s="11">
         <v>60000</v>
       </c>
-      <c r="E123" s="11">
+      <c r="E123" s="11"/>
+      <c r="F123" s="11">
         <f>831950-30000</f>
         <v>801950</v>
       </c>
-      <c r="F123" s="11">
+      <c r="G123" s="11">
         <v>71050</v>
       </c>
-      <c r="G123" s="11">
+      <c r="H123" s="11">
         <v>695900</v>
       </c>
-      <c r="H123" s="14" t="s">
+      <c r="I123" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="124" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="10">
         <v>45626</v>
       </c>
@@ -3893,21 +4046,22 @@
       <c r="D124" s="11">
         <v>60000</v>
       </c>
-      <c r="E124" s="11">
+      <c r="E124" s="11"/>
+      <c r="F124" s="11">
         <f>836950-25000</f>
         <v>811950</v>
       </c>
-      <c r="F124" s="11">
+      <c r="G124" s="11">
         <v>21050</v>
       </c>
-      <c r="G124" s="11">
+      <c r="H124" s="11">
         <v>755900</v>
       </c>
-      <c r="H124" s="14" t="s">
+      <c r="I124" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="10">
         <v>45628</v>
       </c>
@@ -3917,19 +4071,20 @@
       <c r="D125" s="11">
         <v>60000</v>
       </c>
-      <c r="E125" s="11">
+      <c r="E125" s="11"/>
+      <c r="F125" s="11">
         <f>836950-25000</f>
         <v>811950</v>
       </c>
-      <c r="F125" s="11">
+      <c r="G125" s="11">
         <v>29950</v>
       </c>
-      <c r="G125" s="11">
+      <c r="H125" s="11">
         <v>747000</v>
       </c>
-      <c r="H125" s="14"/>
-    </row>
-    <row r="126" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I125" s="14"/>
+    </row>
+    <row r="126" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="10">
         <v>45632</v>
       </c>
@@ -3939,19 +4094,20 @@
       <c r="D126" s="11">
         <v>60000</v>
       </c>
-      <c r="E126" s="11">
+      <c r="E126" s="11"/>
+      <c r="F126" s="11">
         <f>836950-25000</f>
         <v>811950</v>
       </c>
-      <c r="F126" s="11">
+      <c r="G126" s="11">
         <v>83550</v>
       </c>
-      <c r="G126" s="11">
+      <c r="H126" s="11">
         <v>693400</v>
       </c>
-      <c r="H126" s="14"/>
-    </row>
-    <row r="127" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I126" s="14"/>
+    </row>
+    <row r="127" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="10">
         <v>45632</v>
       </c>
@@ -3961,21 +4117,22 @@
       <c r="D127" s="11">
         <v>60000</v>
       </c>
-      <c r="E127" s="11">
+      <c r="E127" s="11"/>
+      <c r="F127" s="11">
         <v>811950</v>
       </c>
-      <c r="F127" s="11">
-        <f>F126-5000</f>
+      <c r="G127" s="11">
+        <f>G126-5000</f>
         <v>78550</v>
       </c>
-      <c r="G127" s="11">
+      <c r="H127" s="11">
         <v>693400</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="I127" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="128" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="10">
         <v>45632</v>
       </c>
@@ -3985,212 +4142,541 @@
       <c r="D128" s="11">
         <v>60000</v>
       </c>
-      <c r="E128" s="11">
+      <c r="E128" s="11"/>
+      <c r="F128" s="11">
         <f>841950-20000</f>
         <v>821950</v>
       </c>
-      <c r="F128" s="11">
+      <c r="G128" s="11">
         <v>28550</v>
       </c>
-      <c r="G128" s="11">
+      <c r="H128" s="11">
         <v>753400</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="I128" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="129" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="10"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
+    <row r="129" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="10">
+        <v>45640</v>
+      </c>
+      <c r="C129" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D129" s="11">
+        <v>60000</v>
+      </c>
       <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="11"/>
-    </row>
-    <row r="130" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="10"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
+      <c r="F129" s="11">
+        <f>841950-20000-6500</f>
+        <v>815450</v>
+      </c>
+      <c r="G129" s="11">
+        <f>28550-6500</f>
+        <v>22050</v>
+      </c>
+      <c r="H129" s="11">
+        <v>753400</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C130" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D130" s="11">
+        <v>60000</v>
+      </c>
       <c r="E130" s="11"/>
-      <c r="F130" s="11"/>
-      <c r="G130" s="11"/>
-      <c r="H130" s="14"/>
-    </row>
-    <row r="131" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="10"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11"/>
+      <c r="F130" s="11">
+        <f>841950-20000-6500</f>
+        <v>815450</v>
+      </c>
+      <c r="G130" s="11">
+        <v>239400</v>
+      </c>
+      <c r="H130" s="11">
+        <v>536050</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C131" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D131" s="11">
+        <v>60000</v>
+      </c>
       <c r="E131" s="11"/>
-      <c r="F131" s="11"/>
-      <c r="G131" s="11"/>
-    </row>
-    <row r="132" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="10"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
+      <c r="F131" s="11">
+        <f>841950-20000-6500</f>
+        <v>815450</v>
+      </c>
+      <c r="G131" s="11">
+        <v>236400</v>
+      </c>
+      <c r="H131" s="11">
+        <v>536050</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C132" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D132" s="11">
+        <v>60000</v>
+      </c>
       <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="11"/>
-    </row>
-    <row r="133" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="10"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
+      <c r="F132" s="11">
+        <f>952850-17000-25300</f>
+        <v>910550</v>
+      </c>
+      <c r="G132" s="11">
+        <v>36400</v>
+      </c>
+      <c r="H132" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I132" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C133" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D133" s="11">
+        <v>60000</v>
+      </c>
       <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="11"/>
-    </row>
-    <row r="134" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="10"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11"/>
+      <c r="F133" s="11">
+        <f>952850-17000-25300</f>
+        <v>910550</v>
+      </c>
+      <c r="G133" s="11">
+        <f>36400-4000</f>
+        <v>32400</v>
+      </c>
+      <c r="H133" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I133" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C134" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D134" s="11">
+        <v>60000</v>
+      </c>
       <c r="E134" s="11"/>
-      <c r="F134" s="11"/>
-      <c r="G134" s="11"/>
-    </row>
-    <row r="135" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="10"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
-      <c r="F135" s="11"/>
-      <c r="G135" s="11"/>
-    </row>
-    <row r="136" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="10"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="11"/>
-    </row>
-    <row r="137" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="10"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
-      <c r="F137" s="11"/>
-      <c r="G137" s="11"/>
-    </row>
-    <row r="138" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="10"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
-      <c r="G138" s="11"/>
-    </row>
-    <row r="139" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F134" s="11">
+        <f>952850-17000-25300</f>
+        <v>910550</v>
+      </c>
+      <c r="G134" s="11">
+        <f>G133-13400</f>
+        <v>19000</v>
+      </c>
+      <c r="H134" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I134" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C135" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D135" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E135" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F135" s="11">
+        <v>910550</v>
+      </c>
+      <c r="G135" s="11">
+        <v>19000</v>
+      </c>
+      <c r="H135" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C136" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D136" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E136" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F136" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G136" s="11">
+        <v>19000</v>
+      </c>
+      <c r="H136" s="11">
+        <v>868450</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="10">
+        <v>45650</v>
+      </c>
+      <c r="C137" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D137" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E137" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F137" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G137" s="11">
+        <v>27250</v>
+      </c>
+      <c r="H137" s="11">
+        <v>860200</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="10">
+        <v>45650</v>
+      </c>
+      <c r="C138" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D138" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E138" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F138" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G138" s="11">
+        <v>27250</v>
+      </c>
+      <c r="H138" s="11">
+        <v>860200</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="10"/>
       <c r="C139" s="11"/>
       <c r="D139" s="11"/>
       <c r="E139" s="11"/>
       <c r="F139" s="11"/>
       <c r="G139" s="11"/>
-    </row>
-    <row r="140" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H139" s="11"/>
+      <c r="I139" s="14"/>
+    </row>
+    <row r="140" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B140" s="10"/>
       <c r="C140" s="11"/>
       <c r="D140" s="11"/>
       <c r="E140" s="11"/>
       <c r="F140" s="11"/>
       <c r="G140" s="11"/>
-    </row>
-    <row r="141" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H140" s="11"/>
+      <c r="I140" s="14"/>
+    </row>
+    <row r="141" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="10"/>
       <c r="C141" s="11"/>
       <c r="D141" s="11"/>
       <c r="E141" s="11"/>
       <c r="F141" s="11"/>
       <c r="G141" s="11"/>
-    </row>
-    <row r="142" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H141" s="11"/>
+    </row>
+    <row r="142" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B142" s="10"/>
       <c r="C142" s="11"/>
       <c r="D142" s="11"/>
       <c r="E142" s="11"/>
       <c r="F142" s="11"/>
       <c r="G142" s="11"/>
-    </row>
-    <row r="143" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H142" s="11"/>
+      <c r="I142" s="14"/>
+    </row>
+    <row r="143" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="10"/>
       <c r="C143" s="11"/>
       <c r="D143" s="11"/>
       <c r="E143" s="11"/>
       <c r="F143" s="11"/>
       <c r="G143" s="11"/>
-    </row>
-    <row r="144" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H143" s="11"/>
+    </row>
+    <row r="144" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="10"/>
       <c r="C144" s="11"/>
       <c r="D144" s="11"/>
       <c r="E144" s="11"/>
       <c r="F144" s="11"/>
       <c r="G144" s="11"/>
-    </row>
-    <row r="145" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H144" s="11"/>
+      <c r="I144" s="14"/>
+      <c r="J144" s="14"/>
+    </row>
+    <row r="145" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="10"/>
       <c r="C145" s="11"/>
       <c r="D145" s="11"/>
       <c r="E145" s="11"/>
       <c r="F145" s="11"/>
       <c r="G145" s="11"/>
-    </row>
-    <row r="146" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H145" s="11"/>
+    </row>
+    <row r="146" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="10"/>
       <c r="C146" s="11"/>
       <c r="D146" s="11"/>
       <c r="E146" s="11"/>
       <c r="F146" s="11"/>
       <c r="G146" s="11"/>
-    </row>
-    <row r="147" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H146" s="11"/>
+    </row>
+    <row r="147" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B147" s="10"/>
       <c r="C147" s="11"/>
       <c r="D147" s="11"/>
       <c r="E147" s="11"/>
       <c r="F147" s="11"/>
       <c r="G147" s="11"/>
-    </row>
-    <row r="148" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H147" s="11"/>
+      <c r="I147" s="14"/>
+    </row>
+    <row r="148" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="10"/>
       <c r="C148" s="11"/>
       <c r="D148" s="11"/>
       <c r="E148" s="11"/>
       <c r="F148" s="11"/>
       <c r="G148" s="11"/>
-    </row>
-    <row r="149" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H148" s="11"/>
+    </row>
+    <row r="149" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B149" s="10"/>
       <c r="C149" s="11"/>
       <c r="D149" s="11"/>
       <c r="E149" s="11"/>
       <c r="F149" s="11"/>
       <c r="G149" s="11"/>
-    </row>
-    <row r="150" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H149" s="11"/>
+    </row>
+    <row r="150" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B150" s="10"/>
       <c r="C150" s="11"/>
       <c r="D150" s="11"/>
       <c r="E150" s="11"/>
       <c r="F150" s="11"/>
       <c r="G150" s="11"/>
-    </row>
-    <row r="151" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H150" s="11"/>
+    </row>
+    <row r="151" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B151" s="10"/>
       <c r="C151" s="11"/>
       <c r="D151" s="11"/>
       <c r="E151" s="11"/>
       <c r="F151" s="11"/>
       <c r="G151" s="11"/>
-    </row>
-    <row r="152" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H151" s="11"/>
+    </row>
+    <row r="152" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B152" s="10"/>
       <c r="C152" s="11"/>
       <c r="D152" s="11"/>
       <c r="E152" s="11"/>
       <c r="F152" s="11"/>
       <c r="G152" s="11"/>
+      <c r="H152" s="11"/>
+    </row>
+    <row r="153" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="10"/>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="11"/>
+      <c r="G153" s="11"/>
+      <c r="H153" s="11"/>
+    </row>
+    <row r="154" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="10"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="11"/>
+      <c r="G154" s="11"/>
+      <c r="H154" s="11"/>
+    </row>
+    <row r="155" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="10"/>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="11"/>
+      <c r="G155" s="11"/>
+      <c r="H155" s="11"/>
+    </row>
+    <row r="156" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="10"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="11"/>
+    </row>
+    <row r="157" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="10"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+      <c r="G157" s="11"/>
+      <c r="H157" s="11"/>
+    </row>
+    <row r="168" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H168" s="3">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="169" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H169" s="3">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="170" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H170" s="3">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="171" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H171" s="3">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="172" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H172" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="173" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H173" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="174" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H174" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="175" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H175" s="3">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="176" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H176" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="177" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H177" s="3">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="178" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F178" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H178" s="3">
+        <f>SUM(H168:H177)</f>
+        <v>174700</v>
+      </c>
+    </row>
+    <row r="179" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H179" s="3">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="180" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H180" s="3">
+        <f>H179-H178</f>
+        <v>25300</v>
+      </c>
+    </row>
+    <row r="181" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D181" s="3">
+        <f>174700+7900+13400+4000</f>
+        <v>200000</v>
+      </c>
+      <c r="H181" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="182" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H182" s="3">
+        <f>H180-H181</f>
+        <v>21300</v>
+      </c>
+    </row>
+    <row r="183" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I183" s="2">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="184" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I184" s="14">
+        <f>H182-I183</f>
+        <v>13400</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -13,8 +13,105 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="F140" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F141" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F142" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -156,6 +253,12 @@
   <si>
     <t>deposit</t>
   </si>
+  <si>
+    <t>loan angom bijenty 50000 (due 10000)</t>
+  </si>
+  <si>
+    <t>rambhabati 7900 clear</t>
+  </si>
 </sst>
 </file>
 
@@ -166,7 +269,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +309,19 @@
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -446,7 +562,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -925,11 +1040,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="196722688"/>
-        <c:axId val="196724224"/>
+        <c:axId val="143708160"/>
+        <c:axId val="143709696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="196722688"/>
+        <c:axId val="143708160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -972,14 +1087,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="196724224"/>
+        <c:crossAx val="143709696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="196724224"/>
+        <c:axId val="143709696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1030,7 +1145,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="196722688"/>
+        <c:crossAx val="143708160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1044,7 +1159,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1401,14 +1515,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4406,43 +4520,104 @@
       </c>
     </row>
     <row r="139" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="10"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="11"/>
-      <c r="H139" s="11"/>
+      <c r="B139" s="10">
+        <v>45651</v>
+      </c>
+      <c r="C139" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D139" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E139" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F139" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G139" s="11">
+        <v>35250</v>
+      </c>
+      <c r="H139" s="11">
+        <v>852200</v>
+      </c>
       <c r="I139" s="14"/>
     </row>
     <row r="140" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="10"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="11"/>
-      <c r="H140" s="11"/>
-      <c r="I140" s="14"/>
+      <c r="B140" s="10">
+        <v>45651</v>
+      </c>
+      <c r="C140" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D140" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E140" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F140" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G140" s="11">
+        <v>-4750</v>
+      </c>
+      <c r="H140" s="11">
+        <v>912200</v>
+      </c>
+      <c r="I140" s="14" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="141" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="10"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11"/>
-      <c r="G141" s="11"/>
-      <c r="H141" s="11"/>
+      <c r="B141" s="10">
+        <v>45654</v>
+      </c>
+      <c r="C141" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D141" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E141" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F141" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G141" s="11">
+        <v>3650</v>
+      </c>
+      <c r="H141" s="11">
+        <v>903800</v>
+      </c>
+      <c r="I141" s="14"/>
     </row>
     <row r="142" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="10"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
-      <c r="G142" s="11"/>
-      <c r="H142" s="11"/>
-      <c r="I142" s="14"/>
+      <c r="B142" s="10">
+        <v>45654</v>
+      </c>
+      <c r="C142" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D142" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E142" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F142" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G142" s="11">
+        <v>-4250</v>
+      </c>
+      <c r="H142" s="11">
+        <v>903800</v>
+      </c>
+      <c r="I142" s="14" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="143" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="10"/>
@@ -4472,6 +4647,7 @@
       <c r="F145" s="11"/>
       <c r="G145" s="11"/>
       <c r="H145" s="11"/>
+      <c r="I145" s="14"/>
     </row>
     <row r="146" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="10"/>
@@ -4518,6 +4694,7 @@
       <c r="F150" s="11"/>
       <c r="G150" s="11"/>
       <c r="H150" s="11"/>
+      <c r="I150" s="14"/>
     </row>
     <row r="151" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B151" s="10"/>
@@ -4682,5 +4859,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6000" windowWidth="20640" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="6000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
+    <sheet name="2025TrendAnalysis" sheetId="16" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621" iterateDelta="1E-4"/>
 </workbook>
@@ -106,12 +107,325 @@
         </r>
       </text>
     </comment>
+    <comment ref="F143" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E144" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+sales of rice: 14600
+dividend: 7300
+pay to ranjit: 8000+3500
+ranjita balance: -4200
+ranjit deposit 2300
+pay to ranjit: -1900
+ranjit deposit: 5000
+ranjit deposit total: 5000+2300</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F144" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+sunanda due 5400</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="F17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+967450 total
+10000 deposit
+17000 sunanda due
+7900 rambhabati due
+10000 bijenty due
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+sales of rice: 14600
+dividend: 7300
+pay to ranjit: 8000+3500
+ranjita balance: -4200
+ranjit deposit 2300
+pay to ranjit: -1900
+ranjit deposit: 5000
+ranjit deposit total: 5000+2300</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+sunanda due 5400</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+sunanda due 5400</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+sunanda due 5400</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -258,6 +572,12 @@
   </si>
   <si>
     <t>rambhabati 7900 clear</t>
+  </si>
+  <si>
+    <t>pay sunanda 11600; bijenti 10000</t>
+  </si>
+  <si>
+    <t>pay sunanda 5400</t>
   </si>
 </sst>
 </file>
@@ -1040,11 +1360,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="143708160"/>
-        <c:axId val="143709696"/>
+        <c:axId val="179944832"/>
+        <c:axId val="179958912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="143708160"/>
+        <c:axId val="179944832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1087,14 +1407,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143709696"/>
+        <c:crossAx val="179958912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="143709696"/>
+        <c:axId val="179958912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1145,7 +1465,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143708160"/>
+        <c:crossAx val="179944832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1159,6 +1479,450 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000322" l="0.70000000000000062" r="0.70000000000000062" t="0.75000000000000322" header="0.30000000000000032" footer="0.30000000000000032"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Trend Analysis</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2025TrendAnalysis'!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>equity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!#REF!</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!$C$3:$C$3</c:f>
+              <c:numCache>
+                <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>35000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-588A-4FD6-90A1-C2BC5C3DF530}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2025TrendAnalysis'!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FirmValue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!#REF!</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!$F$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-588A-4FD6-90A1-C2BC5C3DF530}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2025TrendAnalysis'!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CashBalance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!#REF!</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!$G$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-588A-4FD6-90A1-C2BC5C3DF530}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2025TrendAnalysis'!$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Outstanding Amount</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!#REF!</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2025TrendAnalysis'!$H$3:$H$3</c:f>
+              <c:numCache>
+                <c:formatCode>_ "₹"\ * #,##0.00_ ;_ "₹"\ * \-#,##0.00_ ;_ "₹"\ * "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-588A-4FD6-90A1-C2BC5C3DF530}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="213006208"/>
+        <c:axId val="213007744"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="213006208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="213007744"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="213007744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="213006208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1244,6 +2008,43 @@
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1515,7 +2316,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4620,23 +5421,54 @@
       </c>
     </row>
     <row r="143" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="10"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
+      <c r="B143" s="10">
+        <v>45661</v>
+      </c>
+      <c r="C143" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D143" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E143" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F143" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G143" s="11">
+        <v>19300</v>
+      </c>
+      <c r="H143" s="11">
+        <v>880250</v>
+      </c>
     </row>
     <row r="144" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="10"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="F144" s="11"/>
-      <c r="G144" s="11"/>
-      <c r="H144" s="11"/>
-      <c r="I144" s="14"/>
+      <c r="B144" s="10">
+        <v>45661</v>
+      </c>
+      <c r="C144" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D144" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E144" s="11">
+        <f>10000+7300</f>
+        <v>17300</v>
+      </c>
+      <c r="F144" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G144" s="11">
+        <v>-2300</v>
+      </c>
+      <c r="H144" s="11">
+        <v>880250</v>
+      </c>
+      <c r="I144" s="14" t="s">
+        <v>49</v>
+      </c>
       <c r="J144" s="14"/>
     </row>
     <row r="145" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4657,6 +5489,7 @@
       <c r="F146" s="11"/>
       <c r="G146" s="11"/>
       <c r="H146" s="11"/>
+      <c r="I146" s="14"/>
     </row>
     <row r="147" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B147" s="10"/>
@@ -4861,4 +5694,763 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:J61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="15" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="2:9" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="10">
+        <v>45632</v>
+      </c>
+      <c r="C4" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D4" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11">
+        <v>811950</v>
+      </c>
+      <c r="G4" s="11" t="e">
+        <f>#REF!-5000</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H4" s="11">
+        <v>693400</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="10">
+        <v>45632</v>
+      </c>
+      <c r="C5" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D5" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11">
+        <f>841950-20000</f>
+        <v>821950</v>
+      </c>
+      <c r="G5" s="11">
+        <v>28550</v>
+      </c>
+      <c r="H5" s="11">
+        <v>753400</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="10">
+        <v>45640</v>
+      </c>
+      <c r="C6" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D6" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11">
+        <f>841950-20000-6500</f>
+        <v>815450</v>
+      </c>
+      <c r="G6" s="11">
+        <f>28550-6500</f>
+        <v>22050</v>
+      </c>
+      <c r="H6" s="11">
+        <v>753400</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C7" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D7" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11">
+        <f>841950-20000-6500</f>
+        <v>815450</v>
+      </c>
+      <c r="G7" s="11">
+        <v>239400</v>
+      </c>
+      <c r="H7" s="11">
+        <v>536050</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C8" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D8" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11">
+        <f>841950-20000-6500</f>
+        <v>815450</v>
+      </c>
+      <c r="G8" s="11">
+        <v>236400</v>
+      </c>
+      <c r="H8" s="11">
+        <v>536050</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C9" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D9" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11">
+        <f>952850-17000-25300</f>
+        <v>910550</v>
+      </c>
+      <c r="G9" s="11">
+        <v>36400</v>
+      </c>
+      <c r="H9" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C10" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D10" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11">
+        <f>952850-17000-25300</f>
+        <v>910550</v>
+      </c>
+      <c r="G10" s="11">
+        <f>36400-4000</f>
+        <v>32400</v>
+      </c>
+      <c r="H10" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C11" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D11" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11">
+        <f>952850-17000-25300</f>
+        <v>910550</v>
+      </c>
+      <c r="G11" s="11">
+        <f>G10-13400</f>
+        <v>19000</v>
+      </c>
+      <c r="H11" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C12" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D12" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E12" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F12" s="11">
+        <v>910550</v>
+      </c>
+      <c r="G12" s="11">
+        <v>19000</v>
+      </c>
+      <c r="H12" s="11">
+        <v>856450</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="10">
+        <v>45647</v>
+      </c>
+      <c r="C13" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D13" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E13" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F13" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G13" s="11">
+        <v>19000</v>
+      </c>
+      <c r="H13" s="11">
+        <v>868450</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="10">
+        <v>45650</v>
+      </c>
+      <c r="C14" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D14" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E14" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F14" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G14" s="11">
+        <v>27250</v>
+      </c>
+      <c r="H14" s="11">
+        <v>860200</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="10">
+        <v>45650</v>
+      </c>
+      <c r="C15" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D15" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G15" s="11">
+        <v>27250</v>
+      </c>
+      <c r="H15" s="11">
+        <v>860200</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="10">
+        <v>45651</v>
+      </c>
+      <c r="C16" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D16" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E16" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F16" s="11">
+        <v>912550</v>
+      </c>
+      <c r="G16" s="11">
+        <v>35250</v>
+      </c>
+      <c r="H16" s="11">
+        <v>852200</v>
+      </c>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="10">
+        <v>45651</v>
+      </c>
+      <c r="C17" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D17" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E17" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F17" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G17" s="11">
+        <v>-4750</v>
+      </c>
+      <c r="H17" s="11">
+        <v>912200</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="10">
+        <v>45654</v>
+      </c>
+      <c r="C18" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D18" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E18" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F18" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G18" s="11">
+        <v>3650</v>
+      </c>
+      <c r="H18" s="11">
+        <v>903800</v>
+      </c>
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="10">
+        <v>45654</v>
+      </c>
+      <c r="C19" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D19" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E19" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F19" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G19" s="11">
+        <v>-4250</v>
+      </c>
+      <c r="H19" s="11">
+        <v>903800</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="10">
+        <v>45661</v>
+      </c>
+      <c r="C20" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D20" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E20" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F20" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G20" s="11">
+        <v>19300</v>
+      </c>
+      <c r="H20" s="11">
+        <v>880250</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="10">
+        <v>45661</v>
+      </c>
+      <c r="C21" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D21" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E21" s="11">
+        <f>10000+7300</f>
+        <v>17300</v>
+      </c>
+      <c r="F21" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G21" s="11">
+        <v>-2300</v>
+      </c>
+      <c r="H21" s="11">
+        <v>880250</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="10">
+        <v>45668</v>
+      </c>
+      <c r="C22" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D22" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E22" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F22" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G22" s="11">
+        <v>23450</v>
+      </c>
+      <c r="H22" s="11">
+        <v>854500</v>
+      </c>
+      <c r="I22" s="14"/>
+    </row>
+    <row r="23" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="10">
+        <v>45668</v>
+      </c>
+      <c r="C23" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D23" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E23" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F23" s="11">
+        <v>922550</v>
+      </c>
+      <c r="G23" s="11">
+        <v>18050</v>
+      </c>
+      <c r="H23" s="11">
+        <v>854500</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="14">
+        <f>G22-5400</f>
+        <v>18050</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="14"/>
+    </row>
+    <row r="28" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+    </row>
+    <row r="32" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+    </row>
+    <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+    </row>
+    <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H45" s="3">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H46" s="3">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H47" s="3">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H48" s="3">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H49" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H50" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H51" s="3">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H52" s="3">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H53" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H54" s="3">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F55" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55" s="3">
+        <f>SUM(H45:H54)</f>
+        <v>174700</v>
+      </c>
+    </row>
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H56" s="3">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H57" s="3">
+        <f>H56-H55</f>
+        <v>25300</v>
+      </c>
+    </row>
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D58" s="3">
+        <f>174700+7900+13400+4000</f>
+        <v>200000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H59" s="3">
+        <f>H57-H58</f>
+        <v>21300</v>
+      </c>
+    </row>
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I60" s="2">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I61" s="14">
+        <f>H59-I60</f>
+        <v>13400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -578,6 +578,18 @@
   </si>
   <si>
     <t>pay sunanda 5400</t>
+  </si>
+  <si>
+    <t>remove asiqi 50000+anita 33000</t>
+  </si>
+  <si>
+    <t>pay marup 6500</t>
+  </si>
+  <si>
+    <t>pay loan induleikha 20000</t>
+  </si>
+  <si>
+    <t>pay loan sweety 20000</t>
   </si>
 </sst>
 </file>
@@ -1360,11 +1372,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="179944832"/>
-        <c:axId val="179958912"/>
+        <c:axId val="197169152"/>
+        <c:axId val="197170688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="179944832"/>
+        <c:axId val="197169152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1407,14 +1419,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="179958912"/>
+        <c:crossAx val="197170688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="179958912"/>
+        <c:axId val="197170688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1465,7 +1477,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="179944832"/>
+        <c:crossAx val="197169152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1628,9 +1640,9 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
+            <c:multiLvlStrRef>
               <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:numRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1678,9 +1690,9 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
+            <c:multiLvlStrRef>
               <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:numRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1725,9 +1737,9 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
+            <c:multiLvlStrRef>
               <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:numRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1772,9 +1784,9 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
+            <c:multiLvlStrRef>
               <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:numRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1802,11 +1814,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="213006208"/>
-        <c:axId val="213007744"/>
+        <c:axId val="197740800"/>
+        <c:axId val="197746688"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="213006208"/>
+        <c:axId val="197740800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1849,7 +1861,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="213007744"/>
+        <c:crossAx val="197746688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1857,7 +1869,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="213007744"/>
+        <c:axId val="197746688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1908,7 +1920,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="213006208"/>
+        <c:crossAx val="197740800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2316,7 +2328,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5698,7 +5710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J61"/>
+  <dimension ref="B1:J62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -6247,64 +6259,160 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="14">
-        <f>G22-5400</f>
+      <c r="B24" s="10">
+        <v>45670</v>
+      </c>
+      <c r="C24" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D24" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E24" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F24" s="11">
+        <v>839550</v>
+      </c>
+      <c r="G24" s="11">
         <v>18050</v>
       </c>
+      <c r="H24" s="11">
+        <v>771500</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="25" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+      <c r="B25" s="10">
+        <v>45670</v>
+      </c>
+      <c r="C25" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D25" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E25" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F25" s="11">
+        <f>922550-83000</f>
+        <v>839550</v>
+      </c>
+      <c r="G25" s="11">
+        <v>34400</v>
+      </c>
+      <c r="H25" s="11">
+        <v>755150</v>
+      </c>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="B26" s="10">
+        <v>45670</v>
+      </c>
+      <c r="C26" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D26" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E26" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F26" s="11">
+        <f>853350-E26</f>
+        <v>836050</v>
+      </c>
+      <c r="G26" s="11">
+        <v>14400</v>
+      </c>
+      <c r="H26" s="11">
+        <v>778950</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="27" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
+      <c r="B27" s="10">
+        <v>45675</v>
+      </c>
+      <c r="C27" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D27" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E27" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F27" s="11">
+        <f>853350-E27</f>
+        <v>836050</v>
+      </c>
+      <c r="G27" s="11">
+        <v>33100</v>
+      </c>
+      <c r="H27" s="11">
+        <v>760250</v>
+      </c>
       <c r="I27" s="14"/>
     </row>
     <row r="28" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="10"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="B28" s="10">
+        <v>45675</v>
+      </c>
+      <c r="C28" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D28" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E28" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F28" s="11">
+        <f>853350-E28-6500</f>
+        <v>829550</v>
+      </c>
+      <c r="G28" s="11">
+        <v>26600</v>
+      </c>
+      <c r="H28" s="11">
+        <v>784050</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="29" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
+      <c r="B29" s="10">
+        <v>45675</v>
+      </c>
+      <c r="C29" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D29" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E29" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F29" s="11">
+        <v>833350</v>
+      </c>
+      <c r="G29" s="11">
+        <v>6600</v>
+      </c>
+      <c r="H29" s="11">
+        <v>784050</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="30" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="10"/>
@@ -6314,6 +6422,7 @@
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
+      <c r="I30" s="14"/>
     </row>
     <row r="31" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="10"/>
@@ -6323,6 +6432,7 @@
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
+      <c r="I31" s="14"/>
     </row>
     <row r="32" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="10"/>
@@ -6351,29 +6461,33 @@
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H45" s="3">
-        <v>10600</v>
-      </c>
+    <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H46" s="3">
-        <v>8600</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H47" s="3">
-        <v>17400</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H48" s="3">
-        <v>27000</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="49" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H49" s="3">
-        <v>14800</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="50" spans="4:9" x14ac:dyDescent="0.25">
@@ -6383,67 +6497,72 @@
     </row>
     <row r="51" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H51" s="3">
-        <v>7700</v>
+        <v>14800</v>
       </c>
     </row>
     <row r="52" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H52" s="3">
-        <v>4800</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="53" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H53" s="3">
-        <v>33000</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="54" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H54" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H55" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="F55" s="3" t="s">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F56" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H55" s="3">
-        <f>SUM(H45:H54)</f>
+      <c r="H56" s="3">
+        <f>SUM(H46:H55)</f>
         <v>174700</v>
-      </c>
-    </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H56" s="3">
-        <v>200000</v>
       </c>
     </row>
     <row r="57" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H57" s="3">
-        <f>H56-H55</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H58" s="3">
+        <f>H57-H56</f>
         <v>25300</v>
       </c>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D58" s="3">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D59" s="3">
         <f>174700+7900+13400+4000</f>
         <v>200000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H59" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H59" s="3">
-        <f>H57-H58</f>
+    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H60" s="3">
+        <f>H58-H59</f>
         <v>21300</v>
       </c>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="I60" s="2">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I61" s="2">
         <v>7900</v>
       </c>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="I61" s="14">
-        <f>H59-I60</f>
+    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I62" s="14">
+        <f>H60-I61</f>
         <v>13400</v>
       </c>
     </row>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -590,6 +590,36 @@
   </si>
   <si>
     <t>pay loan sweety 20000</t>
+  </si>
+  <si>
+    <t>actual/projected  receivable</t>
+  </si>
+  <si>
+    <t>53600/39700</t>
+  </si>
+  <si>
+    <t>pay loan joychandra 50000</t>
+  </si>
+  <si>
+    <t>46250'/41801</t>
+  </si>
+  <si>
+    <t>'/41800</t>
+  </si>
+  <si>
+    <t>pay loan pratima 10000</t>
+  </si>
+  <si>
+    <t>/42500</t>
+  </si>
+  <si>
+    <t>30100/42500</t>
+  </si>
+  <si>
+    <t>pay loan bidyakumar 35000</t>
+  </si>
+  <si>
+    <t>/44950</t>
   </si>
 </sst>
 </file>
@@ -787,7 +817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -826,6 +856,9 @@
     </xf>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1372,11 +1405,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="197169152"/>
-        <c:axId val="197170688"/>
+        <c:axId val="197685248"/>
+        <c:axId val="197686784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="197169152"/>
+        <c:axId val="197685248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1419,14 +1452,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197170688"/>
+        <c:crossAx val="197686784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="197170688"/>
+        <c:axId val="197686784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1477,7 +1510,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197169152"/>
+        <c:crossAx val="197685248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1814,11 +1847,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="197740800"/>
-        <c:axId val="197746688"/>
+        <c:axId val="197998848"/>
+        <c:axId val="198004736"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="197740800"/>
+        <c:axId val="197998848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1861,7 +1894,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197746688"/>
+        <c:crossAx val="198004736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1869,7 +1902,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="197746688"/>
+        <c:axId val="198004736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1920,7 +1953,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197740800"/>
+        <c:crossAx val="197998848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2040,13 +2073,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2328,7 +2361,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5710,7 +5743,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J62"/>
+  <dimension ref="B1:K62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -5718,14 +5751,14 @@
     <col min="3" max="5" width="15" style="3" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="25.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="8" max="9" width="19.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:9" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:10" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
         <v>16</v>
@@ -5745,8 +5778,11 @@
       <c r="H2" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -5758,8 +5794,9 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="2:9" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10">
         <v>45632</v>
       </c>
@@ -5780,11 +5817,12 @@
       <c r="H4" s="11">
         <v>693400</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="11"/>
+      <c r="J4" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
         <v>45632</v>
       </c>
@@ -5805,11 +5843,12 @@
       <c r="H5" s="11">
         <v>753400</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="11"/>
+      <c r="J5" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="10">
         <v>45640</v>
       </c>
@@ -5831,11 +5870,12 @@
       <c r="H6" s="11">
         <v>753400</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="11"/>
+      <c r="J6" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>45647</v>
       </c>
@@ -5856,8 +5896,9 @@
       <c r="H7" s="11">
         <v>536050</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10">
         <v>45647</v>
       </c>
@@ -5878,11 +5919,12 @@
       <c r="H8" s="11">
         <v>536050</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="11"/>
+      <c r="J8" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
         <v>45647</v>
       </c>
@@ -5903,11 +5945,12 @@
       <c r="H9" s="11">
         <v>856450</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="11"/>
+      <c r="J9" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>45647</v>
       </c>
@@ -5929,11 +5972,12 @@
       <c r="H10" s="11">
         <v>856450</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="11"/>
+      <c r="J10" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
         <v>45647</v>
       </c>
@@ -5955,11 +5999,12 @@
       <c r="H11" s="11">
         <v>856450</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="11"/>
+      <c r="J11" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
         <v>45647</v>
       </c>
@@ -5981,11 +6026,12 @@
       <c r="H12" s="11">
         <v>856450</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="11"/>
+      <c r="J12" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10">
         <v>45647</v>
       </c>
@@ -6007,11 +6053,12 @@
       <c r="H13" s="11">
         <v>868450</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="11"/>
+      <c r="J13" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>45650</v>
       </c>
@@ -6033,8 +6080,9 @@
       <c r="H14" s="11">
         <v>860200</v>
       </c>
-    </row>
-    <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
         <v>45650</v>
       </c>
@@ -6056,8 +6104,9 @@
       <c r="H15" s="11">
         <v>860200</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10">
         <v>45651</v>
       </c>
@@ -6079,9 +6128,10 @@
       <c r="H16" s="11">
         <v>852200</v>
       </c>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="11"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10">
         <v>45651</v>
       </c>
@@ -6103,11 +6153,12 @@
       <c r="H17" s="11">
         <v>912200</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="11"/>
+      <c r="J17" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>45654</v>
       </c>
@@ -6129,9 +6180,10 @@
       <c r="H18" s="11">
         <v>903800</v>
       </c>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="11"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="10">
         <v>45654</v>
       </c>
@@ -6153,11 +6205,12 @@
       <c r="H19" s="11">
         <v>903800</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="11"/>
+      <c r="J19" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="10">
         <v>45661</v>
       </c>
@@ -6179,8 +6232,9 @@
       <c r="H20" s="11">
         <v>880250</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="10">
         <v>45661</v>
       </c>
@@ -6203,12 +6257,13 @@
       <c r="H21" s="11">
         <v>880250</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="11"/>
+      <c r="J21" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="J21" s="14"/>
-    </row>
-    <row r="22" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10">
         <v>45668</v>
       </c>
@@ -6230,9 +6285,10 @@
       <c r="H22" s="11">
         <v>854500</v>
       </c>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="11"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="10">
         <v>45668</v>
       </c>
@@ -6254,11 +6310,12 @@
       <c r="H23" s="11">
         <v>854500</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="11"/>
+      <c r="J23" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="10">
         <v>45670</v>
       </c>
@@ -6280,11 +6337,12 @@
       <c r="H24" s="11">
         <v>771500</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="11"/>
+      <c r="J24" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
         <v>45670</v>
       </c>
@@ -6307,9 +6365,10 @@
       <c r="H25" s="11">
         <v>755150</v>
       </c>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I25" s="11"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10">
         <v>45670</v>
       </c>
@@ -6332,11 +6391,12 @@
       <c r="H26" s="11">
         <v>778950</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="11"/>
+      <c r="J26" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
         <v>45675</v>
       </c>
@@ -6359,9 +6419,10 @@
       <c r="H27" s="11">
         <v>760250</v>
       </c>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I27" s="11"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
         <v>45675</v>
       </c>
@@ -6384,11 +6445,12 @@
       <c r="H28" s="11">
         <v>784050</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="11"/>
+      <c r="J28" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <v>45675</v>
       </c>
@@ -6410,161 +6472,309 @@
       <c r="H29" s="11">
         <v>784050</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="11"/>
+      <c r="J29" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="10"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="10"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="10"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="10"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="10"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H46" s="3">
-        <v>10600</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H47" s="3">
-        <v>8600</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H48" s="3">
-        <v>17400</v>
-      </c>
-    </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H49" s="3">
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H50" s="3">
-        <v>14800</v>
-      </c>
-    </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H51" s="3">
-        <v>14800</v>
-      </c>
-    </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H52" s="3">
-        <v>7700</v>
-      </c>
-    </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H53" s="3">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H54" s="3">
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H55" s="3">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="F56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H56" s="3">
-        <f>SUM(H46:H55)</f>
-        <v>174700</v>
-      </c>
-    </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H57" s="3">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H58" s="3">
-        <f>H57-H56</f>
-        <v>25300</v>
-      </c>
-    </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D59" s="3">
-        <f>174700+7900+13400+4000</f>
-        <v>200000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H60" s="3">
-        <f>H58-H59</f>
-        <v>21300</v>
-      </c>
-    </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="I61" s="2">
-        <v>7900</v>
-      </c>
-    </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="I62" s="14">
-        <f>H60-I61</f>
-        <v>13400</v>
-      </c>
+    <row r="30" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="10">
+        <v>45683</v>
+      </c>
+      <c r="C30" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D30" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E30" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F30" s="11">
+        <f>H30+D30+G30-E30</f>
+        <v>828150</v>
+      </c>
+      <c r="G30" s="11">
+        <v>61000</v>
+      </c>
+      <c r="H30" s="11">
+        <v>724450</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="10">
+        <v>45683</v>
+      </c>
+      <c r="C31" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D31" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E31" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F31" s="11">
+        <f>H31+D31+G31-E31</f>
+        <v>837950</v>
+      </c>
+      <c r="G31" s="11">
+        <v>11000</v>
+      </c>
+      <c r="H31" s="11">
+        <v>784250</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="10">
+        <v>45689</v>
+      </c>
+      <c r="C32" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D32" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E32" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F32" s="11">
+        <f>H32+D32+G32-E32</f>
+        <v>837950</v>
+      </c>
+      <c r="G32" s="11">
+        <v>33400</v>
+      </c>
+      <c r="H32" s="11">
+        <v>761850</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="10">
+        <v>45689</v>
+      </c>
+      <c r="C33" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D33" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E33" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F33" s="11">
+        <v>839950</v>
+      </c>
+      <c r="G33" s="11">
+        <v>23400</v>
+      </c>
+      <c r="H33" s="11">
+        <v>773850</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="10">
+        <v>45695</v>
+      </c>
+      <c r="C34" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D34" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E34" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F34" s="11">
+        <v>839950</v>
+      </c>
+      <c r="G34" s="11">
+        <v>53600</v>
+      </c>
+      <c r="H34" s="11">
+        <v>743750</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="10">
+        <v>45695</v>
+      </c>
+      <c r="C35" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D35" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E35" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F35" s="11">
+        <v>847050</v>
+      </c>
+      <c r="G35" s="11">
+        <v>18600</v>
+      </c>
+      <c r="H35" s="11">
+        <v>785750</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="10">
+        <v>45696</v>
+      </c>
+      <c r="C36" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D36" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E36" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F36" s="11">
+        <v>847050</v>
+      </c>
+      <c r="G36" s="11">
+        <v>21850</v>
+      </c>
+      <c r="H36" s="11">
+        <v>782500</v>
+      </c>
+      <c r="I36" s="16"/>
+    </row>
+    <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="16"/>
+    </row>
+    <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="16"/>
+    </row>
+    <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="16"/>
+    </row>
+    <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="16"/>
+    </row>
+    <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="10"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="16"/>
+    </row>
+    <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="16"/>
+    </row>
+    <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="16"/>
+    </row>
+    <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="16"/>
+    </row>
+    <row r="62" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J62" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -620,6 +620,18 @@
   </si>
   <si>
     <t>/44950</t>
+  </si>
+  <si>
+    <t>/45650</t>
+  </si>
+  <si>
+    <t>pay loan a manao</t>
+  </si>
+  <si>
+    <t>34450/45650</t>
+  </si>
+  <si>
+    <t>pay bomcha 6500</t>
   </si>
 </sst>
 </file>
@@ -1405,11 +1417,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="197685248"/>
-        <c:axId val="197686784"/>
+        <c:axId val="145124352"/>
+        <c:axId val="145134336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="197685248"/>
+        <c:axId val="145124352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1452,14 +1464,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197686784"/>
+        <c:crossAx val="145134336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="197686784"/>
+        <c:axId val="145134336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1510,7 +1522,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197685248"/>
+        <c:crossAx val="145124352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1630,7 +1642,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1847,11 +1858,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="197998848"/>
-        <c:axId val="198004736"/>
+        <c:axId val="146351616"/>
+        <c:axId val="146353152"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="197998848"/>
+        <c:axId val="146351616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1894,7 +1905,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="198004736"/>
+        <c:crossAx val="146353152"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1902,7 +1913,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="198004736"/>
+        <c:axId val="146353152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1953,7 +1964,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="197998848"/>
+        <c:crossAx val="146351616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1967,7 +1978,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6672,45 +6682,112 @@
       <c r="I36" s="16"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="10"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
+      <c r="B37" s="10">
+        <v>45698</v>
+      </c>
+      <c r="C37" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D37" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E37" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F37" s="11">
+        <v>847050</v>
+      </c>
+      <c r="G37" s="11">
+        <v>32900</v>
+      </c>
+      <c r="H37" s="11">
+        <v>771450</v>
+      </c>
       <c r="I37" s="16"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="10"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="16"/>
+      <c r="B38" s="10">
+        <v>45698</v>
+      </c>
+      <c r="C38" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D38" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E38" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F38" s="11">
+        <v>851050</v>
+      </c>
+      <c r="G38" s="11">
+        <v>12900</v>
+      </c>
+      <c r="H38" s="11">
+        <v>795450</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="10"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="16"/>
+      <c r="B39" s="10">
+        <v>45702</v>
+      </c>
+      <c r="C39" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D39" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E39" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F39" s="11">
+        <v>851050</v>
+      </c>
+      <c r="G39" s="11">
+        <v>36300</v>
+      </c>
+      <c r="H39" s="11">
+        <v>772050</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="10"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="14"/>
+      <c r="B40" s="10">
+        <v>45702</v>
+      </c>
+      <c r="C40" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D40" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E40" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F40" s="11">
+        <v>844550</v>
+      </c>
+      <c r="G40" s="11">
+        <v>29800</v>
+      </c>
+      <c r="H40" s="11">
+        <v>772050</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="10"/>
@@ -6732,6 +6809,7 @@
       <c r="G42" s="11"/>
       <c r="H42" s="11"/>
       <c r="I42" s="16"/>
+      <c r="J42" s="14"/>
     </row>
     <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="10"/>
@@ -6742,6 +6820,7 @@
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="16"/>
+      <c r="J43" s="14"/>
     </row>
     <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="10"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -632,6 +632,24 @@
   </si>
   <si>
     <t>pay bomcha 6500</t>
+  </si>
+  <si>
+    <t>37750/45650</t>
+  </si>
+  <si>
+    <t>marup angom 10000</t>
+  </si>
+  <si>
+    <t>36450/45650</t>
+  </si>
+  <si>
+    <t>loan sonia 20000</t>
+  </si>
+  <si>
+    <t>loan sheenarani 10000</t>
+  </si>
+  <si>
+    <t>/43550</t>
   </si>
 </sst>
 </file>
@@ -1417,11 +1435,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="145124352"/>
-        <c:axId val="145134336"/>
+        <c:axId val="207515008"/>
+        <c:axId val="207524992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="145124352"/>
+        <c:axId val="207515008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1464,14 +1482,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="145134336"/>
+        <c:crossAx val="207524992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="145134336"/>
+        <c:axId val="207524992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1522,7 +1540,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="145124352"/>
+        <c:crossAx val="207515008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1858,11 +1876,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="146351616"/>
-        <c:axId val="146353152"/>
+        <c:axId val="207882112"/>
+        <c:axId val="207883648"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="146351616"/>
+        <c:axId val="207882112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1905,7 +1923,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="146353152"/>
+        <c:crossAx val="207883648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1913,7 +1931,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="146353152"/>
+        <c:axId val="207883648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1964,7 +1982,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="146351616"/>
+        <c:crossAx val="207882112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2371,7 +2389,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6783,64 +6801,146 @@
         <v>772050</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J40" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
+      <c r="B41" s="10">
+        <v>45710</v>
+      </c>
+      <c r="C41" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D41" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E41" s="11">
+        <v>17300</v>
+      </c>
+      <c r="F41" s="11">
+        <v>844550</v>
+      </c>
+      <c r="G41" s="11">
+        <v>66950</v>
+      </c>
+      <c r="H41" s="11">
+        <v>734900</v>
+      </c>
       <c r="I41" s="16"/>
       <c r="J41" s="14"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="10"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
+      <c r="B42" s="10">
+        <v>45710</v>
+      </c>
+      <c r="C42" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D42" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E42" s="11">
+        <f>17300+4000</f>
+        <v>21300</v>
+      </c>
+      <c r="F42" s="11">
+        <v>834550</v>
+      </c>
+      <c r="G42" s="11">
+        <v>60950</v>
+      </c>
+      <c r="H42" s="11">
+        <v>734900</v>
+      </c>
       <c r="I42" s="16"/>
-      <c r="J42" s="14"/>
+      <c r="J42" s="14" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="10"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
+      <c r="B43" s="10">
+        <v>45710</v>
+      </c>
+      <c r="C43" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D43" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E43" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F43" s="11">
+        <v>836450</v>
+      </c>
+      <c r="G43" s="11">
+        <v>50950</v>
+      </c>
+      <c r="H43" s="11">
+        <v>746800</v>
+      </c>
       <c r="I43" s="16"/>
-      <c r="J43" s="14"/>
+      <c r="J43" s="14" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="10"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="16"/>
+      <c r="B44" s="10">
+        <v>45711</v>
+      </c>
+      <c r="C44" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D44" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E44" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F44" s="11">
+        <v>836450</v>
+      </c>
+      <c r="G44" s="11">
+        <v>53550</v>
+      </c>
+      <c r="H44" s="11">
+        <v>744200</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="10"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="16"/>
+      <c r="B45" s="10">
+        <v>45711</v>
+      </c>
+      <c r="C45" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D45" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E45" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F45" s="11">
+        <v>840450</v>
+      </c>
+      <c r="G45" s="11">
+        <v>33550</v>
+      </c>
+      <c r="H45" s="11">
+        <v>768200</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="10"/>
@@ -6852,7 +6952,61 @@
       <c r="H46" s="11"/>
       <c r="I46" s="16"/>
     </row>
-    <row r="62" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F49" s="3">
+        <f>600+100+1400+500+500+200</f>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="50" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F50" s="3">
+        <f>200+1000</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="51" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F51" s="3">
+        <f>200+500+500+200</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="52" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F52" s="3">
+        <f>100+600+350+800+800+800+2000+1400</f>
+        <v>6850</v>
+      </c>
+    </row>
+    <row r="53" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F53" s="3">
+        <f>400+500+500</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="54" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F54" s="3">
+        <f>100+600+200+500+500</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="55" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F55" s="3">
+        <f>200+700+1200+400+700+8000+2800+500+500+500+2800+2800</f>
+        <v>21100</v>
+      </c>
+    </row>
+    <row r="56" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F56" s="3">
+        <f>2500+100</f>
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="57" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F57" s="3">
+        <f>SUM(F50:F56)</f>
+        <v>36450</v>
+      </c>
+    </row>
+    <row r="62" spans="6:10" x14ac:dyDescent="0.25">
       <c r="J62" s="14"/>
     </row>
   </sheetData>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -650,6 +650,15 @@
   </si>
   <si>
     <t>/43550</t>
+  </si>
+  <si>
+    <t>13800/43550</t>
+  </si>
+  <si>
+    <t>loan bijenti 20000</t>
+  </si>
+  <si>
+    <t>loan 10000 updated to 20000 sheenarani</t>
   </si>
 </sst>
 </file>
@@ -716,7 +725,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -744,6 +753,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF33CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -847,7 +862,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -887,6 +902,15 @@
     <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1435,11 +1459,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="207515008"/>
-        <c:axId val="207524992"/>
+        <c:axId val="195456000"/>
+        <c:axId val="195461888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="207515008"/>
+        <c:axId val="195456000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1482,14 +1506,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="207524992"/>
+        <c:crossAx val="195461888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="207524992"/>
+        <c:axId val="195461888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1540,7 +1564,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="207515008"/>
+        <c:crossAx val="195456000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1660,6 +1684,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1876,11 +1901,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="207882112"/>
-        <c:axId val="207883648"/>
+        <c:axId val="195831296"/>
+        <c:axId val="195832832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="207882112"/>
+        <c:axId val="195831296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1923,7 +1948,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="207883648"/>
+        <c:crossAx val="195832832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1931,7 +1956,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="207883648"/>
+        <c:axId val="195832832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1982,7 +2007,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="207882112"/>
+        <c:crossAx val="195831296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1996,6 +2021,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2389,7 +2415,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5771,7 +5797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K62"/>
+  <dimension ref="B1:K63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -6943,71 +6969,159 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="10"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="16"/>
-    </row>
-    <row r="49" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F49" s="3">
-        <f>600+100+1400+500+500+200</f>
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="50" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F50" s="3">
-        <f>200+1000</f>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="51" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F51" s="3">
-        <f>200+500+500+200</f>
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="52" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F52" s="3">
-        <f>100+600+350+800+800+800+2000+1400</f>
-        <v>6850</v>
-      </c>
-    </row>
-    <row r="53" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F53" s="3">
-        <f>400+500+500</f>
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="54" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F54" s="3">
-        <f>100+600+200+500+500</f>
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="55" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F55" s="3">
-        <f>200+700+1200+400+700+8000+2800+500+500+500+2800+2800</f>
-        <v>21100</v>
-      </c>
-    </row>
-    <row r="56" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F56" s="3">
-        <f>2500+100</f>
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="57" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F57" s="3">
-        <f>SUM(F50:F56)</f>
-        <v>36450</v>
-      </c>
-    </row>
-    <row r="62" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="J62" s="14"/>
+      <c r="B46" s="17">
+        <v>45718</v>
+      </c>
+      <c r="C46" s="18">
+        <v>188380</v>
+      </c>
+      <c r="D46" s="18">
+        <v>60000</v>
+      </c>
+      <c r="E46" s="18">
+        <v>21300</v>
+      </c>
+      <c r="F46" s="18">
+        <v>840450</v>
+      </c>
+      <c r="G46" s="18">
+        <v>47350</v>
+      </c>
+      <c r="H46" s="18">
+        <v>754400</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="10">
+        <v>45719</v>
+      </c>
+      <c r="C47" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D47" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E47" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F47" s="11">
+        <v>840450</v>
+      </c>
+      <c r="G47" s="11">
+        <v>58850</v>
+      </c>
+      <c r="H47" s="11">
+        <v>742900</v>
+      </c>
+      <c r="I47" s="16"/>
+    </row>
+    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="10">
+        <v>45719</v>
+      </c>
+      <c r="C48" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D48" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E48" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F48" s="11">
+        <v>844250</v>
+      </c>
+      <c r="G48" s="11">
+        <v>38850</v>
+      </c>
+      <c r="H48" s="11">
+        <v>766700</v>
+      </c>
+      <c r="I48" s="16"/>
+      <c r="J48" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="10">
+        <v>45724</v>
+      </c>
+      <c r="C49" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D49" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E49" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F49" s="11">
+        <v>844250</v>
+      </c>
+      <c r="G49" s="11">
+        <v>47750</v>
+      </c>
+      <c r="H49" s="11">
+        <v>757800</v>
+      </c>
+      <c r="I49" s="16"/>
+    </row>
+    <row r="50" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="10">
+        <v>45724</v>
+      </c>
+      <c r="C50" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D50" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E50" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F50" s="11">
+        <v>846150</v>
+      </c>
+      <c r="G50" s="11">
+        <v>37750</v>
+      </c>
+      <c r="H50" s="11">
+        <v>769700</v>
+      </c>
+      <c r="I50" s="16"/>
+      <c r="J50" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="10"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="16"/>
+    </row>
+    <row r="52" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="10"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J55" s="15"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J63" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="83">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -659,6 +659,21 @@
   </si>
   <si>
     <t>loan 10000 updated to 20000 sheenarani</t>
+  </si>
+  <si>
+    <t>loan 20000 renita</t>
+  </si>
+  <si>
+    <t>dividend 15000; marup 16500+10000</t>
+  </si>
+  <si>
+    <t>loan minakumari 20000</t>
+  </si>
+  <si>
+    <t>loan 30000 kamala</t>
+  </si>
+  <si>
+    <t>marup6500</t>
   </si>
 </sst>
 </file>
@@ -1459,11 +1474,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="195456000"/>
-        <c:axId val="195461888"/>
+        <c:axId val="144743808"/>
+        <c:axId val="144745600"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="195456000"/>
+        <c:axId val="144743808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1506,14 +1521,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="195461888"/>
+        <c:crossAx val="144745600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="195461888"/>
+        <c:axId val="144745600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1564,7 +1579,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="195456000"/>
+        <c:crossAx val="144743808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1901,11 +1916,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="195831296"/>
-        <c:axId val="195832832"/>
+        <c:axId val="195569536"/>
+        <c:axId val="195571072"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="195831296"/>
+        <c:axId val="195569536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1948,7 +1963,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="195832832"/>
+        <c:crossAx val="195571072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1956,7 +1971,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="195832832"/>
+        <c:axId val="195571072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2007,7 +2022,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="195831296"/>
+        <c:crossAx val="195569536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2415,7 +2430,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5797,7 +5812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K63"/>
+  <dimension ref="B1:K74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -7097,31 +7112,341 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="10"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
+      <c r="B51" s="10">
+        <v>45726</v>
+      </c>
+      <c r="C51" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D51" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E51" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F51" s="11">
+        <v>846150</v>
+      </c>
+      <c r="G51" s="11">
+        <v>60200</v>
+      </c>
+      <c r="H51" s="11">
+        <v>747250</v>
+      </c>
       <c r="I51" s="16"/>
     </row>
-    <row r="52" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="10"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
+    <row r="52" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="10">
+        <v>45726</v>
+      </c>
+      <c r="C52" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D52" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E52" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F52" s="11">
+        <v>850150</v>
+      </c>
+      <c r="G52" s="11">
+        <v>40200</v>
+      </c>
+      <c r="H52" s="11">
+        <v>771250</v>
+      </c>
       <c r="I52" s="16"/>
-      <c r="J52" s="15"/>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J55" s="15"/>
+      <c r="J52" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="10">
+        <v>45740</v>
+      </c>
+      <c r="C53" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D53" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E53" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F53" s="11">
+        <v>850150</v>
+      </c>
+      <c r="G53" s="11">
+        <v>93550</v>
+      </c>
+      <c r="H53" s="11">
+        <v>717900</v>
+      </c>
+      <c r="I53" s="16"/>
+      <c r="J53" s="15"/>
+    </row>
+    <row r="54" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="10">
+        <v>45740</v>
+      </c>
+      <c r="C54" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D54" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E54" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F54" s="11">
+        <v>823650</v>
+      </c>
+      <c r="G54" s="11">
+        <f>G53-26500</f>
+        <v>67050</v>
+      </c>
+      <c r="H54" s="11">
+        <v>717900</v>
+      </c>
+      <c r="I54" s="16"/>
+      <c r="J54" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="10">
+        <v>45740</v>
+      </c>
+      <c r="C55" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D55" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E55" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F55" s="11">
+        <v>827450</v>
+      </c>
+      <c r="G55" s="11">
+        <v>47050</v>
+      </c>
+      <c r="H55" s="11">
+        <v>741700</v>
+      </c>
+      <c r="I55" s="16"/>
+      <c r="J55" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="10">
+        <v>45756</v>
+      </c>
+      <c r="C56" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D56" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E56" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F56" s="11">
+        <v>827450</v>
+      </c>
+      <c r="G56" s="11">
+        <v>94950</v>
+      </c>
+      <c r="H56" s="11">
+        <v>693800</v>
+      </c>
+      <c r="I56" s="16"/>
+      <c r="J56" s="15"/>
+    </row>
+    <row r="57" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="10">
+        <v>45756</v>
+      </c>
+      <c r="C57" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D57" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E57" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F57" s="11">
+        <v>833450</v>
+      </c>
+      <c r="G57" s="11">
+        <v>64950</v>
+      </c>
+      <c r="H57" s="11">
+        <v>729800</v>
+      </c>
+      <c r="I57" s="16"/>
+      <c r="J57" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="10">
+        <v>45758</v>
+      </c>
+      <c r="C58" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D58" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E58" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F58" s="11">
+        <v>833450</v>
+      </c>
+      <c r="G58" s="11">
+        <v>68950</v>
+      </c>
+      <c r="H58" s="11">
+        <v>725800</v>
+      </c>
+      <c r="I58" s="16"/>
+      <c r="J58" s="15"/>
+    </row>
+    <row r="59" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="10">
+        <v>45758</v>
+      </c>
+      <c r="C59" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D59" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E59" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F59" s="11">
+        <v>833450</v>
+      </c>
+      <c r="G59" s="11">
+        <v>62450</v>
+      </c>
+      <c r="H59" s="11">
+        <v>725800</v>
+      </c>
+      <c r="I59" s="16"/>
+      <c r="J59" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="10"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="15"/>
+    </row>
+    <row r="61" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="10"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="15"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J62" s="15"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D64" s="3">
+        <f>G58-6500</f>
+        <v>62450</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G65" s="3">
+        <f>100+200+200+500+1000+500</f>
+        <v>2500</v>
+      </c>
+      <c r="H65" s="3">
+        <f>G65</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G66" s="3">
+        <f>100+200+200+500+500</f>
+        <v>1500</v>
+      </c>
+      <c r="H66" s="3">
+        <f>H65+G66</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H67" s="3">
+        <f>H66+G67</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H68" s="3">
+        <f>H67+G68</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H69" s="3">
+        <f>H68+G69</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H70" s="3">
+        <f>H69+G70</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H71" s="3">
+        <f>H70+G71</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="72" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H72" s="3">
+        <f>H71+G72</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="73" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H73" s="3">
+        <f>H72+G73</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="74" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H74" s="3">
+        <f>H73+G74</f>
+        <v>4000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -674,6 +674,27 @@
   </si>
   <si>
     <t>marup6500</t>
+  </si>
+  <si>
+    <t>kiranmala loan 10000</t>
+  </si>
+  <si>
+    <t>loans dinita 10000; sandhyarani 10000; angom bijenti 50000 ; romial ; 20000</t>
+  </si>
+  <si>
+    <t>marup 108000</t>
+  </si>
+  <si>
+    <t>lukhamlu adjust 100</t>
+  </si>
+  <si>
+    <t>loan thasana 5000 ; lukhamlu 10000</t>
+  </si>
+  <si>
+    <t>loan narmada 20000; indulekha 20000; sweety 20000; inaobi 20000</t>
+  </si>
+  <si>
+    <t>loan naocha 10000; achoubi 10000</t>
   </si>
 </sst>
 </file>
@@ -1474,11 +1495,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="144743808"/>
-        <c:axId val="144745600"/>
+        <c:axId val="142245888"/>
+        <c:axId val="142247424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="144743808"/>
+        <c:axId val="142245888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1521,14 +1542,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="144745600"/>
+        <c:crossAx val="142247424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="144745600"/>
+        <c:axId val="142247424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1579,7 +1600,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="144743808"/>
+        <c:crossAx val="142245888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1699,7 +1720,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1916,11 +1936,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="195569536"/>
-        <c:axId val="195571072"/>
+        <c:axId val="143591680"/>
+        <c:axId val="143601664"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="195569536"/>
+        <c:axId val="143591680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1963,7 +1983,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="195571072"/>
+        <c:crossAx val="143601664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1971,7 +1991,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="195571072"/>
+        <c:axId val="143601664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2022,7 +2042,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="195569536"/>
+        <c:crossAx val="143591680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2036,7 +2056,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2430,7 +2449,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5812,7 +5831,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K74"/>
+  <dimension ref="B1:K78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -7333,7 +7352,7 @@
         <v>21300</v>
       </c>
       <c r="F59" s="11">
-        <v>833450</v>
+        <v>826950</v>
       </c>
       <c r="G59" s="11">
         <v>62450</v>
@@ -7347,106 +7366,381 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="10"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
+      <c r="B60" s="10">
+        <v>45760</v>
+      </c>
+      <c r="C60" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D60" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E60" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F60" s="11">
+        <v>826950</v>
+      </c>
+      <c r="G60" s="11">
+        <v>76050</v>
+      </c>
+      <c r="H60" s="11">
+        <v>712200</v>
+      </c>
       <c r="I60" s="16"/>
       <c r="J60" s="15"/>
     </row>
     <row r="61" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="10"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
+      <c r="B61" s="10">
+        <v>45760</v>
+      </c>
+      <c r="C61" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D61" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E61" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F61" s="11">
+        <v>828950</v>
+      </c>
+      <c r="G61" s="11">
+        <v>66050</v>
+      </c>
+      <c r="H61" s="11">
+        <v>724200</v>
+      </c>
       <c r="I61" s="16"/>
-      <c r="J61" s="15"/>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J61" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="10">
+        <v>45768</v>
+      </c>
+      <c r="C62" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D62" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E62" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F62" s="11">
+        <v>828950</v>
+      </c>
+      <c r="G62" s="11">
+        <v>113700</v>
+      </c>
+      <c r="H62" s="11">
+        <v>676550</v>
+      </c>
+      <c r="I62" s="16"/>
       <c r="J62" s="15"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J63" s="14"/>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D64" s="3">
-        <f>G58-6500</f>
-        <v>62450</v>
-      </c>
-    </row>
-    <row r="65" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G65" s="3">
-        <f>100+200+200+500+1000+500</f>
-        <v>2500</v>
-      </c>
-      <c r="H65" s="3">
-        <f>G65</f>
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="66" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G66" s="3">
-        <f>100+200+200+500+500</f>
-        <v>1500</v>
-      </c>
-      <c r="H66" s="3">
-        <f>H65+G66</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="67" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H67" s="3">
-        <f>H66+G67</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="68" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H68" s="3">
-        <f>H67+G68</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="69" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H69" s="3">
-        <f>H68+G69</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="70" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H70" s="3">
-        <f>H69+G70</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="71" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H71" s="3">
-        <f>H70+G71</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="72" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H72" s="3">
-        <f>H71+G72</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="73" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H73" s="3">
-        <f>H72+G73</f>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="74" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="H74" s="3">
-        <f>H73+G74</f>
-        <v>4000</v>
-      </c>
+    <row r="63" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="10">
+        <v>45768</v>
+      </c>
+      <c r="C63" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D63" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E63" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F63" s="11">
+        <v>846950</v>
+      </c>
+      <c r="G63" s="11">
+        <v>23700</v>
+      </c>
+      <c r="H63" s="11">
+        <v>784550</v>
+      </c>
+      <c r="I63" s="16"/>
+      <c r="J63" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="10">
+        <v>45768</v>
+      </c>
+      <c r="C64" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D64" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E64" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F64" s="11">
+        <v>954950</v>
+      </c>
+      <c r="G64" s="11">
+        <v>131700</v>
+      </c>
+      <c r="H64" s="11">
+        <v>784550</v>
+      </c>
+      <c r="I64" s="16"/>
+      <c r="J64" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="10">
+        <v>45770</v>
+      </c>
+      <c r="C65" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D65" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E65" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F65" s="11">
+        <v>954850</v>
+      </c>
+      <c r="G65" s="11">
+        <v>136800</v>
+      </c>
+      <c r="H65" s="11">
+        <v>779350</v>
+      </c>
+      <c r="I65" s="16"/>
+      <c r="J65" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="10">
+        <v>45770</v>
+      </c>
+      <c r="C66" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D66" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E66" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F66" s="11">
+        <v>957700</v>
+      </c>
+      <c r="G66" s="11">
+        <v>121800</v>
+      </c>
+      <c r="H66" s="11">
+        <v>797200</v>
+      </c>
+      <c r="I66" s="16"/>
+      <c r="J66" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="10">
+        <v>45772</v>
+      </c>
+      <c r="C67" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D67" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E67" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F67" s="11">
+        <v>957700</v>
+      </c>
+      <c r="G67" s="11">
+        <v>145450</v>
+      </c>
+      <c r="H67" s="11">
+        <v>773550</v>
+      </c>
+      <c r="I67" s="16"/>
+      <c r="J67" s="15"/>
+    </row>
+    <row r="68" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="10">
+        <v>45772</v>
+      </c>
+      <c r="C68" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D68" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E68" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F68" s="11">
+        <v>973100</v>
+      </c>
+      <c r="G68" s="11">
+        <v>65450</v>
+      </c>
+      <c r="H68" s="11">
+        <v>868950</v>
+      </c>
+      <c r="I68" s="16"/>
+      <c r="J68" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="10">
+        <v>45777</v>
+      </c>
+      <c r="C69" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D69" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E69" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F69" s="11">
+        <v>973100</v>
+      </c>
+      <c r="G69" s="11">
+        <v>82250</v>
+      </c>
+      <c r="H69" s="11">
+        <v>852150</v>
+      </c>
+      <c r="I69" s="16"/>
+      <c r="J69" s="15"/>
+    </row>
+    <row r="70" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="10">
+        <v>45777</v>
+      </c>
+      <c r="C70" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D70" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E70" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F70" s="11">
+        <v>976900</v>
+      </c>
+      <c r="G70" s="11">
+        <v>62250</v>
+      </c>
+      <c r="H70" s="11">
+        <v>875950</v>
+      </c>
+      <c r="I70" s="16"/>
+      <c r="J70" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="10"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="10"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="15"/>
+    </row>
+    <row r="73" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="10"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="15"/>
+    </row>
+    <row r="74" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="10"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="15"/>
+    </row>
+    <row r="75" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="10"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="15"/>
+    </row>
+    <row r="76" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="10"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="15"/>
+    </row>
+    <row r="77" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="10"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="15"/>
+    </row>
+    <row r="78" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="10"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -695,6 +695,9 @@
   </si>
   <si>
     <t>loan naocha 10000; achoubi 10000</t>
+  </si>
+  <si>
+    <t>bidyapati loan 20000</t>
   </si>
 </sst>
 </file>
@@ -1495,11 +1498,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="142245888"/>
-        <c:axId val="142247424"/>
+        <c:axId val="153460736"/>
+        <c:axId val="153462272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="142245888"/>
+        <c:axId val="153460736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1542,14 +1545,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="142247424"/>
+        <c:crossAx val="153462272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="142247424"/>
+        <c:axId val="153462272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1600,7 +1603,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="142245888"/>
+        <c:crossAx val="153460736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1936,11 +1939,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="143591680"/>
-        <c:axId val="143601664"/>
+        <c:axId val="153757952"/>
+        <c:axId val="153759744"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="143591680"/>
+        <c:axId val="153757952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1983,7 +1986,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143601664"/>
+        <c:crossAx val="153759744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1991,7 +1994,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="143601664"/>
+        <c:axId val="153759744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2042,7 +2045,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143591680"/>
+        <c:crossAx val="153757952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2449,7 +2452,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7655,48 +7658,108 @@
       </c>
     </row>
     <row r="71" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="10"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
+      <c r="B71" s="10">
+        <v>45779</v>
+      </c>
+      <c r="C71" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D71" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E71" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F71" s="11">
+        <v>976900</v>
+      </c>
+      <c r="G71" s="11">
+        <v>71050</v>
+      </c>
+      <c r="H71" s="11">
+        <v>867150</v>
+      </c>
       <c r="I71" s="16"/>
       <c r="J71" s="15"/>
     </row>
     <row r="72" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="10"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
+      <c r="B72" s="10">
+        <v>45779</v>
+      </c>
+      <c r="C72" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D72" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E72" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F72" s="11">
+        <v>980700</v>
+      </c>
+      <c r="G72" s="11">
+        <v>51050</v>
+      </c>
+      <c r="H72" s="11">
+        <v>890950</v>
+      </c>
       <c r="I72" s="16"/>
-      <c r="J72" s="15"/>
+      <c r="J72" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="73" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="10"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
+      <c r="B73" s="10">
+        <v>45792</v>
+      </c>
+      <c r="C73" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D73" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E73" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F73" s="11">
+        <v>980700</v>
+      </c>
+      <c r="G73" s="11">
+        <v>94350</v>
+      </c>
+      <c r="H73" s="11">
+        <v>847650</v>
+      </c>
       <c r="I73" s="16"/>
       <c r="J73" s="15"/>
     </row>
     <row r="74" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="10"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
+      <c r="B74" s="10">
+        <v>45792</v>
+      </c>
+      <c r="C74" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D74" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E74" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F74" s="11">
+        <v>974200</v>
+      </c>
+      <c r="G74" s="11">
+        <v>87850</v>
+      </c>
+      <c r="H74" s="11">
+        <v>847650</v>
+      </c>
       <c r="I74" s="16"/>
-      <c r="J74" s="15"/>
+      <c r="J74" s="15" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="75" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="10"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -698,6 +698,12 @@
   </si>
   <si>
     <t>bidyapati loan 20000</t>
+  </si>
+  <si>
+    <t>marup 6000</t>
+  </si>
+  <si>
+    <t>loan dhanabir 10000, budhachandra 10000, jemeson 10000</t>
   </si>
 </sst>
 </file>
@@ -1498,11 +1504,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="153460736"/>
-        <c:axId val="153462272"/>
+        <c:axId val="197165056"/>
+        <c:axId val="197166592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="153460736"/>
+        <c:axId val="197165056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1545,14 +1551,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153462272"/>
+        <c:crossAx val="197166592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="153462272"/>
+        <c:axId val="197166592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1603,7 +1609,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153460736"/>
+        <c:crossAx val="197165056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1723,6 +1729,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1939,11 +1946,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="153757952"/>
-        <c:axId val="153759744"/>
+        <c:axId val="197658880"/>
+        <c:axId val="197668864"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="153757952"/>
+        <c:axId val="197658880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1986,7 +1993,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153759744"/>
+        <c:crossAx val="197668864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1994,7 +2001,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="153759744"/>
+        <c:axId val="197668864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2045,7 +2052,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153757952"/>
+        <c:crossAx val="197658880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2059,6 +2066,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2452,7 +2460,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5840,7 +5848,7 @@
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" style="2" customWidth="1"/>
     <col min="3" max="5" width="15" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.85546875" style="3" customWidth="1"/>
     <col min="8" max="9" width="19.140625" style="3" customWidth="1"/>
     <col min="10" max="10" width="25.28515625" style="2" customWidth="1"/>
@@ -7762,37 +7770,85 @@
       </c>
     </row>
     <row r="75" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="10"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
+      <c r="B75" s="10">
+        <v>45803</v>
+      </c>
+      <c r="C75" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D75" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E75" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F75" s="11">
+        <v>974200</v>
+      </c>
+      <c r="G75" s="11">
+        <v>132750</v>
+      </c>
+      <c r="H75" s="11">
+        <v>802750</v>
+      </c>
       <c r="I75" s="16"/>
       <c r="J75" s="15"/>
     </row>
     <row r="76" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="10"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
+      <c r="B76" s="10">
+        <v>45803</v>
+      </c>
+      <c r="C76" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D76" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E76" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F76" s="11">
+        <f>H76+G76+D76-E76</f>
+        <v>968200</v>
+      </c>
+      <c r="G76" s="11">
+        <v>126750</v>
+      </c>
+      <c r="H76" s="11">
+        <v>802750</v>
+      </c>
       <c r="I76" s="16"/>
-      <c r="J76" s="15"/>
+      <c r="J76" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="77" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="10"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
+      <c r="B77" s="10">
+        <v>45803</v>
+      </c>
+      <c r="C77" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D77" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E77" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F77" s="11">
+        <f>H77+G77+D77-E77</f>
+        <v>973900</v>
+      </c>
+      <c r="G77" s="11">
+        <v>96750</v>
+      </c>
+      <c r="H77" s="11">
+        <v>838450</v>
+      </c>
       <c r="I77" s="16"/>
-      <c r="J77" s="15"/>
+      <c r="J77" s="15" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="78" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="10"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="1"/>
   </bookViews>
@@ -10,7 +10,7 @@
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
     <sheet name="2025TrendAnalysis" sheetId="16" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -20,7 +20,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F140" authorId="0">
+    <comment ref="F140" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -49,7 +49,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F141" authorId="0">
+    <comment ref="F141" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F142" authorId="0">
+    <comment ref="F142" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F143" authorId="0">
+    <comment ref="F143" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E144" authorId="0">
+    <comment ref="E144" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -167,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F144" authorId="0">
+    <comment ref="F144" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -201,7 +201,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F17" authorId="0">
+    <comment ref="F17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -230,7 +230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0">
+    <comment ref="F18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -259,7 +259,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F19" authorId="0">
+    <comment ref="F19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -288,7 +288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="0">
+    <comment ref="F20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -317,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0">
+    <comment ref="E21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -348,7 +348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0">
+    <comment ref="F21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -372,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0">
+    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -396,7 +396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0">
+    <comment ref="F23" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="96">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -704,12 +704,21 @@
   </si>
   <si>
     <t>loan dhanabir 10000, budhachandra 10000, jemeson 10000</t>
+  </si>
+  <si>
+    <t>loan bijenty 20000, sheenarani 20000</t>
+  </si>
+  <si>
+    <t>mona 1800 writeoff</t>
+  </si>
+  <si>
+    <t>marup 16500+11000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
@@ -987,7 +996,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1149,7 +1158,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1263,7 +1272,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1374,7 +1383,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1488,7 +1497,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1502,7 +1511,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="197165056"/>
         <c:axId val="197166592"/>
@@ -1690,7 +1698,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1729,7 +1737,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1771,11 +1778,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:multiLvlStrRef>
-          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'2025TrendAnalysis'!$C$3:$C$3</c:f>
@@ -1789,7 +1791,22 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredCategoryTitle>
+                <c15:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'2025TrendAnalysis'!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:multiLvlStrRef>
+                </c15:cat>
+              </c15:filteredCategoryTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1821,11 +1838,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:multiLvlStrRef>
-          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'2025TrendAnalysis'!$F$3:$F$3</c:f>
@@ -1836,7 +1848,22 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredCategoryTitle>
+                <c15:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'2025TrendAnalysis'!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:multiLvlStrRef>
+                </c15:cat>
+              </c15:filteredCategoryTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1868,11 +1895,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:multiLvlStrRef>
-          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'2025TrendAnalysis'!$G$3:$G$3</c:f>
@@ -1883,7 +1905,22 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredCategoryTitle>
+                <c15:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'2025TrendAnalysis'!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:multiLvlStrRef>
+                </c15:cat>
+              </c15:filteredCategoryTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1915,11 +1952,6 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'2025TrendAnalysis'!#REF!</c:f>
-            </c:multiLvlStrRef>
-          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'2025TrendAnalysis'!$H$3:$H$3</c:f>
@@ -1930,7 +1962,22 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredCategoryTitle>
+                <c15:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'2025TrendAnalysis'!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:multiLvlStrRef>
+                </c15:cat>
+              </c15:filteredCategoryTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-588A-4FD6-90A1-C2BC5C3DF530}"/>
             </c:ext>
@@ -1944,7 +1991,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="197658880"/>
         <c:axId val="197668864"/>
@@ -2066,7 +2112,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2248,7 +2293,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2283,7 +2328,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2460,7 +2505,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5842,7 +5887,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K78"/>
+  <dimension ref="B1:K92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -7851,15 +7896,307 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="10"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
+      <c r="B78" s="10">
+        <v>45810</v>
+      </c>
+      <c r="C78" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D78" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E78" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F78" s="11">
+        <f>H78+G78+D78-E78</f>
+        <v>973900</v>
+      </c>
+      <c r="G78" s="11">
+        <v>137900</v>
+      </c>
+      <c r="H78" s="11">
+        <v>797300</v>
+      </c>
       <c r="I78" s="16"/>
       <c r="J78" s="15"/>
+    </row>
+    <row r="79" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="10">
+        <v>45810</v>
+      </c>
+      <c r="C79" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D79" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E79" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F79" s="11">
+        <v>981500</v>
+      </c>
+      <c r="G79" s="11">
+        <v>97900</v>
+      </c>
+      <c r="H79" s="11">
+        <v>844900</v>
+      </c>
+      <c r="I79" s="16"/>
+      <c r="J79" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="10">
+        <v>45810</v>
+      </c>
+      <c r="C80" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D80" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E80" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F80" s="11">
+        <f>H80+G80+D80-E80</f>
+        <v>979700</v>
+      </c>
+      <c r="G80" s="11">
+        <v>97900</v>
+      </c>
+      <c r="H80" s="11">
+        <v>843100</v>
+      </c>
+      <c r="I80" s="16"/>
+      <c r="J80" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="10">
+        <v>45831</v>
+      </c>
+      <c r="C81" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D81" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E81" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F81" s="11">
+        <f>H81+G81+D81-E81</f>
+        <v>979700</v>
+      </c>
+      <c r="G81" s="11">
+        <v>153250</v>
+      </c>
+      <c r="H81" s="11">
+        <v>787750</v>
+      </c>
+      <c r="I81" s="16"/>
+      <c r="J81" s="15"/>
+    </row>
+    <row r="82" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="10">
+        <v>45831</v>
+      </c>
+      <c r="C82" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D82" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E82" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F82" s="11">
+        <f>H82+G82+D82-E82</f>
+        <v>952200</v>
+      </c>
+      <c r="G82" s="11">
+        <v>125750</v>
+      </c>
+      <c r="H82" s="11">
+        <v>787750</v>
+      </c>
+      <c r="I82" s="16"/>
+      <c r="J82" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="10">
+        <v>45831</v>
+      </c>
+      <c r="C83" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D83" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E83" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F83" s="11">
+        <v>956200</v>
+      </c>
+      <c r="G83" s="11">
+        <v>105750</v>
+      </c>
+      <c r="H83" s="11">
+        <v>811750</v>
+      </c>
+      <c r="I83" s="16"/>
+      <c r="J83" s="15"/>
+    </row>
+    <row r="84" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="10">
+        <v>45840</v>
+      </c>
+      <c r="C84" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D84" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E84" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F84" s="11">
+        <v>956200</v>
+      </c>
+      <c r="G84" s="11">
+        <v>133500</v>
+      </c>
+      <c r="H84" s="11">
+        <v>784000</v>
+      </c>
+      <c r="I84" s="16"/>
+      <c r="J84" s="15"/>
+    </row>
+    <row r="85" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="10">
+        <v>45840</v>
+      </c>
+      <c r="C85" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D85" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E85" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F85" s="11">
+        <v>960200</v>
+      </c>
+      <c r="G85" s="11">
+        <v>113500</v>
+      </c>
+      <c r="H85" s="11">
+        <v>808000</v>
+      </c>
+      <c r="I85" s="16"/>
+      <c r="J85" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="10">
+        <v>45842</v>
+      </c>
+      <c r="C86" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D86" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E86" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F86" s="11">
+        <v>960200</v>
+      </c>
+      <c r="G86" s="11">
+        <v>114150</v>
+      </c>
+      <c r="H86" s="11">
+        <v>807350</v>
+      </c>
+      <c r="I86" s="16"/>
+      <c r="J86" s="15"/>
+    </row>
+    <row r="87" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="10"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="16"/>
+      <c r="J87" s="15"/>
+    </row>
+    <row r="88" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="10"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="16"/>
+      <c r="J88" s="15"/>
+    </row>
+    <row r="89" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="10"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="15"/>
+    </row>
+    <row r="90" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="10"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="16"/>
+      <c r="J90" s="15"/>
+    </row>
+    <row r="91" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="10"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="15"/>
+    </row>
+    <row r="92" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="10"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="99">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -713,6 +713,15 @@
   </si>
   <si>
     <t>marup 16500+11000</t>
+  </si>
+  <si>
+    <t>loan ibeyaima 20000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">priya loan 50000 </t>
+  </si>
+  <si>
+    <t>6500 marup</t>
   </si>
 </sst>
 </file>
@@ -8133,59 +8142,135 @@
       <c r="J86" s="15"/>
     </row>
     <row r="87" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="10"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="11"/>
+      <c r="B87" s="10">
+        <v>45847</v>
+      </c>
+      <c r="C87" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D87" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E87" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F87" s="11">
+        <v>960200</v>
+      </c>
+      <c r="G87" s="11">
+        <v>137650</v>
+      </c>
+      <c r="H87" s="11">
+        <v>783850</v>
+      </c>
       <c r="I87" s="16"/>
       <c r="J87" s="15"/>
     </row>
     <row r="88" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="10"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11"/>
-      <c r="H88" s="11"/>
+      <c r="B88" s="10">
+        <v>45847</v>
+      </c>
+      <c r="C88" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D88" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E88" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F88" s="11">
+        <v>964000</v>
+      </c>
+      <c r="G88" s="11">
+        <v>117650</v>
+      </c>
+      <c r="H88" s="11">
+        <v>807650</v>
+      </c>
       <c r="I88" s="16"/>
-      <c r="J88" s="15"/>
+      <c r="J88" s="15" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="89" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="10"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="11"/>
+      <c r="B89" s="10">
+        <v>45851</v>
+      </c>
+      <c r="C89" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D89" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E89" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F89" s="11">
+        <v>964000</v>
+      </c>
+      <c r="G89" s="11">
+        <v>163500</v>
+      </c>
+      <c r="H89" s="11">
+        <v>761800</v>
+      </c>
       <c r="I89" s="16"/>
       <c r="J89" s="15"/>
     </row>
     <row r="90" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="10"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="11"/>
+      <c r="B90" s="10">
+        <v>45851</v>
+      </c>
+      <c r="C90" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D90" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E90" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F90" s="11">
+        <v>994000</v>
+      </c>
+      <c r="G90" s="11">
+        <v>113500</v>
+      </c>
+      <c r="H90" s="11">
+        <v>841800</v>
+      </c>
       <c r="I90" s="16"/>
-      <c r="J90" s="15"/>
+      <c r="J90" s="15" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="91" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="10"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="11"/>
+      <c r="B91" s="10">
+        <v>45851</v>
+      </c>
+      <c r="C91" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D91" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E91" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F91" s="11">
+        <v>987500</v>
+      </c>
+      <c r="G91" s="11">
+        <v>107000</v>
+      </c>
+      <c r="H91" s="11">
+        <v>841800</v>
+      </c>
       <c r="I91" s="16"/>
-      <c r="J91" s="15"/>
+      <c r="J91" s="15" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="92" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="10"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -722,6 +722,9 @@
   </si>
   <si>
     <t>6500 marup</t>
+  </si>
+  <si>
+    <t>loan pratima 10000</t>
   </si>
 </sst>
 </file>
@@ -788,7 +791,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -816,12 +819,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF33CCCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -925,7 +922,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -967,13 +964,7 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1746,6 +1737,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2121,6 +2113,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5896,7 +5889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K92"/>
+  <dimension ref="B1:K97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -7068,28 +7061,28 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="17">
+      <c r="B46" s="10">
         <v>45718</v>
       </c>
-      <c r="C46" s="18">
-        <v>188380</v>
-      </c>
-      <c r="D46" s="18">
-        <v>60000</v>
-      </c>
-      <c r="E46" s="18">
+      <c r="C46" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D46" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E46" s="11">
         <v>21300</v>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="11">
         <v>840450</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="11">
         <v>47350</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="11">
         <v>754400</v>
       </c>
-      <c r="I46" s="19" t="s">
+      <c r="I46" s="16" t="s">
         <v>75</v>
       </c>
     </row>
@@ -8245,7 +8238,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="10">
         <v>45851</v>
       </c>
@@ -8261,7 +8254,7 @@
       <c r="F91" s="11">
         <v>987500</v>
       </c>
-      <c r="G91" s="11">
+      <c r="G91" s="17">
         <v>107000</v>
       </c>
       <c r="H91" s="11">
@@ -8272,16 +8265,148 @@
         <v>98</v>
       </c>
     </row>
-    <row r="92" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="10"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="11"/>
+    <row r="92" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="10">
+        <v>45859</v>
+      </c>
+      <c r="C92" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D92" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E92" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F92" s="11">
+        <v>987500</v>
+      </c>
+      <c r="G92" s="17">
+        <v>127700</v>
+      </c>
+      <c r="H92" s="11">
+        <v>821100</v>
+      </c>
       <c r="I92" s="16"/>
       <c r="J92" s="15"/>
+    </row>
+    <row r="93" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="10">
+        <v>45859</v>
+      </c>
+      <c r="C93" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D93" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E93" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F93" s="11">
+        <f>987500-6000</f>
+        <v>981500</v>
+      </c>
+      <c r="G93" s="17">
+        <v>121700</v>
+      </c>
+      <c r="H93" s="11">
+        <v>821100</v>
+      </c>
+      <c r="I93" s="16"/>
+      <c r="J93" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="10">
+        <v>45859</v>
+      </c>
+      <c r="C94" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D94" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E94" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F94" s="11">
+        <v>983500</v>
+      </c>
+      <c r="G94" s="17">
+        <v>111700</v>
+      </c>
+      <c r="H94" s="11">
+        <v>833100</v>
+      </c>
+      <c r="I94" s="16"/>
+      <c r="J94" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="10">
+        <v>45864</v>
+      </c>
+      <c r="C95" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D95" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E95" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F95" s="11">
+        <v>983800</v>
+      </c>
+      <c r="G95" s="17">
+        <v>137850</v>
+      </c>
+      <c r="H95" s="11">
+        <v>807250</v>
+      </c>
+      <c r="I95" s="16"/>
+      <c r="J95" s="15"/>
+    </row>
+    <row r="96" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="10">
+        <v>45864</v>
+      </c>
+      <c r="C96" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D96" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E96" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F96" s="11">
+        <v>987600</v>
+      </c>
+      <c r="G96" s="11">
+        <v>117850</v>
+      </c>
+      <c r="H96" s="11">
+        <v>831050</v>
+      </c>
+      <c r="I96" s="16"/>
+      <c r="J96" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="10"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="16"/>
+      <c r="J97" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -725,6 +725,15 @@
   </si>
   <si>
     <t>loan pratima 10000</t>
+  </si>
+  <si>
+    <t>loan kamala 40000</t>
+  </si>
+  <si>
+    <t>loan renita 15000</t>
+  </si>
+  <si>
+    <t>loan kiranmala 10000, dinita 10000 , sandhyarani 10000</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1746,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2113,7 +2121,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5889,7 +5896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K97"/>
+  <dimension ref="B1:K109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -8370,7 +8377,7 @@
       <c r="I95" s="16"/>
       <c r="J95" s="15"/>
     </row>
-    <row r="96" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="10">
         <v>45864</v>
       </c>
@@ -8398,15 +8405,251 @@
       </c>
     </row>
     <row r="97" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="10"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
-      <c r="H97" s="11"/>
+      <c r="B97" s="10">
+        <v>45875</v>
+      </c>
+      <c r="C97" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D97" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E97" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F97" s="11">
+        <v>987600</v>
+      </c>
+      <c r="G97" s="17">
+        <v>150750</v>
+      </c>
+      <c r="H97" s="11">
+        <v>798150</v>
+      </c>
       <c r="I97" s="16"/>
       <c r="J97" s="15"/>
+    </row>
+    <row r="98" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="10">
+        <v>45875</v>
+      </c>
+      <c r="C98" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D98" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E98" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F98" s="11">
+        <v>995600</v>
+      </c>
+      <c r="G98" s="17">
+        <v>110750</v>
+      </c>
+      <c r="H98" s="11">
+        <v>846150</v>
+      </c>
+      <c r="I98" s="16"/>
+      <c r="J98" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="10">
+        <v>45879</v>
+      </c>
+      <c r="C99" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D99" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E99" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F99" s="11">
+        <v>995600</v>
+      </c>
+      <c r="G99" s="17">
+        <v>138600</v>
+      </c>
+      <c r="H99" s="11">
+        <v>818300</v>
+      </c>
+      <c r="I99" s="16"/>
+      <c r="J99" s="15"/>
+    </row>
+    <row r="100" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="10">
+        <v>45879</v>
+      </c>
+      <c r="C100" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D100" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E100" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F100" s="11">
+        <v>998600</v>
+      </c>
+      <c r="G100" s="11">
+        <v>123600</v>
+      </c>
+      <c r="H100" s="11">
+        <v>836300</v>
+      </c>
+      <c r="I100" s="16"/>
+      <c r="J100" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="10">
+        <v>45880</v>
+      </c>
+      <c r="C101" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D101" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E101" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F101" s="11">
+        <v>998600</v>
+      </c>
+      <c r="G101" s="11">
+        <v>150750</v>
+      </c>
+      <c r="H101" s="11">
+        <v>809150</v>
+      </c>
+      <c r="I101" s="16"/>
+      <c r="J101" s="15"/>
+    </row>
+    <row r="102" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="10">
+        <v>45880</v>
+      </c>
+      <c r="C102" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D102" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E102" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F102" s="11">
+        <v>1004600</v>
+      </c>
+      <c r="G102" s="11">
+        <v>120750</v>
+      </c>
+      <c r="H102" s="11">
+        <v>845150</v>
+      </c>
+      <c r="I102" s="16"/>
+      <c r="J102" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="10">
+        <v>45883</v>
+      </c>
+      <c r="C103" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D103" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E103" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F103" s="11">
+        <v>1004600</v>
+      </c>
+      <c r="G103" s="11">
+        <v>126700</v>
+      </c>
+      <c r="H103" s="11">
+        <v>839200</v>
+      </c>
+      <c r="I103" s="16"/>
+      <c r="J103" s="15"/>
+    </row>
+    <row r="104" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="10"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="11"/>
+      <c r="G104" s="11"/>
+      <c r="H104" s="11"/>
+      <c r="I104" s="16"/>
+      <c r="J104" s="15"/>
+    </row>
+    <row r="105" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="10"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="11"/>
+      <c r="H105" s="11"/>
+      <c r="I105" s="16"/>
+      <c r="J105" s="15"/>
+    </row>
+    <row r="106" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="10"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
+      <c r="H106" s="11"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="15"/>
+    </row>
+    <row r="107" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="10"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="11"/>
+      <c r="I107" s="16"/>
+      <c r="J107" s="15"/>
+    </row>
+    <row r="108" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="10"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="11"/>
+      <c r="I108" s="16"/>
+      <c r="J108" s="15"/>
+    </row>
+    <row r="109" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="10"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="11"/>
+      <c r="I109" s="16"/>
+      <c r="J109" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="106">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -734,6 +734,15 @@
   </si>
   <si>
     <t>loan kiranmala 10000, dinita 10000 , sandhyarani 10000</t>
+  </si>
+  <si>
+    <t>bomcha 6500, wangkhei 6000</t>
+  </si>
+  <si>
+    <t>loan achoubi 20000, naocha 10000</t>
+  </si>
+  <si>
+    <t>loan thasana 5000</t>
   </si>
 </sst>
 </file>
@@ -5896,7 +5905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K109"/>
+  <dimension ref="B1:K121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -8586,70 +8595,292 @@
       <c r="J103" s="15"/>
     </row>
     <row r="104" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="10"/>
-      <c r="C104" s="11"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="11"/>
-      <c r="G104" s="11"/>
-      <c r="H104" s="11"/>
+      <c r="B104" s="10">
+        <v>45894</v>
+      </c>
+      <c r="C104" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D104" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E104" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F104" s="11">
+        <v>1004600</v>
+      </c>
+      <c r="G104" s="11">
+        <v>176250</v>
+      </c>
+      <c r="H104" s="11">
+        <v>789650</v>
+      </c>
       <c r="I104" s="16"/>
       <c r="J104" s="15"/>
     </row>
     <row r="105" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="10"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="11"/>
+      <c r="B105" s="10">
+        <v>45894</v>
+      </c>
+      <c r="C105" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D105" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E105" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F105" s="11">
+        <v>1004600</v>
+      </c>
+      <c r="G105" s="11">
+        <v>176250</v>
+      </c>
+      <c r="H105" s="11">
+        <v>789650</v>
+      </c>
       <c r="I105" s="16"/>
-      <c r="J105" s="15"/>
+      <c r="J105" s="15" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="106" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="10"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="11"/>
-      <c r="G106" s="11"/>
-      <c r="H106" s="11"/>
+      <c r="B106" s="10">
+        <v>45894</v>
+      </c>
+      <c r="C106" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D106" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E106" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F106" s="11">
+        <v>992100</v>
+      </c>
+      <c r="G106" s="11">
+        <v>163750</v>
+      </c>
+      <c r="H106" s="11">
+        <v>789650</v>
+      </c>
       <c r="I106" s="16"/>
       <c r="J106" s="15"/>
     </row>
     <row r="107" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="10"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="11"/>
-      <c r="H107" s="11"/>
+      <c r="B107" s="10">
+        <v>45894</v>
+      </c>
+      <c r="C107" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D107" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E107" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F107" s="11">
+        <v>997800</v>
+      </c>
+      <c r="G107" s="11">
+        <v>133750</v>
+      </c>
+      <c r="H107" s="11">
+        <v>825350</v>
+      </c>
       <c r="I107" s="16"/>
-      <c r="J107" s="15"/>
+      <c r="J107" s="15" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="108" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="10"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="11"/>
+      <c r="B108" s="10">
+        <v>45898</v>
+      </c>
+      <c r="C108" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D108" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E108" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F108" s="11">
+        <v>997800</v>
+      </c>
+      <c r="G108" s="11">
+        <v>141650</v>
+      </c>
+      <c r="H108" s="11">
+        <v>817450</v>
+      </c>
       <c r="I108" s="16"/>
       <c r="J108" s="15"/>
     </row>
     <row r="109" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="10"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="11"/>
+      <c r="B109" s="10">
+        <v>45898</v>
+      </c>
+      <c r="C109" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D109" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E109" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F109" s="11">
+        <v>998750</v>
+      </c>
+      <c r="G109" s="11">
+        <v>136650</v>
+      </c>
+      <c r="H109" s="11">
+        <v>823400</v>
+      </c>
       <c r="I109" s="16"/>
-      <c r="J109" s="15"/>
+      <c r="J109" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="10"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="11"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="11"/>
+      <c r="I110" s="16"/>
+      <c r="J110" s="15"/>
+    </row>
+    <row r="111" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="10"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="16"/>
+      <c r="J111" s="15"/>
+    </row>
+    <row r="112" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="10"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="11"/>
+      <c r="H112" s="11"/>
+      <c r="I112" s="16"/>
+      <c r="J112" s="15"/>
+    </row>
+    <row r="113" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="10"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
+      <c r="F113" s="11"/>
+      <c r="G113" s="11"/>
+      <c r="H113" s="11"/>
+      <c r="I113" s="16"/>
+      <c r="J113" s="15"/>
+    </row>
+    <row r="114" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="10"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="11"/>
+      <c r="H114" s="11"/>
+      <c r="I114" s="16"/>
+      <c r="J114" s="15"/>
+    </row>
+    <row r="115" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="10"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
+      <c r="F115" s="11"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="11"/>
+      <c r="I115" s="16"/>
+      <c r="J115" s="15"/>
+    </row>
+    <row r="116" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="10"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="16"/>
+      <c r="J116" s="15"/>
+    </row>
+    <row r="117" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="10"/>
+      <c r="C117" s="11"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
+      <c r="F117" s="11"/>
+      <c r="G117" s="11"/>
+      <c r="H117" s="11"/>
+      <c r="I117" s="16"/>
+      <c r="J117" s="15"/>
+    </row>
+    <row r="118" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="10"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
+      <c r="F118" s="11"/>
+      <c r="G118" s="11"/>
+      <c r="H118" s="11"/>
+      <c r="I118" s="16"/>
+      <c r="J118" s="15"/>
+    </row>
+    <row r="119" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="10"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="11"/>
+      <c r="H119" s="11"/>
+      <c r="I119" s="16"/>
+      <c r="J119" s="15"/>
+    </row>
+    <row r="120" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="10"/>
+      <c r="C120" s="11"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="11"/>
+      <c r="H120" s="11"/>
+      <c r="I120" s="16"/>
+      <c r="J120" s="15"/>
+    </row>
+    <row r="121" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="10"/>
+      <c r="C121" s="11"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
+      <c r="F121" s="11"/>
+      <c r="G121" s="11"/>
+      <c r="H121" s="11"/>
+      <c r="I121" s="16"/>
+      <c r="J121" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="112">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -743,6 +743,24 @@
   </si>
   <si>
     <t>loan thasana 5000</t>
+  </si>
+  <si>
+    <t>loan thasana added 5000</t>
+  </si>
+  <si>
+    <t>loan indulekha 20000</t>
+  </si>
+  <si>
+    <t>loan sweety 20000</t>
+  </si>
+  <si>
+    <t>loan bidyapati 10000</t>
+  </si>
+  <si>
+    <t>marup 6000+6500+500floodcharity</t>
+  </si>
+  <si>
+    <t>narmada loan 20000</t>
   </si>
 </sst>
 </file>
@@ -8751,125 +8769,290 @@
       </c>
     </row>
     <row r="110" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="10"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
-      <c r="G110" s="11"/>
-      <c r="H110" s="11"/>
+      <c r="B110" s="10">
+        <v>45901</v>
+      </c>
+      <c r="C110" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D110" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E110" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F110" s="11">
+        <v>998750</v>
+      </c>
+      <c r="G110" s="11">
+        <v>139950</v>
+      </c>
+      <c r="H110" s="11">
+        <v>820100</v>
+      </c>
       <c r="I110" s="16"/>
       <c r="J110" s="15"/>
     </row>
     <row r="111" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="10"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="11"/>
-      <c r="H111" s="11"/>
+      <c r="B111" s="10">
+        <v>45901</v>
+      </c>
+      <c r="C111" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D111" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E111" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F111" s="11">
+        <v>999700</v>
+      </c>
+      <c r="G111" s="11">
+        <v>134950</v>
+      </c>
+      <c r="H111" s="11">
+        <v>826050</v>
+      </c>
       <c r="I111" s="16"/>
-      <c r="J111" s="15"/>
+      <c r="J111" s="15" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="112" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="10"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="11"/>
-      <c r="G112" s="11"/>
-      <c r="H112" s="11"/>
+      <c r="B112" s="10">
+        <v>45901</v>
+      </c>
+      <c r="C112" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D112" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E112" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F112" s="11">
+        <v>999700</v>
+      </c>
+      <c r="G112" s="11">
+        <v>155150</v>
+      </c>
+      <c r="H112" s="11">
+        <v>805850</v>
+      </c>
       <c r="I112" s="16"/>
-      <c r="J112" s="15"/>
     </row>
     <row r="113" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="10"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="11"/>
-      <c r="G113" s="11"/>
-      <c r="H113" s="11"/>
+      <c r="B113" s="10">
+        <v>45901</v>
+      </c>
+      <c r="C113" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D113" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E113" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F113" s="11">
+        <v>1003500</v>
+      </c>
+      <c r="G113" s="11">
+        <v>135150</v>
+      </c>
+      <c r="H113" s="11">
+        <v>829650</v>
+      </c>
       <c r="I113" s="16"/>
-      <c r="J113" s="15"/>
+      <c r="J113" s="15" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="114" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="10"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="11"/>
-      <c r="G114" s="11"/>
-      <c r="H114" s="11"/>
+      <c r="B114" s="10">
+        <v>45910</v>
+      </c>
+      <c r="C114" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D114" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E114" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F114" s="11">
+        <v>1003500</v>
+      </c>
+      <c r="G114" s="11">
+        <v>162650</v>
+      </c>
+      <c r="H114" s="11">
+        <v>802150</v>
+      </c>
       <c r="I114" s="16"/>
       <c r="J114" s="15"/>
     </row>
     <row r="115" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="10"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="11"/>
-      <c r="H115" s="11"/>
+      <c r="B115" s="10">
+        <v>45910</v>
+      </c>
+      <c r="C115" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D115" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E115" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F115" s="11">
+        <v>1007300</v>
+      </c>
+      <c r="G115" s="11">
+        <v>142650</v>
+      </c>
+      <c r="H115" s="11">
+        <v>825950</v>
+      </c>
       <c r="I115" s="16"/>
-      <c r="J115" s="15"/>
+      <c r="J115" s="15" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="116" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="10"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="11"/>
-      <c r="H116" s="11"/>
+      <c r="B116" s="10">
+        <v>45921</v>
+      </c>
+      <c r="C116" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D116" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E116" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F116" s="11">
+        <v>1007300</v>
+      </c>
+      <c r="G116" s="11">
+        <v>173250</v>
+      </c>
+      <c r="H116" s="11">
+        <v>795350</v>
+      </c>
       <c r="I116" s="16"/>
       <c r="J116" s="15"/>
     </row>
     <row r="117" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="10"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="11"/>
-      <c r="H117" s="11"/>
+      <c r="B117" s="10">
+        <v>45921</v>
+      </c>
+      <c r="C117" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D117" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E117" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F117" s="11">
+        <v>994300</v>
+      </c>
+      <c r="G117" s="11">
+        <v>160250</v>
+      </c>
+      <c r="H117" s="11">
+        <v>795350</v>
+      </c>
       <c r="I117" s="16"/>
-      <c r="J117" s="15"/>
+      <c r="J117" s="15" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="118" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="10"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="11"/>
-      <c r="H118" s="11"/>
+      <c r="B118" s="10">
+        <v>45921</v>
+      </c>
+      <c r="C118" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D118" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E118" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F118" s="11">
+        <v>996200</v>
+      </c>
+      <c r="G118" s="11">
+        <v>150250</v>
+      </c>
+      <c r="H118" s="11">
+        <v>807250</v>
+      </c>
       <c r="I118" s="16"/>
-      <c r="J118" s="15"/>
+      <c r="J118" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="119" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="10"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="11"/>
-      <c r="H119" s="11"/>
+      <c r="B119" s="10">
+        <v>45928</v>
+      </c>
+      <c r="C119" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D119" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E119" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F119" s="11">
+        <v>996200</v>
+      </c>
+      <c r="G119" s="11">
+        <v>176850</v>
+      </c>
+      <c r="H119" s="11">
+        <v>780650</v>
+      </c>
       <c r="I119" s="16"/>
       <c r="J119" s="15"/>
     </row>
     <row r="120" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="10"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
-      <c r="G120" s="11"/>
-      <c r="H120" s="11"/>
+      <c r="B120" s="10">
+        <v>45928</v>
+      </c>
+      <c r="C120" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D120" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E120" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F120" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="G120" s="11">
+        <v>156850</v>
+      </c>
+      <c r="H120" s="11">
+        <v>804450</v>
+      </c>
       <c r="I120" s="16"/>
-      <c r="J120" s="15"/>
+      <c r="J120" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="121" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="10"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="114">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -761,16 +761,23 @@
   </si>
   <si>
     <t>narmada loan 20000</t>
+  </si>
+  <si>
+    <t>rambhabati and sunanda loan adjustment</t>
+  </si>
+  <si>
+    <t>loan jameson and group 50000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -859,7 +866,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -953,12 +960,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1001,6 +1034,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5923,7 +5962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K121"/>
+  <dimension ref="B1:K133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -9055,17 +9094,185 @@
       </c>
     </row>
     <row r="121" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="10"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="11"/>
-      <c r="G121" s="11"/>
-      <c r="H121" s="11"/>
+      <c r="B121" s="10">
+        <v>45928</v>
+      </c>
+      <c r="C121" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D121" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E121" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F121" s="11">
+        <v>979200</v>
+      </c>
+      <c r="G121" s="11">
+        <v>156850</v>
+      </c>
+      <c r="H121" s="11">
+        <v>783650</v>
+      </c>
       <c r="I121" s="16"/>
-      <c r="J121" s="15"/>
+      <c r="J121" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="10">
+        <v>45933</v>
+      </c>
+      <c r="C122" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D122" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E122" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F122" s="11">
+        <v>979200</v>
+      </c>
+      <c r="G122" s="11">
+        <v>199750</v>
+      </c>
+      <c r="H122" s="11">
+        <v>740750</v>
+      </c>
+      <c r="I122" s="16"/>
+    </row>
+    <row r="123" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="10">
+        <v>45933</v>
+      </c>
+      <c r="C123" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D123" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E123" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F123" s="11">
+        <f>6500+989200</f>
+        <v>995700</v>
+      </c>
+      <c r="G123" s="11">
+        <f>6500+149750</f>
+        <v>156250</v>
+      </c>
+      <c r="H123" s="11">
+        <v>800750</v>
+      </c>
+      <c r="I123" s="16"/>
+      <c r="J123" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="10">
+        <v>45942</v>
+      </c>
+      <c r="C124" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D124" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E124" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F124" s="11">
+        <f>6500+989200</f>
+        <v>995700</v>
+      </c>
+      <c r="G124" s="11">
+        <v>169150</v>
+      </c>
+      <c r="H124" s="11">
+        <v>787850</v>
+      </c>
+      <c r="I124" s="16"/>
+      <c r="J124" s="15"/>
+    </row>
+    <row r="125" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="10"/>
+      <c r="C125" s="11"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="11"/>
+      <c r="G125" s="11"/>
+      <c r="H125" s="11"/>
+      <c r="I125" s="16"/>
+      <c r="J125" s="15"/>
+    </row>
+    <row r="126" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="10"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="11"/>
+      <c r="G126" s="11"/>
+      <c r="H126" s="11"/>
+      <c r="I126" s="16"/>
+      <c r="J126" s="15"/>
+    </row>
+    <row r="127" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="10"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="16"/>
+      <c r="J127" s="15"/>
+    </row>
+    <row r="128" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B128" s="10"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11"/>
+      <c r="I128" s="16"/>
+      <c r="J128" s="15"/>
+    </row>
+    <row r="129" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="10"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+      <c r="H129" s="11"/>
+      <c r="I129" s="16"/>
+      <c r="J129" s="15"/>
+    </row>
+    <row r="130" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="10"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
+      <c r="F130" s="11"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="11"/>
+      <c r="I130" s="16"/>
+      <c r="J130" s="15"/>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H133" s="18"/>
+      <c r="I133" s="19"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H133:I133"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="116">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -767,6 +767,12 @@
   </si>
   <si>
     <t>loan jameson and group 50000</t>
+  </si>
+  <si>
+    <t>marup 12500added 1000 frpm rambhabati</t>
+  </si>
+  <si>
+    <t>loan pratima 15000</t>
   </si>
 </sst>
 </file>
@@ -1037,10 +1043,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1812,6 +1818,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2187,6 +2194,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5962,7 +5970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K133"/>
+  <dimension ref="B1:K137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -9200,37 +9208,86 @@
       <c r="J124" s="15"/>
     </row>
     <row r="125" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="10"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="11"/>
-      <c r="F125" s="11"/>
-      <c r="G125" s="11"/>
-      <c r="H125" s="11"/>
+      <c r="B125" s="10">
+        <v>45949</v>
+      </c>
+      <c r="C125" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D125" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E125" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F125" s="11">
+        <f>6500+989200</f>
+        <v>995700</v>
+      </c>
+      <c r="G125" s="11">
+        <v>197450</v>
+      </c>
+      <c r="H125" s="11">
+        <v>759550</v>
+      </c>
       <c r="I125" s="16"/>
       <c r="J125" s="15"/>
     </row>
     <row r="126" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="10"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="11"/>
-      <c r="G126" s="11"/>
-      <c r="H126" s="11"/>
+      <c r="B126" s="10">
+        <v>45949</v>
+      </c>
+      <c r="C126" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D126" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E126" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F126" s="11">
+        <f>F125-12500+1000</f>
+        <v>984200</v>
+      </c>
+      <c r="G126" s="11">
+        <f>G125-6500-6000+1000</f>
+        <v>185950</v>
+      </c>
+      <c r="H126" s="11">
+        <v>759550</v>
+      </c>
       <c r="I126" s="16"/>
-      <c r="J126" s="15"/>
+      <c r="J126" s="15" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="127" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="10"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
-      <c r="H127" s="11"/>
+      <c r="B127" s="10">
+        <v>45949</v>
+      </c>
+      <c r="C127" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D127" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E127" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F127" s="11">
+        <v>987200</v>
+      </c>
+      <c r="G127" s="11">
+        <v>170950</v>
+      </c>
+      <c r="H127" s="11">
+        <v>777550</v>
+      </c>
       <c r="I127" s="16"/>
-      <c r="J127" s="15"/>
+      <c r="J127" s="15" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="128" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="10"/>
@@ -9266,13 +9323,38 @@
       <c r="J130" s="15"/>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E133" s="3">
+        <f>500+500+2000+200</f>
+        <v>3200</v>
+      </c>
       <c r="H133" s="18"/>
       <c r="I133" s="19"/>
     </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E134" s="3">
+        <f>1400*3+700+1400+1500+300+300+300+600</f>
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E135" s="3">
+        <f>500+500+1000+200+1400+500+400</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E136" s="3">
+        <f>100+1000+600+4300+500+1400+2400+1000</f>
+        <v>11300</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E137" s="3">
+        <f>SUM(E133:E136)</f>
+        <v>28300</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H133:I133"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="122">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -773,17 +773,34 @@
   </si>
   <si>
     <t>loan pratima 15000</t>
+  </si>
+  <si>
+    <t>chakouba bonus 10000(ranjita +priya)</t>
+  </si>
+  <si>
+    <t>loan naobi</t>
+  </si>
+  <si>
+    <t>loan bijenty 20000</t>
+  </si>
+  <si>
+    <t>sonia loan 20000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loan sheenarani 20k kamala 40k </t>
+  </si>
+  <si>
+    <t>marup 12500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -872,7 +889,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -966,38 +983,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1041,12 +1032,6 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5970,7 +5955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K137"/>
+  <dimension ref="B1:K140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -9290,69 +9275,293 @@
       </c>
     </row>
     <row r="128" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="10"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11"/>
-      <c r="G128" s="11"/>
-      <c r="H128" s="11"/>
+      <c r="B128" s="10">
+        <v>45959</v>
+      </c>
+      <c r="C128" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D128" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E128" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F128" s="11">
+        <v>987200</v>
+      </c>
+      <c r="G128" s="11">
+        <v>217250</v>
+      </c>
+      <c r="H128" s="11">
+        <v>731250</v>
+      </c>
       <c r="I128" s="16"/>
       <c r="J128" s="15"/>
     </row>
     <row r="129" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="10"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="11"/>
-      <c r="H129" s="11"/>
+      <c r="B129" s="10">
+        <v>45959</v>
+      </c>
+      <c r="C129" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D129" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E129" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F129" s="11">
+        <v>977200</v>
+      </c>
+      <c r="G129" s="11">
+        <v>207250</v>
+      </c>
+      <c r="H129" s="11">
+        <v>731250</v>
+      </c>
       <c r="I129" s="16"/>
-      <c r="J129" s="15"/>
+      <c r="J129" s="15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="130" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="10"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="11"/>
-      <c r="F130" s="11"/>
-      <c r="G130" s="11"/>
-      <c r="H130" s="11"/>
+      <c r="B130" s="10">
+        <v>45959</v>
+      </c>
+      <c r="C130" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D130" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E130" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F130" s="11">
+        <v>981200</v>
+      </c>
+      <c r="G130" s="11">
+        <v>187250</v>
+      </c>
+      <c r="H130" s="11">
+        <v>755250</v>
+      </c>
       <c r="I130" s="16"/>
-      <c r="J130" s="15"/>
+      <c r="J130" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B131" s="10">
+        <v>45961</v>
+      </c>
+      <c r="C131" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D131" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E131" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F131" s="11">
+        <v>981200</v>
+      </c>
+      <c r="G131" s="11">
+        <v>199650</v>
+      </c>
+      <c r="H131" s="11">
+        <v>742850</v>
+      </c>
+      <c r="I131" s="16"/>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B132" s="10">
+        <v>45961</v>
+      </c>
+      <c r="C132" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D132" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E132" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F132" s="11">
+        <v>985000</v>
+      </c>
+      <c r="G132" s="11">
+        <v>179650</v>
+      </c>
+      <c r="H132" s="11">
+        <v>766650</v>
+      </c>
+      <c r="I132" s="16"/>
+      <c r="J132" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E133" s="3">
-        <f>500+500+2000+200</f>
-        <v>3200</v>
-      </c>
-      <c r="H133" s="18"/>
-      <c r="I133" s="19"/>
+      <c r="B133" s="10">
+        <v>45971</v>
+      </c>
+      <c r="C133" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D133" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E133" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F133" s="11">
+        <v>985000</v>
+      </c>
+      <c r="G133" s="11">
+        <v>206150</v>
+      </c>
+      <c r="H133" s="11">
+        <v>740150</v>
+      </c>
+      <c r="I133" s="16"/>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E134" s="3">
-        <f>1400*3+700+1400+1500+300+300+300+600</f>
-        <v>9300</v>
+      <c r="B134" s="10">
+        <v>45971</v>
+      </c>
+      <c r="C134" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D134" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E134" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F134" s="11">
+        <v>989000</v>
+      </c>
+      <c r="G134" s="11">
+        <v>186150</v>
+      </c>
+      <c r="H134" s="11">
+        <v>764150</v>
+      </c>
+      <c r="I134" s="16"/>
+      <c r="J134" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E135" s="3">
-        <f>500+500+1000+200+1400+500+400</f>
-        <v>4500</v>
-      </c>
+      <c r="B135" s="10">
+        <v>45977</v>
+      </c>
+      <c r="C135" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D135" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E135" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F135" s="11">
+        <v>989000</v>
+      </c>
+      <c r="G135" s="11">
+        <v>221150</v>
+      </c>
+      <c r="H135" s="11">
+        <v>729150</v>
+      </c>
+      <c r="I135" s="16"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E136" s="3">
-        <f>100+1000+600+4300+500+1400+2400+1000</f>
-        <v>11300</v>
+      <c r="B136" s="10">
+        <v>45977</v>
+      </c>
+      <c r="C136" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D136" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E136" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F136" s="11">
+        <v>1001000</v>
+      </c>
+      <c r="G136" s="11">
+        <v>161150</v>
+      </c>
+      <c r="H136" s="11">
+        <v>801150</v>
+      </c>
+      <c r="I136" s="16"/>
+      <c r="J136" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E137" s="3">
-        <f>SUM(E133:E136)</f>
-        <v>28300</v>
-      </c>
+      <c r="B137" s="10">
+        <v>45977</v>
+      </c>
+      <c r="C137" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D137" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E137" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F137" s="11">
+        <v>988500</v>
+      </c>
+      <c r="G137" s="11">
+        <v>148650</v>
+      </c>
+      <c r="H137" s="11">
+        <v>801150</v>
+      </c>
+      <c r="I137" s="16"/>
+      <c r="J137" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B138" s="10"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="11"/>
+      <c r="H138" s="11"/>
+      <c r="I138" s="16"/>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B139" s="10"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="16"/>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B140" s="10"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="11"/>
+      <c r="H140" s="11"/>
+      <c r="I140" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="123">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -791,6 +791,9 @@
   </si>
   <si>
     <t>marup 12500</t>
+  </si>
+  <si>
+    <t>loan  romila 20000</t>
   </si>
 </sst>
 </file>
@@ -1803,7 +1806,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2179,7 +2181,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5955,7 +5956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K140"/>
+  <dimension ref="B1:K155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -9534,34 +9535,209 @@
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B138" s="10"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
-      <c r="G138" s="11"/>
-      <c r="H138" s="11"/>
+      <c r="B138" s="10">
+        <v>45985</v>
+      </c>
+      <c r="C138" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D138" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E138" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F138" s="11">
+        <v>988500</v>
+      </c>
+      <c r="G138" s="11">
+        <v>184550</v>
+      </c>
+      <c r="H138" s="11">
+        <v>765250</v>
+      </c>
       <c r="I138" s="16"/>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B139" s="10"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="11"/>
-      <c r="H139" s="11"/>
+      <c r="B139" s="10">
+        <v>45985</v>
+      </c>
+      <c r="C139" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D139" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E139" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F139" s="11">
+        <v>992300</v>
+      </c>
+      <c r="G139" s="11">
+        <v>164550</v>
+      </c>
+      <c r="H139" s="11">
+        <v>789050</v>
+      </c>
       <c r="I139" s="16"/>
+      <c r="J139" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B140" s="10"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="11"/>
-      <c r="H140" s="11"/>
+      <c r="B140" s="10">
+        <v>45991</v>
+      </c>
+      <c r="C140" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D140" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E140" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F140" s="11">
+        <v>992300</v>
+      </c>
+      <c r="G140" s="11">
+        <v>188300</v>
+      </c>
+      <c r="H140" s="11">
+        <v>765300</v>
+      </c>
       <c r="I140" s="16"/>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B141" s="10">
+        <v>45991</v>
+      </c>
+      <c r="C141" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D141" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E141" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F141" s="11">
+        <v>996300</v>
+      </c>
+      <c r="G141" s="11">
+        <v>168300</v>
+      </c>
+      <c r="H141" s="11">
+        <v>789300</v>
+      </c>
+      <c r="I141" s="16"/>
+      <c r="J141" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B142" s="10"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="16"/>
+    </row>
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B143" s="10"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11"/>
+      <c r="I143" s="16"/>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B144" s="10"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="16"/>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B145" s="10"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="11"/>
+      <c r="G145" s="11"/>
+      <c r="H145" s="11"/>
+      <c r="I145" s="16"/>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B146" s="10"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="16"/>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B147" s="10"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11"/>
+      <c r="I147" s="16"/>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B148" s="10"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="16"/>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F150" s="3">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F151" s="3">
+        <f>5500-2250</f>
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F152" s="3">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F153" s="3">
+        <f>F150-F151-F152</f>
+        <v>11750</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F154" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F155" s="3">
+        <f>F153-F154</f>
+        <v>4250</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="125">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -794,6 +794,12 @@
   </si>
   <si>
     <t>loan  romila 20000</t>
+  </si>
+  <si>
+    <t>loan inaobi 16000</t>
+  </si>
+  <si>
+    <t>loan budhacandra</t>
   </si>
 </sst>
 </file>
@@ -5956,7 +5962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K155"/>
+  <dimension ref="B1:K148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -9637,46 +9643,108 @@
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B142" s="10"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
-      <c r="G142" s="11"/>
-      <c r="H142" s="11"/>
+      <c r="B142" s="10">
+        <v>45996</v>
+      </c>
+      <c r="C142" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D142" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E142" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F142" s="11">
+        <v>996300</v>
+      </c>
+      <c r="G142" s="11">
+        <v>203500</v>
+      </c>
+      <c r="H142" s="11">
+        <v>754100</v>
+      </c>
       <c r="I142" s="16"/>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B143" s="10"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
+      <c r="B143" s="10">
+        <v>45996</v>
+      </c>
+      <c r="C143" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D143" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E143" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F143" s="11">
+        <v>999500</v>
+      </c>
+      <c r="G143" s="11">
+        <v>187500</v>
+      </c>
+      <c r="H143" s="11">
+        <v>773300</v>
+      </c>
       <c r="I143" s="16"/>
+      <c r="J143" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B144" s="10"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="F144" s="11"/>
-      <c r="G144" s="11"/>
-      <c r="H144" s="11"/>
+      <c r="B144" s="10">
+        <v>45997</v>
+      </c>
+      <c r="C144" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D144" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E144" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F144" s="11">
+        <v>999500</v>
+      </c>
+      <c r="G144" s="11">
+        <v>217050</v>
+      </c>
+      <c r="H144" s="11">
+        <v>743750</v>
+      </c>
       <c r="I144" s="16"/>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B145" s="10"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="11"/>
-      <c r="E145" s="11"/>
-      <c r="F145" s="11"/>
-      <c r="G145" s="11"/>
-      <c r="H145" s="11"/>
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B145" s="10">
+        <v>45997</v>
+      </c>
+      <c r="C145" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D145" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E145" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F145" s="11">
+        <v>1003500</v>
+      </c>
+      <c r="G145" s="11">
+        <v>197050</v>
+      </c>
+      <c r="H145" s="11">
+        <v>767750</v>
+      </c>
       <c r="I145" s="16"/>
-    </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J145" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="10"/>
       <c r="C146" s="11"/>
       <c r="D146" s="11"/>
@@ -9686,7 +9754,7 @@
       <c r="H146" s="11"/>
       <c r="I146" s="16"/>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="10"/>
       <c r="C147" s="11"/>
       <c r="D147" s="11"/>
@@ -9696,7 +9764,7 @@
       <c r="H147" s="11"/>
       <c r="I147" s="16"/>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="10"/>
       <c r="C148" s="11"/>
       <c r="D148" s="11"/>
@@ -9706,39 +9774,6 @@
       <c r="H148" s="11"/>
       <c r="I148" s="16"/>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="F150" s="3">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="F151" s="3">
-        <f>5500-2250</f>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="F152" s="3">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="F153" s="3">
-        <f>F150-F151-F152</f>
-        <v>11750</v>
-      </c>
-    </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="F154" s="3">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="F155" s="3">
-        <f>F153-F154</f>
-        <v>4250</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="128">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -800,6 +800,15 @@
   </si>
   <si>
     <t>loan budhacandra</t>
+  </si>
+  <si>
+    <t>ibeyaima loan 15000</t>
+  </si>
+  <si>
+    <t>wangkhei marup  6000</t>
+  </si>
+  <si>
+    <t>loan renita 20000 kiranmala 10000 denita 10000 sandhyarani 10000</t>
   </si>
 </sst>
 </file>
@@ -5962,7 +5971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K148"/>
+  <dimension ref="B1:K152"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -9745,34 +9754,184 @@
       </c>
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B146" s="10"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
-      <c r="G146" s="11"/>
-      <c r="H146" s="11"/>
+      <c r="B146" s="10">
+        <v>46005</v>
+      </c>
+      <c r="C146" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D146" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E146" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F146" s="11">
+        <v>1003500</v>
+      </c>
+      <c r="G146" s="11">
+        <v>202320</v>
+      </c>
+      <c r="H146" s="11">
+        <v>762480</v>
+      </c>
       <c r="I146" s="16"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B147" s="10"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11"/>
-      <c r="G147" s="11"/>
-      <c r="H147" s="11"/>
+      <c r="B147" s="10">
+        <v>46005</v>
+      </c>
+      <c r="C147" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D147" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E147" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F147" s="11">
+        <v>997000</v>
+      </c>
+      <c r="G147" s="11">
+        <v>195820</v>
+      </c>
+      <c r="H147" s="11">
+        <v>762480</v>
+      </c>
       <c r="I147" s="16"/>
+      <c r="J147" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B148" s="10"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="11"/>
-      <c r="E148" s="11"/>
-      <c r="F148" s="11"/>
-      <c r="G148" s="11"/>
-      <c r="H148" s="11"/>
+      <c r="B148" s="10">
+        <v>46006</v>
+      </c>
+      <c r="C148" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D148" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E148" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F148" s="11">
+        <v>997000</v>
+      </c>
+      <c r="G148" s="11">
+        <v>212690</v>
+      </c>
+      <c r="H148" s="11">
+        <v>745610</v>
+      </c>
       <c r="I148" s="16"/>
+    </row>
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B149" s="10">
+        <v>46006</v>
+      </c>
+      <c r="C149" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D149" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E149" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F149" s="11">
+        <v>999850</v>
+      </c>
+      <c r="G149" s="11">
+        <v>197690</v>
+      </c>
+      <c r="H149" s="11">
+        <v>763460</v>
+      </c>
+      <c r="I149" s="16"/>
+      <c r="J149" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B150" s="10">
+        <v>46018</v>
+      </c>
+      <c r="C150" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D150" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E150" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F150" s="11">
+        <v>999850</v>
+      </c>
+      <c r="G150" s="11">
+        <v>223210</v>
+      </c>
+      <c r="H150" s="11">
+        <v>737940</v>
+      </c>
+      <c r="I150" s="16"/>
+    </row>
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B151" s="10">
+        <v>46018</v>
+      </c>
+      <c r="C151" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D151" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E151" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F151" s="11">
+        <v>993850</v>
+      </c>
+      <c r="G151" s="11">
+        <v>217210</v>
+      </c>
+      <c r="H151" s="11">
+        <v>737940</v>
+      </c>
+      <c r="I151" s="16"/>
+      <c r="J151" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B152" s="10">
+        <v>46018</v>
+      </c>
+      <c r="C152" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D152" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E152" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F152" s="11">
+        <v>1003850</v>
+      </c>
+      <c r="G152" s="11">
+        <v>167210</v>
+      </c>
+      <c r="H152" s="11">
+        <v>797940</v>
+      </c>
+      <c r="I152" s="16"/>
+      <c r="J152" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
     <sheet name="2025TrendAnalysis" sheetId="16" r:id="rId2"/>
+    <sheet name="2026TrendAnalysis" sheetId="17" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -28,7 +29,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -37,7 +38,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -57,7 +58,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -66,7 +67,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -86,7 +87,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -95,7 +96,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -115,7 +116,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -124,7 +125,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -144,7 +145,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -153,7 +154,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sales of rice: 14600
@@ -175,7 +176,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -184,7 +185,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sunanda due 5400</t>
@@ -209,7 +210,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -218,7 +219,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -238,7 +239,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -247,7 +248,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -267,7 +268,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -276,7 +277,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -296,7 +297,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -305,7 +306,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 967450 total
@@ -325,7 +326,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -334,7 +335,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sales of rice: 14600
@@ -356,7 +357,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -365,7 +366,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sunanda due 5400</t>
@@ -380,7 +381,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -389,7 +390,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sunanda due 5400</t>
@@ -404,7 +405,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -413,7 +414,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 sunanda due 5400</t>
@@ -425,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="130">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -809,6 +810,12 @@
   </si>
   <si>
     <t>loan renita 20000 kiranmala 10000 denita 10000 sandhyarani 10000</t>
+  </si>
+  <si>
+    <t>marup 6500+6000; grocery 2000+1700</t>
+  </si>
+  <si>
+    <t>anand izra Rs 60000; payable to aboong 14650; online transfer 28100+10000=38100</t>
   </si>
 </sst>
 </file>
@@ -865,14 +872,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1821,6 +1828,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2196,6 +2204,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5971,7 +5980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K152"/>
+  <dimension ref="B1:K157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -9933,10 +9942,553 @@
         <v>127</v>
       </c>
     </row>
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B153" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C153" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D153" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E153" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F153" s="11">
+        <v>1003850</v>
+      </c>
+      <c r="G153" s="11">
+        <v>236510</v>
+      </c>
+      <c r="H153" s="11">
+        <v>728640</v>
+      </c>
+      <c r="I153" s="16"/>
+    </row>
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B154" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C154" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D154" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E154" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F154" s="11">
+        <v>987650</v>
+      </c>
+      <c r="G154" s="11">
+        <v>220310</v>
+      </c>
+      <c r="H154" s="11">
+        <v>728640</v>
+      </c>
+      <c r="I154" s="16"/>
+      <c r="J154" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B155" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C155" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D155" s="11">
+        <f>60000+60000-14650</f>
+        <v>105350</v>
+      </c>
+      <c r="E155" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F155" s="11">
+        <v>994900</v>
+      </c>
+      <c r="G155" s="11">
+        <f>220310-38100</f>
+        <v>182210</v>
+      </c>
+      <c r="H155" s="11">
+        <v>728640</v>
+      </c>
+      <c r="I155" s="16"/>
+      <c r="J155" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B156" s="10"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="11"/>
+      <c r="I156" s="16"/>
+    </row>
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B157" s="10"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+      <c r="G157" s="11"/>
+      <c r="H157" s="11"/>
+      <c r="I157" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:J19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="15" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" style="3" customWidth="1"/>
+    <col min="8" max="9" width="19.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:10" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="10">
+        <v>45996</v>
+      </c>
+      <c r="C4" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D4" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E4" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F4" s="11">
+        <v>996300</v>
+      </c>
+      <c r="G4" s="11">
+        <v>203500</v>
+      </c>
+      <c r="H4" s="11">
+        <v>754100</v>
+      </c>
+      <c r="I4" s="16"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="10">
+        <v>45996</v>
+      </c>
+      <c r="C5" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D5" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E5" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F5" s="11">
+        <v>999500</v>
+      </c>
+      <c r="G5" s="11">
+        <v>187500</v>
+      </c>
+      <c r="H5" s="11">
+        <v>773300</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="10">
+        <v>45997</v>
+      </c>
+      <c r="C6" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D6" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E6" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F6" s="11">
+        <v>999500</v>
+      </c>
+      <c r="G6" s="11">
+        <v>217050</v>
+      </c>
+      <c r="H6" s="11">
+        <v>743750</v>
+      </c>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="10">
+        <v>45997</v>
+      </c>
+      <c r="C7" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D7" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E7" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F7" s="11">
+        <v>1003500</v>
+      </c>
+      <c r="G7" s="11">
+        <v>197050</v>
+      </c>
+      <c r="H7" s="11">
+        <v>767750</v>
+      </c>
+      <c r="I7" s="16"/>
+      <c r="J7" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="10">
+        <v>46005</v>
+      </c>
+      <c r="C8" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D8" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E8" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F8" s="11">
+        <v>1003500</v>
+      </c>
+      <c r="G8" s="11">
+        <v>202320</v>
+      </c>
+      <c r="H8" s="11">
+        <v>762480</v>
+      </c>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="10">
+        <v>46005</v>
+      </c>
+      <c r="C9" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D9" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E9" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F9" s="11">
+        <v>997000</v>
+      </c>
+      <c r="G9" s="11">
+        <v>195820</v>
+      </c>
+      <c r="H9" s="11">
+        <v>762480</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="10">
+        <v>46006</v>
+      </c>
+      <c r="C10" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D10" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E10" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F10" s="11">
+        <v>997000</v>
+      </c>
+      <c r="G10" s="11">
+        <v>212690</v>
+      </c>
+      <c r="H10" s="11">
+        <v>745610</v>
+      </c>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="10">
+        <v>46006</v>
+      </c>
+      <c r="C11" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D11" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E11" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F11" s="11">
+        <v>999850</v>
+      </c>
+      <c r="G11" s="11">
+        <v>197690</v>
+      </c>
+      <c r="H11" s="11">
+        <v>763460</v>
+      </c>
+      <c r="I11" s="16"/>
+      <c r="J11" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="10">
+        <v>46018</v>
+      </c>
+      <c r="C12" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D12" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E12" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F12" s="11">
+        <v>999850</v>
+      </c>
+      <c r="G12" s="11">
+        <v>223210</v>
+      </c>
+      <c r="H12" s="11">
+        <v>737940</v>
+      </c>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="10">
+        <v>46018</v>
+      </c>
+      <c r="C13" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D13" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E13" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F13" s="11">
+        <v>993850</v>
+      </c>
+      <c r="G13" s="11">
+        <v>217210</v>
+      </c>
+      <c r="H13" s="11">
+        <v>737940</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="10">
+        <v>46018</v>
+      </c>
+      <c r="C14" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D14" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E14" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1003850</v>
+      </c>
+      <c r="G14" s="11">
+        <v>167210</v>
+      </c>
+      <c r="H14" s="11">
+        <v>797940</v>
+      </c>
+      <c r="I14" s="16"/>
+      <c r="J14" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C15" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D15" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F15" s="11">
+        <v>1003850</v>
+      </c>
+      <c r="G15" s="11">
+        <v>236510</v>
+      </c>
+      <c r="H15" s="11">
+        <v>728640</v>
+      </c>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C16" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D16" s="11">
+        <v>60000</v>
+      </c>
+      <c r="E16" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F16" s="11">
+        <v>987650</v>
+      </c>
+      <c r="G16" s="11">
+        <v>220310</v>
+      </c>
+      <c r="H16" s="11">
+        <v>728640</v>
+      </c>
+      <c r="I16" s="16"/>
+      <c r="J16" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C17" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D17" s="11">
+        <f>60000+60000-14650</f>
+        <v>105350</v>
+      </c>
+      <c r="E17" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F17" s="11">
+        <v>994900</v>
+      </c>
+      <c r="G17" s="11">
+        <f>220310-38100</f>
+        <v>182210</v>
+      </c>
+      <c r="H17" s="11">
+        <v>728640</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
     <sheet name="2025TrendAnalysis" sheetId="16" r:id="rId2"/>
     <sheet name="2026TrendAnalysis" sheetId="17" r:id="rId3"/>
+    <sheet name="trackingonline transaction" sheetId="18" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -426,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="142">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -816,6 +817,42 @@
   </si>
   <si>
     <t>anand izra Rs 60000; payable to aboong 14650; online transfer 28100+10000=38100</t>
+  </si>
+  <si>
+    <t>loan reena 10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjust priya loans of totalling 186900 as 1lakhs 90thousand </t>
+  </si>
+  <si>
+    <t>marup 6500+6000</t>
+  </si>
+  <si>
+    <t>loan pratima 20000 ibeyaima 30000 bijenty 50000</t>
+  </si>
+  <si>
+    <t>loan kamala 40000 sonia 20000</t>
+  </si>
+  <si>
+    <t>loan sanarei 140000 (chaoba 50000)</t>
+  </si>
+  <si>
+    <t>loan bidyabati 10000</t>
+  </si>
+  <si>
+    <t>loan ronel 20000</t>
+  </si>
+  <si>
+    <t>Credit (taken) from Chaoba</t>
+  </si>
+  <si>
+    <t>by Tungfam</t>
+  </si>
+  <si>
+    <t>online adjusted to HDFCBank (Aboong)</t>
+  </si>
+  <si>
+    <t>transferred to bechau</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1058,6 +1095,7 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1828,7 +1866,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2204,7 +2241,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10052,7 +10088,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J19"/>
+  <dimension ref="B1:J36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -10446,7 +10482,7 @@
         <v>188380</v>
       </c>
       <c r="D17" s="11">
-        <f>60000+60000-14650</f>
+        <f t="shared" ref="D17:D34" si="0">60000+60000-14650</f>
         <v>105350</v>
       </c>
       <c r="E17" s="11">
@@ -10468,27 +10504,541 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="10"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="B18" s="10">
+        <v>46061</v>
+      </c>
+      <c r="C18" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D18" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E18" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F18" s="11">
+        <v>994900</v>
+      </c>
+      <c r="G18" s="11">
+        <v>192160</v>
+      </c>
+      <c r="H18" s="11">
+        <v>718690</v>
+      </c>
       <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="10"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="B19" s="10">
+        <v>46061</v>
+      </c>
+      <c r="C19" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D19" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E19" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F19" s="11">
+        <v>996800</v>
+      </c>
+      <c r="G19" s="11">
+        <v>182160</v>
+      </c>
+      <c r="H19" s="11">
+        <v>730590</v>
+      </c>
       <c r="I19" s="16"/>
+      <c r="J19" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C20" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D20" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E20" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F20" s="11">
+        <v>996800</v>
+      </c>
+      <c r="G20" s="11">
+        <v>188660</v>
+      </c>
+      <c r="H20" s="11">
+        <v>724090</v>
+      </c>
+      <c r="I20" s="16"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C21" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D21" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E21" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F21" s="11">
+        <v>996800</v>
+      </c>
+      <c r="G21" s="11">
+        <v>375560</v>
+      </c>
+      <c r="H21" s="11">
+        <v>537190</v>
+      </c>
+      <c r="I21" s="16"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C22" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D22" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E22" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F22" s="11">
+        <v>996800</v>
+      </c>
+      <c r="G22" s="11">
+        <v>375560</v>
+      </c>
+      <c r="H22" s="11">
+        <v>537190</v>
+      </c>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C23" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D23" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E23" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F23" s="11">
+        <v>996800</v>
+      </c>
+      <c r="G23" s="11">
+        <v>185560</v>
+      </c>
+      <c r="H23" s="11">
+        <v>727190</v>
+      </c>
+      <c r="I23" s="16"/>
+      <c r="J23" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="10">
+        <v>46073</v>
+      </c>
+      <c r="C24" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D24" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E24" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F24" s="11">
+        <v>984300</v>
+      </c>
+      <c r="G24" s="11">
+        <v>173060</v>
+      </c>
+      <c r="H24" s="11">
+        <v>727190</v>
+      </c>
+      <c r="I24" s="16"/>
+      <c r="J24" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="10">
+        <v>46082</v>
+      </c>
+      <c r="C25" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D25" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E25" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F25" s="11">
+        <v>984300</v>
+      </c>
+      <c r="G25" s="11">
+        <v>227110</v>
+      </c>
+      <c r="H25" s="11">
+        <v>673140</v>
+      </c>
+      <c r="I25" s="16"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="10">
+        <v>46082</v>
+      </c>
+      <c r="C26" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D26" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E26" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F26" s="11">
+        <v>1003800</v>
+      </c>
+      <c r="G26" s="11">
+        <v>127110</v>
+      </c>
+      <c r="H26" s="11">
+        <v>792640</v>
+      </c>
+      <c r="I26" s="16"/>
+      <c r="J26" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="10">
+        <v>46087</v>
+      </c>
+      <c r="C27" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D27" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E27" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F27" s="11">
+        <v>1003800</v>
+      </c>
+      <c r="G27" s="11">
+        <v>140610</v>
+      </c>
+      <c r="H27" s="11">
+        <v>779140</v>
+      </c>
+      <c r="I27" s="16"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="10">
+        <v>46087</v>
+      </c>
+      <c r="C28" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D28" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E28" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F28" s="11">
+        <v>1015800</v>
+      </c>
+      <c r="G28" s="11">
+        <v>80610</v>
+      </c>
+      <c r="H28" s="11">
+        <v>851140</v>
+      </c>
+      <c r="I28" s="16"/>
+      <c r="J28" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="10">
+        <v>46088</v>
+      </c>
+      <c r="C29" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D29" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E29" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F29" s="11">
+        <v>1015800</v>
+      </c>
+      <c r="G29" s="11">
+        <v>92850</v>
+      </c>
+      <c r="H29" s="11">
+        <v>838900</v>
+      </c>
+      <c r="I29" s="16"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="10">
+        <v>46088</v>
+      </c>
+      <c r="C30" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D30" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E30" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F30" s="11">
+        <v>1042400</v>
+      </c>
+      <c r="G30" s="11">
+        <v>-47150</v>
+      </c>
+      <c r="H30" s="11">
+        <v>1005500</v>
+      </c>
+      <c r="I30" s="16"/>
+      <c r="J30" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="10">
+        <v>46089</v>
+      </c>
+      <c r="C31" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D31" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E31" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F31" s="11">
+        <v>1042400</v>
+      </c>
+      <c r="G31" s="11">
+        <v>-42290</v>
+      </c>
+      <c r="H31" s="11">
+        <v>1000640</v>
+      </c>
+      <c r="I31" s="16"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="10">
+        <v>46089</v>
+      </c>
+      <c r="C32" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D32" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E32" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F32" s="11">
+        <v>1044400</v>
+      </c>
+      <c r="G32" s="11">
+        <v>-52290</v>
+      </c>
+      <c r="H32" s="11">
+        <v>1012640</v>
+      </c>
+      <c r="I32" s="16"/>
+      <c r="J32" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="10">
+        <v>46089</v>
+      </c>
+      <c r="C33" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D33" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E33" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F33" s="11">
+        <v>1044400</v>
+      </c>
+      <c r="G33" s="11">
+        <v>-48670</v>
+      </c>
+      <c r="H33" s="11">
+        <v>1009020</v>
+      </c>
+      <c r="I33" s="16"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="10">
+        <v>46092</v>
+      </c>
+      <c r="C34" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D34" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E34" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F34" s="11">
+        <v>1048200</v>
+      </c>
+      <c r="G34" s="11">
+        <v>-68670</v>
+      </c>
+      <c r="H34" s="11">
+        <v>1032820</v>
+      </c>
+      <c r="I34" s="16"/>
+      <c r="J34" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="16"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>46090</v>
+      </c>
+      <c r="B4">
+        <v>20000</v>
+      </c>
+      <c r="C4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
+        <v>46092</v>
+      </c>
+      <c r="B5">
+        <v>20000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>46092</v>
+      </c>
+      <c r="B6">
+        <v>10000</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="18">
+        <v>46092</v>
+      </c>
+      <c r="B7">
+        <v>2500</v>
+      </c>
+      <c r="C7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f>SUM(B4:B12)</f>
+        <v>52500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="6000" windowWidth="15360" windowHeight="2010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2023TrendAnalysis" sheetId="15" r:id="rId1"/>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="157">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -853,6 +853,51 @@
   </si>
   <si>
     <t>transferred to bechau</t>
+  </si>
+  <si>
+    <t>transferred to benao  8000 (500 for vegeatables/7500 for benao)</t>
+  </si>
+  <si>
+    <t>loan lanvhenbi 60000 bala 20000 bidyalaxmi 5000</t>
+  </si>
+  <si>
+    <t>Buncha Maroop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bechau </t>
+  </si>
+  <si>
+    <t>aboong</t>
+  </si>
+  <si>
+    <t>mother</t>
+  </si>
+  <si>
+    <t>tungfam (nanao)</t>
+  </si>
+  <si>
+    <t>no loan issue</t>
+  </si>
+  <si>
+    <t>loan nanao 10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> withdrawn  9300  baenao (online transfer 8000) ranjit 11300+ranjita 700</t>
+  </si>
+  <si>
+    <t>marup bomcha 11500</t>
+  </si>
+  <si>
+    <t>wangkhei marup 11000</t>
+  </si>
+  <si>
+    <t>chicken 250</t>
+  </si>
+  <si>
+    <t>dada 1300(chiraoba fish vegetable and tablet on march 18 adjusted with deposit  11300</t>
+  </si>
+  <si>
+    <t>130000+12000+10000+11500</t>
   </si>
 </sst>
 </file>
@@ -864,7 +909,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -917,6 +962,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1050,7 +1103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1096,6 +1149,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1866,6 +1920,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2241,6 +2296,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10088,7 +10144,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J36"/>
+  <dimension ref="B1:J52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -10482,7 +10538,7 @@
         <v>188380</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" ref="D17:D34" si="0">60000+60000-14650</f>
+        <f t="shared" ref="D17:D45" si="0">60000+60000-14650</f>
         <v>105350</v>
       </c>
       <c r="E17" s="11">
@@ -10953,24 +11009,346 @@
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="B35" s="10">
+        <v>46094</v>
+      </c>
+      <c r="C35" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D35" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E35" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F35" s="11">
+        <v>1048200</v>
+      </c>
+      <c r="G35" s="11">
+        <v>-55810</v>
+      </c>
+      <c r="H35" s="11">
+        <v>1019960</v>
+      </c>
       <c r="I35" s="16"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="10"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
+      <c r="B36" s="10">
+        <v>46094</v>
+      </c>
+      <c r="C36" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D36" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E36" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F36" s="11">
+        <v>1064400</v>
+      </c>
+      <c r="G36" s="11">
+        <v>-140810</v>
+      </c>
+      <c r="H36" s="11">
+        <v>1121160</v>
+      </c>
       <c r="I36" s="16"/>
+      <c r="J36" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="10">
+        <v>46095</v>
+      </c>
+      <c r="C37" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D37" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E37" s="11">
+        <v>21300</v>
+      </c>
+      <c r="F37" s="11">
+        <v>1064400</v>
+      </c>
+      <c r="G37" s="11">
+        <v>-140400</v>
+      </c>
+      <c r="H37" s="11">
+        <v>1120750</v>
+      </c>
+      <c r="I37" s="16"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="10">
+        <v>46095</v>
+      </c>
+      <c r="C38" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D38" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E38" s="11">
+        <v>12000</v>
+      </c>
+      <c r="F38" s="11">
+        <v>1064400</v>
+      </c>
+      <c r="G38" s="11">
+        <v>-149700</v>
+      </c>
+      <c r="H38" s="11">
+        <v>1120750</v>
+      </c>
+      <c r="I38" s="16"/>
+      <c r="J38" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="10">
+        <v>46095</v>
+      </c>
+      <c r="C39" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D39" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E39" s="11">
+        <f>130000+12000</f>
+        <v>142000</v>
+      </c>
+      <c r="F39" s="11">
+        <v>1064400</v>
+      </c>
+      <c r="G39" s="11">
+        <v>-19700</v>
+      </c>
+      <c r="H39" s="11">
+        <v>1120750</v>
+      </c>
+      <c r="I39" s="16"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C40" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D40" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E40" s="11">
+        <f>130000+12000</f>
+        <v>142000</v>
+      </c>
+      <c r="F40" s="11">
+        <v>1064400</v>
+      </c>
+      <c r="G40" s="11">
+        <v>46300</v>
+      </c>
+      <c r="H40" s="11">
+        <v>1054750</v>
+      </c>
+      <c r="I40" s="16"/>
+      <c r="J40" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C41" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D41" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E41" s="11">
+        <f>130000+12000+10000</f>
+        <v>152000</v>
+      </c>
+      <c r="F41" s="11">
+        <v>1064400</v>
+      </c>
+      <c r="G41" s="11">
+        <v>46300</v>
+      </c>
+      <c r="H41" s="11">
+        <v>1064750</v>
+      </c>
+      <c r="I41" s="16"/>
+      <c r="J41" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C42" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D42" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E42" s="11">
+        <f>130000+12000+10000+11500</f>
+        <v>163500</v>
+      </c>
+      <c r="F42" s="11">
+        <v>1052900</v>
+      </c>
+      <c r="G42" s="11">
+        <v>46300</v>
+      </c>
+      <c r="H42" s="11">
+        <v>1064750</v>
+      </c>
+      <c r="I42" s="16"/>
+      <c r="J42" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C43" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D43" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E43" s="11">
+        <f>130000+12000+10000+11500</f>
+        <v>163500</v>
+      </c>
+      <c r="F43" s="11">
+        <v>1041900</v>
+      </c>
+      <c r="G43" s="11">
+        <v>35300</v>
+      </c>
+      <c r="H43" s="11">
+        <v>1064750</v>
+      </c>
+      <c r="I43" s="16"/>
+      <c r="J43" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C44" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D44" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E44" s="11">
+        <f>130000+12000+10000+11500</f>
+        <v>163500</v>
+      </c>
+      <c r="F44" s="11">
+        <v>1041650</v>
+      </c>
+      <c r="G44" s="11">
+        <v>35050</v>
+      </c>
+      <c r="H44" s="11">
+        <v>1064750</v>
+      </c>
+      <c r="I44" s="16"/>
+      <c r="J44" s="14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C45" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D45" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E45" s="11">
+        <f>130000+12000+10000+11500-1300</f>
+        <v>162200</v>
+      </c>
+      <c r="F45" s="11">
+        <v>1041650</v>
+      </c>
+      <c r="G45" s="11">
+        <v>33750</v>
+      </c>
+      <c r="H45" s="11">
+        <v>1064750</v>
+      </c>
+      <c r="I45" s="16"/>
+      <c r="J45" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="16"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E48" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="3">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="3">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="3">
+        <f>E49+E50+E51</f>
+        <v>151500</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10980,15 +11358,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:C13"/>
+  <dimension ref="A3:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>46090</v>
       </c>
@@ -10999,7 +11377,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>46092</v>
       </c>
@@ -11010,18 +11388,20 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>46092</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="19">
         <v>10000</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="19" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>46092</v>
       </c>
@@ -11032,13 +11412,110 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <f>SUM(B4:B12)</f>
-        <v>52500</v>
-      </c>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>46093</v>
+      </c>
+      <c r="B8">
+        <v>7500</v>
+      </c>
+      <c r="C8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>46094</v>
+      </c>
+      <c r="B9">
+        <v>70000</v>
+      </c>
+      <c r="C9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>46096</v>
+      </c>
+      <c r="B10">
+        <v>11500</v>
+      </c>
+      <c r="C10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>46099</v>
+      </c>
+      <c r="B11">
+        <v>5000</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>46103</v>
+      </c>
+      <c r="B12">
+        <v>10000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15" s="18">
+        <v>46099</v>
+      </c>
+      <c r="H15">
+        <v>4000</v>
+      </c>
+      <c r="I15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>SUM(B4:B15)</f>
+        <v>156500</v>
+      </c>
+      <c r="G16" s="18">
+        <v>46103</v>
+      </c>
+      <c r="H16">
+        <v>11000</v>
+      </c>
+      <c r="I16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="19"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="19"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="19"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="19"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="164">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -897,7 +897,28 @@
     <t>dada 1300(chiraoba fish vegetable and tablet on march 18 adjusted with deposit  11300</t>
   </si>
   <si>
-    <t>130000+12000+10000+11500</t>
+    <t>loan sandhyarani 10000</t>
+  </si>
+  <si>
+    <t>vegetable and fish 1600+6500(marup)</t>
+  </si>
+  <si>
+    <t>ranjita deposit 80000</t>
+  </si>
+  <si>
+    <t>marup bomcha 6500+11000</t>
+  </si>
+  <si>
+    <t>loan 20000 sudhana</t>
+  </si>
+  <si>
+    <t>marup  16500 (bomcha)</t>
+  </si>
+  <si>
+    <t>minarani loan 20000</t>
+  </si>
+  <si>
+    <t>naoton loan 10000</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1941,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2296,7 +2316,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10144,7 +10163,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J52"/>
+  <dimension ref="B1:J61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -10538,7 +10557,7 @@
         <v>188380</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" ref="D17:D45" si="0">60000+60000-14650</f>
+        <f t="shared" ref="D17:D61" si="0">60000+60000-14650</f>
         <v>105350</v>
       </c>
       <c r="E17" s="11">
@@ -11315,39 +11334,442 @@
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="10"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
+      <c r="B46" s="10">
+        <v>46125</v>
+      </c>
+      <c r="C46" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D46" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E46" s="11">
+        <f>130000+12000+10000+11500-1300</f>
+        <v>162200</v>
+      </c>
+      <c r="F46" s="11">
+        <v>1041650</v>
+      </c>
+      <c r="G46" s="11">
+        <v>73050</v>
+      </c>
+      <c r="H46" s="11">
+        <v>1025450</v>
+      </c>
       <c r="I46" s="16"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E48" s="3" t="s">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="10">
+        <v>46125</v>
+      </c>
+      <c r="C47" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D47" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E47" s="11">
+        <f>130000+12000+10000+11500-1300</f>
+        <v>162200</v>
+      </c>
+      <c r="F47" s="11">
+        <v>1043550</v>
+      </c>
+      <c r="G47" s="11">
+        <v>63050</v>
+      </c>
+      <c r="H47" s="11">
+        <v>1037350</v>
+      </c>
+      <c r="I47" s="16"/>
+      <c r="J47" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="3">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="3">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="3">
-        <f>E49+E50+E51</f>
-        <v>151500</v>
+    <row r="48" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="10">
+        <v>46129</v>
+      </c>
+      <c r="C48" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D48" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E48" s="11">
+        <f>130000+12000+10000+11500-1300</f>
+        <v>162200</v>
+      </c>
+      <c r="F48" s="11">
+        <v>1043550</v>
+      </c>
+      <c r="G48" s="11">
+        <v>76900</v>
+      </c>
+      <c r="H48" s="11">
+        <v>1023500</v>
+      </c>
+      <c r="I48" s="16"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="10">
+        <v>46129</v>
+      </c>
+      <c r="C49" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D49" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E49" s="11">
+        <f>130000+12000+10000+11500-1300</f>
+        <v>162200</v>
+      </c>
+      <c r="F49" s="11">
+        <v>1035450</v>
+      </c>
+      <c r="G49" s="11">
+        <v>68800</v>
+      </c>
+      <c r="H49" s="11">
+        <v>1023500</v>
+      </c>
+      <c r="I49" s="16"/>
+      <c r="J49" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="10">
+        <v>46129</v>
+      </c>
+      <c r="C50" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D50" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E50" s="11">
+        <v>242200</v>
+      </c>
+      <c r="F50" s="11">
+        <v>1035450</v>
+      </c>
+      <c r="G50" s="11">
+        <v>148800</v>
+      </c>
+      <c r="H50" s="11">
+        <v>1023500</v>
+      </c>
+      <c r="I50" s="16"/>
+      <c r="J50" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="10">
+        <v>46129</v>
+      </c>
+      <c r="C51" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D51" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E51" s="11">
+        <f t="shared" ref="E51:E61" si="1">10200+12000+80000</f>
+        <v>102200</v>
+      </c>
+      <c r="F51" s="11">
+        <v>1035450</v>
+      </c>
+      <c r="G51" s="11">
+        <v>8800</v>
+      </c>
+      <c r="H51" s="11">
+        <v>1023500</v>
+      </c>
+      <c r="I51" s="16"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="10">
+        <v>46144</v>
+      </c>
+      <c r="C52" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D52" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E52" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F52" s="11">
+        <v>1035450</v>
+      </c>
+      <c r="G52" s="11">
+        <v>58600</v>
+      </c>
+      <c r="H52" s="11">
+        <v>973700</v>
+      </c>
+      <c r="I52" s="16"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="10">
+        <v>46144</v>
+      </c>
+      <c r="C53" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D53" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E53" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F53" s="11">
+        <v>1017950</v>
+      </c>
+      <c r="G53" s="11">
+        <v>41100</v>
+      </c>
+      <c r="H53" s="11">
+        <v>973700</v>
+      </c>
+      <c r="I53" s="16"/>
+      <c r="J53" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="10">
+        <v>46145</v>
+      </c>
+      <c r="C54" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D54" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E54" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F54" s="11">
+        <v>1021750</v>
+      </c>
+      <c r="G54" s="11">
+        <v>21100</v>
+      </c>
+      <c r="H54" s="11">
+        <v>997500</v>
+      </c>
+      <c r="I54" s="16"/>
+      <c r="J54" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C55" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D55" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E55" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F55" s="11">
+        <v>1021750</v>
+      </c>
+      <c r="G55" s="11">
+        <v>28100</v>
+      </c>
+      <c r="H55" s="11">
+        <v>990500</v>
+      </c>
+      <c r="I55" s="16"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C56" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D56" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E56" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F56" s="11">
+        <v>1025550</v>
+      </c>
+      <c r="G56" s="11">
+        <v>8100</v>
+      </c>
+      <c r="H56" s="11">
+        <v>1014300</v>
+      </c>
+      <c r="I56" s="16"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C57" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D57" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E57" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F57" s="11">
+        <v>1025550</v>
+      </c>
+      <c r="G57" s="11">
+        <v>28800</v>
+      </c>
+      <c r="H57" s="11">
+        <v>993600</v>
+      </c>
+      <c r="I57" s="16"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="10">
+        <v>46150</v>
+      </c>
+      <c r="C58" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D58" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E58" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F58" s="11">
+        <v>1029350</v>
+      </c>
+      <c r="G58" s="11">
+        <v>8800</v>
+      </c>
+      <c r="H58" s="11">
+        <v>1017400</v>
+      </c>
+      <c r="I58" s="16"/>
+      <c r="J58" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C59" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D59" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E59" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F59" s="11">
+        <v>1029550</v>
+      </c>
+      <c r="G59" s="11">
+        <v>47400</v>
+      </c>
+      <c r="H59" s="11">
+        <v>979000</v>
+      </c>
+      <c r="I59" s="16"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C60" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D60" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E60" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F60" s="11">
+        <v>1013050</v>
+      </c>
+      <c r="G60" s="11">
+        <v>30900</v>
+      </c>
+      <c r="H60" s="11">
+        <v>979000</v>
+      </c>
+      <c r="I60" s="16"/>
+      <c r="J60" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C61" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D61" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E61" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F61" s="11">
+        <v>1013050</v>
+      </c>
+      <c r="G61" s="11">
+        <v>20900</v>
+      </c>
+      <c r="H61" s="11">
+        <v>989000</v>
+      </c>
+      <c r="I61" s="16"/>
+      <c r="J61" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="169">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -919,6 +919,21 @@
   </si>
   <si>
     <t>naoton loan 10000</t>
+  </si>
+  <si>
+    <t>bomcha marup 16500+wangkhei marup 11000 baenao deposit withdrawal 2000</t>
+  </si>
+  <si>
+    <t>bidyabati loan 10000</t>
+  </si>
+  <si>
+    <t>adjusted ayangpalli  ibeyaima</t>
+  </si>
+  <si>
+    <t>loan ibeyaima ayangpalli 30000</t>
+  </si>
+  <si>
+    <t>grocery 5000</t>
   </si>
 </sst>
 </file>
@@ -10163,7 +10178,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J61"/>
+  <dimension ref="B1:J67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -10557,7 +10572,7 @@
         <v>188380</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" ref="D17:D61" si="0">60000+60000-14650</f>
+        <f t="shared" ref="D17:D67" si="0">60000+60000-14650</f>
         <v>105350</v>
       </c>
       <c r="E17" s="11">
@@ -11483,7 +11498,7 @@
         <v>105350</v>
       </c>
       <c r="E51" s="11">
-        <f t="shared" ref="E51:E61" si="1">10200+12000+80000</f>
+        <f t="shared" ref="E51:E62" si="1">10200+12000+80000</f>
         <v>102200</v>
       </c>
       <c r="F51" s="11">
@@ -11770,6 +11785,177 @@
       <c r="I61" s="16"/>
       <c r="J61" s="2" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C62" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D62" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E62" s="11">
+        <f t="shared" si="1"/>
+        <v>102200</v>
+      </c>
+      <c r="F62" s="11">
+        <v>1013050</v>
+      </c>
+      <c r="G62" s="11">
+        <v>63800</v>
+      </c>
+      <c r="H62" s="11">
+        <v>946100</v>
+      </c>
+      <c r="I62" s="16"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C63" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D63" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E63" s="11">
+        <f>10200+10000+80000</f>
+        <v>100200</v>
+      </c>
+      <c r="F63" s="11">
+        <v>985550</v>
+      </c>
+      <c r="G63" s="11">
+        <v>34300</v>
+      </c>
+      <c r="H63" s="11">
+        <v>946100</v>
+      </c>
+      <c r="I63" s="16"/>
+      <c r="J63" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C64" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D64" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E64" s="11">
+        <f>10200+10000+80000</f>
+        <v>100200</v>
+      </c>
+      <c r="F64" s="11">
+        <v>987550</v>
+      </c>
+      <c r="G64" s="11">
+        <v>24300</v>
+      </c>
+      <c r="H64" s="11">
+        <v>958100</v>
+      </c>
+      <c r="I64" s="16"/>
+      <c r="J64" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="10">
+        <v>46171</v>
+      </c>
+      <c r="C65" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D65" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E65" s="11">
+        <f>10200+10000+80000</f>
+        <v>100200</v>
+      </c>
+      <c r="F65" s="11">
+        <v>987550</v>
+      </c>
+      <c r="G65" s="11">
+        <v>52700</v>
+      </c>
+      <c r="H65" s="11">
+        <v>929700</v>
+      </c>
+      <c r="I65" s="16"/>
+      <c r="J65" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="10">
+        <v>46171</v>
+      </c>
+      <c r="C66" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D66" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E66" s="11">
+        <f>10200+10000+80000</f>
+        <v>100200</v>
+      </c>
+      <c r="F66" s="11">
+        <v>993250</v>
+      </c>
+      <c r="G66" s="11">
+        <v>22700</v>
+      </c>
+      <c r="H66" s="11">
+        <v>965400</v>
+      </c>
+      <c r="I66" s="16"/>
+      <c r="J66" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" s="10">
+        <v>46171</v>
+      </c>
+      <c r="C67" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D67" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E67" s="11">
+        <f>10200+10000+80000</f>
+        <v>100200</v>
+      </c>
+      <c r="F67" s="11">
+        <v>988250</v>
+      </c>
+      <c r="G67" s="11">
+        <v>17700</v>
+      </c>
+      <c r="H67" s="11">
+        <v>965400</v>
+      </c>
+      <c r="I67" s="16"/>
+      <c r="J67" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="171">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -934,6 +934,12 @@
   </si>
   <si>
     <t>grocery 5000</t>
+  </si>
+  <si>
+    <t>loan inaobi 7000 , renita 18000 , romila 18000</t>
+  </si>
+  <si>
+    <t>bidyabati2 loan 10000</t>
   </si>
 </sst>
 </file>
@@ -10178,7 +10184,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J67"/>
+  <dimension ref="B1:J76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -10572,7 +10578,7 @@
         <v>188380</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" ref="D17:D67" si="0">60000+60000-14650</f>
+        <f t="shared" ref="D17:D73" si="0">60000+60000-14650</f>
         <v>105350</v>
       </c>
       <c r="E17" s="11">
@@ -11825,7 +11831,7 @@
         <v>105350</v>
       </c>
       <c r="E63" s="11">
-        <f>10200+10000+80000</f>
+        <f t="shared" ref="E63:E73" si="2">10200+10000+80000</f>
         <v>100200</v>
       </c>
       <c r="F63" s="11">
@@ -11854,7 +11860,7 @@
         <v>105350</v>
       </c>
       <c r="E64" s="11">
-        <f>10200+10000+80000</f>
+        <f t="shared" si="2"/>
         <v>100200</v>
       </c>
       <c r="F64" s="11">
@@ -11883,7 +11889,7 @@
         <v>105350</v>
       </c>
       <c r="E65" s="11">
-        <f>10200+10000+80000</f>
+        <f t="shared" si="2"/>
         <v>100200</v>
       </c>
       <c r="F65" s="11">
@@ -11912,7 +11918,7 @@
         <v>105350</v>
       </c>
       <c r="E66" s="11">
-        <f>10200+10000+80000</f>
+        <f t="shared" si="2"/>
         <v>100200</v>
       </c>
       <c r="F66" s="11">
@@ -11941,7 +11947,7 @@
         <v>105350</v>
       </c>
       <c r="E67" s="11">
-        <f>10200+10000+80000</f>
+        <f t="shared" si="2"/>
         <v>100200</v>
       </c>
       <c r="F67" s="11">
@@ -11957,6 +11963,201 @@
       <c r="J67" s="2" t="s">
         <v>168</v>
       </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C68" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D68" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E68" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F68" s="11">
+        <v>988250</v>
+      </c>
+      <c r="G68" s="11">
+        <v>65100</v>
+      </c>
+      <c r="H68" s="11">
+        <v>918000</v>
+      </c>
+      <c r="I68" s="16"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C69" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D69" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E69" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F69" s="11">
+        <v>996450</v>
+      </c>
+      <c r="G69" s="11">
+        <v>22100</v>
+      </c>
+      <c r="H69" s="11">
+        <v>969200</v>
+      </c>
+      <c r="I69" s="16"/>
+      <c r="J69" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B70" s="10">
+        <v>46176</v>
+      </c>
+      <c r="C70" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D70" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E70" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F70" s="11">
+        <v>996450</v>
+      </c>
+      <c r="G70" s="11">
+        <v>32990</v>
+      </c>
+      <c r="H70" s="11">
+        <v>958310</v>
+      </c>
+      <c r="I70" s="16"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" s="10">
+        <v>46176</v>
+      </c>
+      <c r="C71" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D71" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E71" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F71" s="11">
+        <v>998450</v>
+      </c>
+      <c r="G71" s="11">
+        <v>22990</v>
+      </c>
+      <c r="H71" s="11">
+        <v>970310</v>
+      </c>
+      <c r="I71" s="16"/>
+      <c r="J71" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" s="10">
+        <v>46177</v>
+      </c>
+      <c r="C72" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D72" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E72" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F72" s="11">
+        <v>998450</v>
+      </c>
+      <c r="G72" s="11">
+        <v>29670</v>
+      </c>
+      <c r="H72" s="11">
+        <v>963630</v>
+      </c>
+      <c r="I72" s="16"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B73" s="10">
+        <v>46177</v>
+      </c>
+      <c r="C73" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D73" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E73" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F73" s="11">
+        <v>1000450</v>
+      </c>
+      <c r="G73" s="11">
+        <v>19670</v>
+      </c>
+      <c r="H73" s="11">
+        <v>975630</v>
+      </c>
+      <c r="I73" s="16"/>
+      <c r="J73" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B74" s="10"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="16"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B75" s="10"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="16"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B76" s="10"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="172">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -940,6 +940,9 @@
   </si>
   <si>
     <t>bidyabati2 loan 10000</t>
+  </si>
+  <si>
+    <t>Gomti loan 20000</t>
   </si>
 </sst>
 </file>
@@ -10184,7 +10187,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J76"/>
+  <dimension ref="B1:J84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
@@ -10578,7 +10581,7 @@
         <v>188380</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" ref="D17:D73" si="0">60000+60000-14650</f>
+        <f t="shared" ref="D17:D78" si="0">60000+60000-14650</f>
         <v>105350</v>
       </c>
       <c r="E17" s="11">
@@ -11831,7 +11834,7 @@
         <v>105350</v>
       </c>
       <c r="E63" s="11">
-        <f t="shared" ref="E63:E73" si="2">10200+10000+80000</f>
+        <f t="shared" ref="E63:E78" si="2">10200+10000+80000</f>
         <v>100200</v>
       </c>
       <c r="F63" s="11">
@@ -12130,34 +12133,200 @@
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B74" s="10"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
+      <c r="B74" s="10">
+        <v>46179</v>
+      </c>
+      <c r="C74" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D74" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E74" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F74" s="11">
+        <v>1000450</v>
+      </c>
+      <c r="G74" s="11">
+        <v>46850</v>
+      </c>
+      <c r="H74" s="11">
+        <v>948450</v>
+      </c>
       <c r="I74" s="16"/>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B75" s="10"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
+      <c r="B75" s="10">
+        <v>46179</v>
+      </c>
+      <c r="C75" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D75" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E75" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F75" s="11">
+        <v>1004250</v>
+      </c>
+      <c r="G75" s="11">
+        <v>26850</v>
+      </c>
+      <c r="H75" s="11">
+        <v>972250</v>
+      </c>
       <c r="I75" s="16"/>
+      <c r="J75" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B76" s="10"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
+      <c r="B76" s="10">
+        <v>46181</v>
+      </c>
+      <c r="C76" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D76" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E76" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F76" s="11">
+        <v>1004250</v>
+      </c>
+      <c r="G76" s="11">
+        <v>34990</v>
+      </c>
+      <c r="H76" s="11">
+        <v>964110</v>
+      </c>
       <c r="I76" s="16"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B77" s="10">
+        <v>46181</v>
+      </c>
+      <c r="C77" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D77" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E77" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F77" s="11">
+        <v>1006150</v>
+      </c>
+      <c r="G77" s="11">
+        <v>24990</v>
+      </c>
+      <c r="H77" s="11">
+        <v>976010</v>
+      </c>
+      <c r="I77" s="16"/>
+      <c r="J77" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B78" s="10">
+        <v>46183</v>
+      </c>
+      <c r="C78" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D78" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E78" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F78" s="11">
+        <v>1006150</v>
+      </c>
+      <c r="G78" s="11">
+        <v>28550</v>
+      </c>
+      <c r="H78" s="11">
+        <v>972450</v>
+      </c>
+      <c r="I78" s="16"/>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B79" s="10"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="16"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B80" s="10"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="16"/>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B81" s="10"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="16"/>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B82" s="10"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="16"/>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B83" s="10"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="16"/>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B84" s="10"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/trendAnalysis.xlsx
+++ b/trendAnalysis.xlsx
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="173">
   <si>
     <t>Outstanding Amount</t>
   </si>
@@ -943,13 +943,17 @@
   </si>
   <si>
     <t>Gomti loan 20000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sunanda monthly loan 120000 adjusted </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-14009]dddd\,\ d\ mmmm\,\ yyyy;@"/>
@@ -1148,7 +1152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1195,6 +1199,7 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -10581,7 +10586,7 @@
         <v>188380</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" ref="D17:D78" si="0">60000+60000-14650</f>
+        <f t="shared" ref="D17:D79" si="0">60000+60000-14650</f>
         <v>105350</v>
       </c>
       <c r="E17" s="11">
@@ -11834,7 +11839,7 @@
         <v>105350</v>
       </c>
       <c r="E63" s="11">
-        <f t="shared" ref="E63:E78" si="2">10200+10000+80000</f>
+        <f t="shared" ref="E63:E79" si="2">10200+10000+80000</f>
         <v>100200</v>
       </c>
       <c r="F63" s="11">
@@ -12269,14 +12274,33 @@
       <c r="I78" s="16"/>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B79" s="10"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
+      <c r="B79" s="10">
+        <v>46183</v>
+      </c>
+      <c r="C79" s="11">
+        <v>188380</v>
+      </c>
+      <c r="D79" s="11">
+        <f t="shared" si="0"/>
+        <v>105350</v>
+      </c>
+      <c r="E79" s="11">
+        <f t="shared" si="2"/>
+        <v>100200</v>
+      </c>
+      <c r="F79" s="11">
+        <v>1035150</v>
+      </c>
+      <c r="G79" s="11">
+        <v>28550</v>
+      </c>
+      <c r="H79" s="11">
+        <v>1001450</v>
+      </c>
       <c r="I79" s="16"/>
+      <c r="J79" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="10"/>
@@ -12288,7 +12312,7 @@
       <c r="H80" s="11"/>
       <c r="I80" s="16"/>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="10"/>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
@@ -12298,7 +12322,7 @@
       <c r="H81" s="11"/>
       <c r="I81" s="16"/>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
@@ -12307,8 +12331,9 @@
       <c r="G82" s="11"/>
       <c r="H82" s="11"/>
       <c r="I82" s="16"/>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J82" s="20"/>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="10"/>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
@@ -12318,7 +12343,7 @@
       <c r="H83" s="11"/>
       <c r="I83" s="16"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="10"/>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
